--- a/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
+++ b/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/land/BLAPE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9228989A-591D-DD40-8520-C3C30B0BE105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9120A831-B2DA-C743-ACC8-7132375E1282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4300" yWindow="780" windowWidth="29900" windowHeight="21360" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="UNFCCC" sheetId="5" r:id="rId2"/>
     <sheet name="Growth Rate" sheetId="6" r:id="rId3"/>
-    <sheet name="BLAPE" sheetId="4" r:id="rId4"/>
+    <sheet name="BLAPE-not Adjusted" sheetId="4" r:id="rId4"/>
+    <sheet name="MEF Projections" sheetId="8" r:id="rId5"/>
+    <sheet name="BLAPE" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
   <si>
     <t>BLAPE BAU LULUCF Anthropogenic Pollutant Emissions</t>
   </si>
@@ -210,6 +212,30 @@
   </si>
   <si>
     <t>forestry sector</t>
+  </si>
+  <si>
+    <t>FOLU Emissions (Mt CO2e)</t>
+  </si>
+  <si>
+    <t>FOLU Emissions (g CO2e)</t>
+  </si>
+  <si>
+    <t>Mt CO2e to g CO2e</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Share of CO2 (g)</t>
+  </si>
+  <si>
+    <t>Share of CH4 (g)</t>
+  </si>
+  <si>
+    <t>Share of N2O (g)</t>
+  </si>
+  <si>
+    <t>FOLU Emissions-Adjusted (g CO2e)</t>
   </si>
 </sst>
 </file>
@@ -540,7 +566,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -614,6 +640,28 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -657,6 +705,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1919,10 +1984,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="136" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="39" t="s">
         <v>41</v>
       </c>
       <c r="C1" s="7" t="s">
@@ -1972,28 +2037,28 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37" t="s">
+      <c r="A2" s="38"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="38"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="42"/>
     </row>
     <row r="3" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="43" t="s">
         <v>54</v>
       </c>
       <c r="B3" s="31" t="s">
@@ -2046,7 +2111,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40"/>
+      <c r="A4" s="44"/>
       <c r="B4" s="32" t="s">
         <v>56</v>
       </c>
@@ -2097,7 +2162,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41"/>
+      <c r="A5" s="45"/>
       <c r="B5" s="17" t="s">
         <v>39</v>
       </c>
@@ -2515,7 +2580,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF1F497D"/>
+    <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:AF1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3893,24 +3958,538 @@
       </c>
     </row>
     <row r="14" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="5"/>
+    </row>
     <row r="16" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="33">
+        <f>SUM(B2:B13)</f>
+        <v>182817947544523.97</v>
+      </c>
+      <c r="C18" s="33">
+        <f t="shared" ref="C18:AF18" si="0">SUM(C2:C13)</f>
+        <v>186405810921847.34</v>
+      </c>
+      <c r="D18" s="33">
+        <f t="shared" si="0"/>
+        <v>188362827309478.31</v>
+      </c>
+      <c r="E18" s="33">
+        <f t="shared" si="0"/>
+        <v>190319843697109.5</v>
+      </c>
+      <c r="F18" s="33">
+        <f t="shared" si="0"/>
+        <v>192276860084740.5</v>
+      </c>
+      <c r="G18" s="33">
+        <f t="shared" si="0"/>
+        <v>194233876472371.53</v>
+      </c>
+      <c r="H18" s="33">
+        <f t="shared" si="0"/>
+        <v>196190892860002.53</v>
+      </c>
+      <c r="I18" s="33">
+        <f t="shared" si="0"/>
+        <v>198147909247633.59</v>
+      </c>
+      <c r="J18" s="33">
+        <f t="shared" si="0"/>
+        <v>200104925635264.59</v>
+      </c>
+      <c r="K18" s="33">
+        <f t="shared" si="0"/>
+        <v>202061942022895.59</v>
+      </c>
+      <c r="L18" s="33">
+        <f t="shared" si="0"/>
+        <v>204018958410526.59</v>
+      </c>
+      <c r="M18" s="33">
+        <f t="shared" si="0"/>
+        <v>205975974798157.62</v>
+      </c>
+      <c r="N18" s="33">
+        <f t="shared" si="0"/>
+        <v>207932991185788.66</v>
+      </c>
+      <c r="O18" s="33">
+        <f t="shared" si="0"/>
+        <v>209890007573419.69</v>
+      </c>
+      <c r="P18" s="33">
+        <f t="shared" si="0"/>
+        <v>211847023961050.72</v>
+      </c>
+      <c r="Q18" s="33">
+        <f t="shared" si="0"/>
+        <v>213804040348681.72</v>
+      </c>
+      <c r="R18" s="33">
+        <f t="shared" si="0"/>
+        <v>215761056736312.72</v>
+      </c>
+      <c r="S18" s="33">
+        <f t="shared" si="0"/>
+        <v>217718073123943.78</v>
+      </c>
+      <c r="T18" s="33">
+        <f t="shared" si="0"/>
+        <v>219675089511574.78</v>
+      </c>
+      <c r="U18" s="33">
+        <f t="shared" si="0"/>
+        <v>221632105899205.81</v>
+      </c>
+      <c r="V18" s="33">
+        <f t="shared" si="0"/>
+        <v>223589122286836.81</v>
+      </c>
+      <c r="W18" s="33">
+        <f t="shared" si="0"/>
+        <v>225546138674467.81</v>
+      </c>
+      <c r="X18" s="33">
+        <f t="shared" si="0"/>
+        <v>227503155062098.81</v>
+      </c>
+      <c r="Y18" s="33">
+        <f t="shared" si="0"/>
+        <v>229460171449729.88</v>
+      </c>
+      <c r="Z18" s="33">
+        <f t="shared" si="0"/>
+        <v>231417187837360.88</v>
+      </c>
+      <c r="AA18" s="33">
+        <f t="shared" si="0"/>
+        <v>233374204224991.91</v>
+      </c>
+      <c r="AB18" s="33">
+        <f t="shared" si="0"/>
+        <v>235331220612622.91</v>
+      </c>
+      <c r="AC18" s="33">
+        <f t="shared" si="0"/>
+        <v>237288237000253.91</v>
+      </c>
+      <c r="AD18" s="33">
+        <f t="shared" si="0"/>
+        <v>239245253387884.94</v>
+      </c>
+      <c r="AE18" s="33">
+        <f t="shared" si="0"/>
+        <v>241202269775515.97</v>
+      </c>
+      <c r="AF18" s="33">
+        <f t="shared" si="0"/>
+        <v>243159286163146.97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19">
+        <f>B2/B18</f>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="C19">
+        <f t="shared" ref="C19:AF19" si="1">C2/C18</f>
+        <v>0.98376126824905452</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905452</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905452</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905452</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905452</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905452</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905452</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905452</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="1"/>
+        <v>0.9837612682490543</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="1"/>
+        <v>0.9837612682490543</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="X19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905452</v>
+      </c>
+      <c r="Y19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="Z19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="AA19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="AB19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="AC19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905452</v>
+      </c>
+      <c r="AD19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="AE19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+      <c r="AF19">
+        <f t="shared" si="1"/>
+        <v>0.98376126824905441</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20">
+        <f>B11/B18</f>
+        <v>1.5228283313496759E-2</v>
+      </c>
+      <c r="C20">
+        <f t="shared" ref="C20:AF20" si="2">C11/C18</f>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496759E-2</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496759E-2</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496757E-2</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496757E-2</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496759E-2</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496759E-2</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496757E-2</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496757E-2</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496762E-2</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496759E-2</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496759E-2</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496759E-2</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="X20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496762E-2</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496759E-2</v>
+      </c>
+      <c r="Z20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="AA20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496759E-2</v>
+      </c>
+      <c r="AB20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="AC20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="AD20">
+        <f t="shared" si="2"/>
+        <v>1.5228283313496759E-2</v>
+      </c>
+      <c r="AE20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" si="2"/>
+        <v>1.522828331349676E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21">
+        <f>B12/B18</f>
+        <v>1.0104484374488072E-3</v>
+      </c>
+      <c r="C21">
+        <f t="shared" ref="C21:AF21" si="3">C12/C18</f>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488072E-3</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488076E-3</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488076E-3</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488072E-3</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488072E-3</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488072E-3</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="X21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="Y21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="Z21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="AA21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="AB21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="AD21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="AE21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="3"/>
+        <v>1.0104484374488074E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4883,4 +5462,1974 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1142EC34-7E3E-C64E-8A49-B83C16A04B23}">
+  <dimension ref="A1:AF9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.83203125" customWidth="1"/>
+    <col min="25" max="25" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A1" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="29">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="29">
+        <v>2021</v>
+      </c>
+      <c r="D1" s="29">
+        <v>2022</v>
+      </c>
+      <c r="E1" s="29">
+        <v>2023</v>
+      </c>
+      <c r="F1" s="29">
+        <v>2024</v>
+      </c>
+      <c r="G1" s="29">
+        <v>2025</v>
+      </c>
+      <c r="H1" s="29">
+        <v>2026</v>
+      </c>
+      <c r="I1" s="29">
+        <v>2027</v>
+      </c>
+      <c r="J1" s="29">
+        <v>2028</v>
+      </c>
+      <c r="K1" s="29">
+        <v>2029</v>
+      </c>
+      <c r="L1" s="29">
+        <v>2030</v>
+      </c>
+      <c r="M1" s="29">
+        <v>2031</v>
+      </c>
+      <c r="N1" s="29">
+        <v>2032</v>
+      </c>
+      <c r="O1" s="29">
+        <v>2033</v>
+      </c>
+      <c r="P1" s="29">
+        <v>2034</v>
+      </c>
+      <c r="Q1" s="29">
+        <v>2035</v>
+      </c>
+      <c r="R1" s="29">
+        <v>2036</v>
+      </c>
+      <c r="S1" s="29">
+        <v>2037</v>
+      </c>
+      <c r="T1" s="29">
+        <v>2038</v>
+      </c>
+      <c r="U1" s="29">
+        <v>2039</v>
+      </c>
+      <c r="V1" s="29">
+        <v>2040</v>
+      </c>
+      <c r="W1" s="29">
+        <v>2041</v>
+      </c>
+      <c r="X1" s="29">
+        <v>2042</v>
+      </c>
+      <c r="Y1" s="29">
+        <v>2043</v>
+      </c>
+      <c r="Z1" s="29">
+        <v>2044</v>
+      </c>
+      <c r="AA1" s="29">
+        <v>2045</v>
+      </c>
+      <c r="AB1" s="29">
+        <v>2046</v>
+      </c>
+      <c r="AC1" s="29">
+        <v>2047</v>
+      </c>
+      <c r="AD1" s="29">
+        <v>2048</v>
+      </c>
+      <c r="AE1" s="29">
+        <v>2049</v>
+      </c>
+      <c r="AF1" s="29">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="2">
+        <v>349</v>
+      </c>
+      <c r="C2">
+        <f>$B$2+(($L$2-$B$2)/($L$1-$B$1))*(C1-$B$1)</f>
+        <v>331.1</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ref="D2:K2" si="0">$B$2+(($L$2-$B$2)/($L$1-$B$1))*(D1-$B$1)</f>
+        <v>313.2</v>
+      </c>
+      <c r="E2">
+        <f t="shared" si="0"/>
+        <v>295.3</v>
+      </c>
+      <c r="F2">
+        <f t="shared" si="0"/>
+        <v>277.39999999999998</v>
+      </c>
+      <c r="G2">
+        <f t="shared" si="0"/>
+        <v>259.5</v>
+      </c>
+      <c r="H2">
+        <f t="shared" si="0"/>
+        <v>241.60000000000002</v>
+      </c>
+      <c r="I2">
+        <f t="shared" si="0"/>
+        <v>223.70000000000002</v>
+      </c>
+      <c r="J2">
+        <f t="shared" si="0"/>
+        <v>205.8</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="0"/>
+        <v>187.9</v>
+      </c>
+      <c r="L2" s="2">
+        <v>170</v>
+      </c>
+      <c r="M2">
+        <f>$L$2+(($V$2-$L$2)/($V$1-$L$1))*(M1-$L$1)</f>
+        <v>155.9</v>
+      </c>
+      <c r="N2">
+        <f t="shared" ref="N2:U2" si="1">$L$2+(($V$2-$L$2)/($V$1-$L$1))*(N1-$L$1)</f>
+        <v>141.80000000000001</v>
+      </c>
+      <c r="O2">
+        <f t="shared" si="1"/>
+        <v>127.7</v>
+      </c>
+      <c r="P2">
+        <f t="shared" si="1"/>
+        <v>113.6</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" si="1"/>
+        <v>99.5</v>
+      </c>
+      <c r="R2">
+        <f t="shared" si="1"/>
+        <v>85.4</v>
+      </c>
+      <c r="S2">
+        <f t="shared" si="1"/>
+        <v>71.3</v>
+      </c>
+      <c r="T2">
+        <f t="shared" si="1"/>
+        <v>57.2</v>
+      </c>
+      <c r="U2">
+        <f t="shared" si="1"/>
+        <v>43.100000000000009</v>
+      </c>
+      <c r="V2">
+        <v>29</v>
+      </c>
+      <c r="W2">
+        <f>$V$2+(($AF$2-$V$2)/($AF$1-$V$1))*(W1-$V$1)</f>
+        <v>15.2</v>
+      </c>
+      <c r="X2">
+        <f t="shared" ref="X2:AE2" si="2">$V$2+(($AF$2-$V$2)/($AF$1-$V$1))*(X1-$V$1)</f>
+        <v>1.3999999999999986</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" si="2"/>
+        <v>-12.400000000000006</v>
+      </c>
+      <c r="Z2">
+        <f t="shared" si="2"/>
+        <v>-26.200000000000003</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" si="2"/>
+        <v>-40</v>
+      </c>
+      <c r="AB2">
+        <f t="shared" si="2"/>
+        <v>-53.800000000000011</v>
+      </c>
+      <c r="AC2">
+        <f t="shared" si="2"/>
+        <v>-67.600000000000009</v>
+      </c>
+      <c r="AD2">
+        <f t="shared" si="2"/>
+        <v>-81.400000000000006</v>
+      </c>
+      <c r="AE2">
+        <f t="shared" si="2"/>
+        <v>-95.2</v>
+      </c>
+      <c r="AF2">
+        <v>-109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3">
+        <f>B2*$B$4</f>
+        <v>349000000000000</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:AF3" si="3">C2*$B$4</f>
+        <v>331100000000000</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="3"/>
+        <v>313200000000000</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="3"/>
+        <v>295300000000000</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="3"/>
+        <v>277399999999999.97</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="3"/>
+        <v>259500000000000</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="3"/>
+        <v>241600000000000.03</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="3"/>
+        <v>223700000000000.03</v>
+      </c>
+      <c r="J3">
+        <f t="shared" si="3"/>
+        <v>205800000000000</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="3"/>
+        <v>187900000000000</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="3"/>
+        <v>170000000000000</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="3"/>
+        <v>155900000000000</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="3"/>
+        <v>141800000000000</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="3"/>
+        <v>127700000000000</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="3"/>
+        <v>113600000000000</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="3"/>
+        <v>99500000000000</v>
+      </c>
+      <c r="R3">
+        <f t="shared" si="3"/>
+        <v>85400000000000</v>
+      </c>
+      <c r="S3">
+        <f t="shared" si="3"/>
+        <v>71300000000000</v>
+      </c>
+      <c r="T3">
+        <f t="shared" si="3"/>
+        <v>57200000000000</v>
+      </c>
+      <c r="U3">
+        <f t="shared" si="3"/>
+        <v>43100000000000.008</v>
+      </c>
+      <c r="V3">
+        <f t="shared" si="3"/>
+        <v>29000000000000</v>
+      </c>
+      <c r="W3">
+        <f t="shared" si="3"/>
+        <v>15200000000000</v>
+      </c>
+      <c r="X3">
+        <f t="shared" si="3"/>
+        <v>1399999999999.9985</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" si="3"/>
+        <v>-12400000000000.006</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" si="3"/>
+        <v>-26200000000000.004</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" si="3"/>
+        <v>-40000000000000</v>
+      </c>
+      <c r="AB3">
+        <f t="shared" si="3"/>
+        <v>-53800000000000.008</v>
+      </c>
+      <c r="AC3">
+        <f t="shared" si="3"/>
+        <v>-67600000000000.008</v>
+      </c>
+      <c r="AD3">
+        <f t="shared" si="3"/>
+        <v>-81400000000000</v>
+      </c>
+      <c r="AE3">
+        <f t="shared" si="3"/>
+        <v>-95200000000000</v>
+      </c>
+      <c r="AF3">
+        <f t="shared" si="3"/>
+        <v>-109000000000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4">
+        <v>1000000000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5">
+        <f>B3/2</f>
+        <v>174500000000000</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:AF5" si="4">C3/2</f>
+        <v>165550000000000</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="4"/>
+        <v>156600000000000</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="4"/>
+        <v>147650000000000</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="4"/>
+        <v>138699999999999.98</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="4"/>
+        <v>129750000000000</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="4"/>
+        <v>120800000000000.02</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="4"/>
+        <v>111850000000000.02</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="4"/>
+        <v>102900000000000</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="4"/>
+        <v>93950000000000</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="4"/>
+        <v>85000000000000</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="4"/>
+        <v>77950000000000</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="4"/>
+        <v>70900000000000</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="4"/>
+        <v>63850000000000</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="4"/>
+        <v>56800000000000</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="4"/>
+        <v>49750000000000</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="4"/>
+        <v>42700000000000</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="4"/>
+        <v>35650000000000</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>28600000000000</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>21550000000000.004</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="4"/>
+        <v>14500000000000</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="4"/>
+        <v>7600000000000</v>
+      </c>
+      <c r="X5">
+        <f t="shared" si="4"/>
+        <v>699999999999.99927</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="4"/>
+        <v>-6200000000000.0029</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="4"/>
+        <v>-13100000000000.002</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="4"/>
+        <v>-20000000000000</v>
+      </c>
+      <c r="AB5">
+        <f t="shared" si="4"/>
+        <v>-26900000000000.004</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" si="4"/>
+        <v>-33800000000000.004</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="4"/>
+        <v>-40700000000000</v>
+      </c>
+      <c r="AE5">
+        <f t="shared" si="4"/>
+        <v>-47600000000000</v>
+      </c>
+      <c r="AF5">
+        <f t="shared" si="4"/>
+        <v>-54500000000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="33"/>
+      <c r="AB8" s="33"/>
+      <c r="AC8" s="33"/>
+      <c r="AD8" s="33"/>
+      <c r="AE8" s="33"/>
+      <c r="AF8" s="33"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="Y9" s="33"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F60411-ADAC-D94F-9CA3-BD5BA5358F0E}">
+  <sheetPr>
+    <tabColor rgb="FF002060"/>
+  </sheetPr>
+  <dimension ref="A1:AF24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A1" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="34">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="34">
+        <v>2021</v>
+      </c>
+      <c r="D1" s="34">
+        <v>2022</v>
+      </c>
+      <c r="E1" s="34">
+        <v>2023</v>
+      </c>
+      <c r="F1" s="34">
+        <v>2024</v>
+      </c>
+      <c r="G1" s="34">
+        <v>2025</v>
+      </c>
+      <c r="H1" s="34">
+        <v>2026</v>
+      </c>
+      <c r="I1" s="34">
+        <v>2027</v>
+      </c>
+      <c r="J1" s="34">
+        <v>2028</v>
+      </c>
+      <c r="K1" s="34">
+        <v>2029</v>
+      </c>
+      <c r="L1" s="34">
+        <v>2030</v>
+      </c>
+      <c r="M1" s="34">
+        <v>2031</v>
+      </c>
+      <c r="N1" s="34">
+        <v>2032</v>
+      </c>
+      <c r="O1" s="34">
+        <v>2033</v>
+      </c>
+      <c r="P1" s="34">
+        <v>2034</v>
+      </c>
+      <c r="Q1" s="34">
+        <v>2035</v>
+      </c>
+      <c r="R1" s="34">
+        <v>2036</v>
+      </c>
+      <c r="S1" s="34">
+        <v>2037</v>
+      </c>
+      <c r="T1" s="34">
+        <v>2038</v>
+      </c>
+      <c r="U1" s="34">
+        <v>2039</v>
+      </c>
+      <c r="V1" s="34">
+        <v>2040</v>
+      </c>
+      <c r="W1" s="34">
+        <v>2041</v>
+      </c>
+      <c r="X1" s="34">
+        <v>2042</v>
+      </c>
+      <c r="Y1" s="34">
+        <v>2043</v>
+      </c>
+      <c r="Z1" s="34">
+        <v>2044</v>
+      </c>
+      <c r="AA1" s="34">
+        <v>2045</v>
+      </c>
+      <c r="AB1" s="34">
+        <v>2046</v>
+      </c>
+      <c r="AC1" s="34">
+        <v>2047</v>
+      </c>
+      <c r="AD1" s="34">
+        <v>2048</v>
+      </c>
+      <c r="AE1" s="34">
+        <v>2049</v>
+      </c>
+      <c r="AF1" s="34">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A2" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="36">
+        <f>'BLAPE-not Adjusted'!B19*'MEF Projections'!B5</f>
+        <v>171666341309460</v>
+      </c>
+      <c r="C2" s="36">
+        <f>'BLAPE-not Adjusted'!C19*'MEF Projections'!C5</f>
+        <v>162861677958630.97</v>
+      </c>
+      <c r="D2" s="36">
+        <f>'BLAPE-not Adjusted'!D19*'MEF Projections'!D5</f>
+        <v>154057014607801.91</v>
+      </c>
+      <c r="E2" s="36">
+        <f>'BLAPE-not Adjusted'!E19*'MEF Projections'!E5</f>
+        <v>145252351256972.88</v>
+      </c>
+      <c r="F2" s="36">
+        <f>'BLAPE-not Adjusted'!F19*'MEF Projections'!F5</f>
+        <v>136447687906143.84</v>
+      </c>
+      <c r="G2" s="36">
+        <f>'BLAPE-not Adjusted'!G19*'MEF Projections'!G5</f>
+        <v>127643024555314.83</v>
+      </c>
+      <c r="H2" s="36">
+        <f>'BLAPE-not Adjusted'!H19*'MEF Projections'!H5</f>
+        <v>118838361204485.8</v>
+      </c>
+      <c r="I2" s="36">
+        <f>'BLAPE-not Adjusted'!I19*'MEF Projections'!I5</f>
+        <v>110033697853656.75</v>
+      </c>
+      <c r="J2" s="36">
+        <f>'BLAPE-not Adjusted'!J19*'MEF Projections'!J5</f>
+        <v>101229034502827.7</v>
+      </c>
+      <c r="K2" s="36">
+        <f>'BLAPE-not Adjusted'!K19*'MEF Projections'!K5</f>
+        <v>92424371151998.672</v>
+      </c>
+      <c r="L2" s="36">
+        <f>'BLAPE-not Adjusted'!L19*'MEF Projections'!L5</f>
+        <v>83619707801169.641</v>
+      </c>
+      <c r="M2" s="36">
+        <f>'BLAPE-not Adjusted'!M19*'MEF Projections'!M5</f>
+        <v>76684190860013.797</v>
+      </c>
+      <c r="N2" s="36">
+        <f>'BLAPE-not Adjusted'!N19*'MEF Projections'!N5</f>
+        <v>69748673918857.961</v>
+      </c>
+      <c r="O2" s="36">
+        <f>'BLAPE-not Adjusted'!O19*'MEF Projections'!O5</f>
+        <v>62813156977702.133</v>
+      </c>
+      <c r="P2" s="36">
+        <f>'BLAPE-not Adjusted'!P19*'MEF Projections'!P5</f>
+        <v>55877640036546.289</v>
+      </c>
+      <c r="Q2" s="36">
+        <f>'BLAPE-not Adjusted'!Q19*'MEF Projections'!Q5</f>
+        <v>48942123095390.453</v>
+      </c>
+      <c r="R2" s="36">
+        <f>'BLAPE-not Adjusted'!R19*'MEF Projections'!R5</f>
+        <v>42006606154234.625</v>
+      </c>
+      <c r="S2" s="36">
+        <f>'BLAPE-not Adjusted'!S19*'MEF Projections'!S5</f>
+        <v>35071089213078.785</v>
+      </c>
+      <c r="T2" s="36">
+        <f>'BLAPE-not Adjusted'!T19*'MEF Projections'!T5</f>
+        <v>28135572271922.953</v>
+      </c>
+      <c r="U2" s="36">
+        <f>'BLAPE-not Adjusted'!U19*'MEF Projections'!U5</f>
+        <v>21200055330767.125</v>
+      </c>
+      <c r="V2" s="36">
+        <f>'BLAPE-not Adjusted'!V19*'MEF Projections'!V5</f>
+        <v>14264538389611.289</v>
+      </c>
+      <c r="W2" s="36">
+        <f>'BLAPE-not Adjusted'!W19*'MEF Projections'!W5</f>
+        <v>7476585638692.8135</v>
+      </c>
+      <c r="X2" s="36">
+        <f>'BLAPE-not Adjusted'!X19*'MEF Projections'!X5</f>
+        <v>688632887774.3374</v>
+      </c>
+      <c r="Y2" s="36">
+        <f>'BLAPE-not Adjusted'!Y19*'MEF Projections'!Y5</f>
+        <v>-6099319863144.1406</v>
+      </c>
+      <c r="Z2" s="36">
+        <f>'BLAPE-not Adjusted'!Z19*'MEF Projections'!Z5</f>
+        <v>-12887272614062.615</v>
+      </c>
+      <c r="AA2" s="36">
+        <f>'BLAPE-not Adjusted'!AA19*'MEF Projections'!AA5</f>
+        <v>-19675225364981.09</v>
+      </c>
+      <c r="AB2" s="36">
+        <f>'BLAPE-not Adjusted'!AB19*'MEF Projections'!AB5</f>
+        <v>-26463178115899.566</v>
+      </c>
+      <c r="AC2" s="36">
+        <f>'BLAPE-not Adjusted'!AC19*'MEF Projections'!AC5</f>
+        <v>-33251130866818.047</v>
+      </c>
+      <c r="AD2" s="36">
+        <f>'BLAPE-not Adjusted'!AD19*'MEF Projections'!AD5</f>
+        <v>-40039083617736.516</v>
+      </c>
+      <c r="AE2" s="36">
+        <f>'BLAPE-not Adjusted'!AE19*'MEF Projections'!AE5</f>
+        <v>-46827036368654.992</v>
+      </c>
+      <c r="AF2" s="36">
+        <f>'BLAPE-not Adjusted'!AF19*'MEF Projections'!AF5</f>
+        <v>-53614989119573.469</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A3" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="36">
+        <v>0</v>
+      </c>
+      <c r="C3" s="36">
+        <v>0</v>
+      </c>
+      <c r="D3" s="36">
+        <v>0</v>
+      </c>
+      <c r="E3" s="36">
+        <v>0</v>
+      </c>
+      <c r="F3" s="36">
+        <v>0</v>
+      </c>
+      <c r="G3" s="36">
+        <v>0</v>
+      </c>
+      <c r="H3" s="36">
+        <v>0</v>
+      </c>
+      <c r="I3" s="36">
+        <v>0</v>
+      </c>
+      <c r="J3" s="36">
+        <v>0</v>
+      </c>
+      <c r="K3" s="36">
+        <v>0</v>
+      </c>
+      <c r="L3" s="36">
+        <v>0</v>
+      </c>
+      <c r="M3" s="36">
+        <v>0</v>
+      </c>
+      <c r="N3" s="36">
+        <v>0</v>
+      </c>
+      <c r="O3" s="36">
+        <v>0</v>
+      </c>
+      <c r="P3" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="36">
+        <v>0</v>
+      </c>
+      <c r="R3" s="36">
+        <v>0</v>
+      </c>
+      <c r="S3" s="36">
+        <v>0</v>
+      </c>
+      <c r="T3" s="36">
+        <v>0</v>
+      </c>
+      <c r="U3" s="36">
+        <v>0</v>
+      </c>
+      <c r="V3" s="36">
+        <v>0</v>
+      </c>
+      <c r="W3" s="36">
+        <v>0</v>
+      </c>
+      <c r="X3" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="36">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="36">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="36">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A4" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="36">
+        <v>0</v>
+      </c>
+      <c r="C4" s="36">
+        <v>0</v>
+      </c>
+      <c r="D4" s="36">
+        <v>0</v>
+      </c>
+      <c r="E4" s="36">
+        <v>0</v>
+      </c>
+      <c r="F4" s="36">
+        <v>0</v>
+      </c>
+      <c r="G4" s="36">
+        <v>0</v>
+      </c>
+      <c r="H4" s="36">
+        <v>0</v>
+      </c>
+      <c r="I4" s="36">
+        <v>0</v>
+      </c>
+      <c r="J4" s="36">
+        <v>0</v>
+      </c>
+      <c r="K4" s="36">
+        <v>0</v>
+      </c>
+      <c r="L4" s="36">
+        <v>0</v>
+      </c>
+      <c r="M4" s="36">
+        <v>0</v>
+      </c>
+      <c r="N4" s="36">
+        <v>0</v>
+      </c>
+      <c r="O4" s="36">
+        <v>0</v>
+      </c>
+      <c r="P4" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="36">
+        <v>0</v>
+      </c>
+      <c r="R4" s="36">
+        <v>0</v>
+      </c>
+      <c r="S4" s="36">
+        <v>0</v>
+      </c>
+      <c r="T4" s="36">
+        <v>0</v>
+      </c>
+      <c r="U4" s="36">
+        <v>0</v>
+      </c>
+      <c r="V4" s="36">
+        <v>0</v>
+      </c>
+      <c r="W4" s="36">
+        <v>0</v>
+      </c>
+      <c r="X4" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="36">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="36">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="36">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A5" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="36">
+        <v>0</v>
+      </c>
+      <c r="C5" s="36">
+        <v>0</v>
+      </c>
+      <c r="D5" s="36">
+        <v>0</v>
+      </c>
+      <c r="E5" s="36">
+        <v>0</v>
+      </c>
+      <c r="F5" s="36">
+        <v>0</v>
+      </c>
+      <c r="G5" s="36">
+        <v>0</v>
+      </c>
+      <c r="H5" s="36">
+        <v>0</v>
+      </c>
+      <c r="I5" s="36">
+        <v>0</v>
+      </c>
+      <c r="J5" s="36">
+        <v>0</v>
+      </c>
+      <c r="K5" s="36">
+        <v>0</v>
+      </c>
+      <c r="L5" s="36">
+        <v>0</v>
+      </c>
+      <c r="M5" s="36">
+        <v>0</v>
+      </c>
+      <c r="N5" s="36">
+        <v>0</v>
+      </c>
+      <c r="O5" s="36">
+        <v>0</v>
+      </c>
+      <c r="P5" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="36">
+        <v>0</v>
+      </c>
+      <c r="R5" s="36">
+        <v>0</v>
+      </c>
+      <c r="S5" s="36">
+        <v>0</v>
+      </c>
+      <c r="T5" s="36">
+        <v>0</v>
+      </c>
+      <c r="U5" s="36">
+        <v>0</v>
+      </c>
+      <c r="V5" s="36">
+        <v>0</v>
+      </c>
+      <c r="W5" s="36">
+        <v>0</v>
+      </c>
+      <c r="X5" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="36">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="36">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="36">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A6" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="36">
+        <v>0</v>
+      </c>
+      <c r="C6" s="36">
+        <v>0</v>
+      </c>
+      <c r="D6" s="36">
+        <v>0</v>
+      </c>
+      <c r="E6" s="36">
+        <v>0</v>
+      </c>
+      <c r="F6" s="36">
+        <v>0</v>
+      </c>
+      <c r="G6" s="36">
+        <v>0</v>
+      </c>
+      <c r="H6" s="36">
+        <v>0</v>
+      </c>
+      <c r="I6" s="36">
+        <v>0</v>
+      </c>
+      <c r="J6" s="36">
+        <v>0</v>
+      </c>
+      <c r="K6" s="36">
+        <v>0</v>
+      </c>
+      <c r="L6" s="36">
+        <v>0</v>
+      </c>
+      <c r="M6" s="36">
+        <v>0</v>
+      </c>
+      <c r="N6" s="36">
+        <v>0</v>
+      </c>
+      <c r="O6" s="36">
+        <v>0</v>
+      </c>
+      <c r="P6" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="36">
+        <v>0</v>
+      </c>
+      <c r="R6" s="36">
+        <v>0</v>
+      </c>
+      <c r="S6" s="36">
+        <v>0</v>
+      </c>
+      <c r="T6" s="36">
+        <v>0</v>
+      </c>
+      <c r="U6" s="36">
+        <v>0</v>
+      </c>
+      <c r="V6" s="36">
+        <v>0</v>
+      </c>
+      <c r="W6" s="36">
+        <v>0</v>
+      </c>
+      <c r="X6" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="36">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="36">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="36">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A7" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="36">
+        <v>0</v>
+      </c>
+      <c r="C7" s="36">
+        <v>0</v>
+      </c>
+      <c r="D7" s="36">
+        <v>0</v>
+      </c>
+      <c r="E7" s="36">
+        <v>0</v>
+      </c>
+      <c r="F7" s="36">
+        <v>0</v>
+      </c>
+      <c r="G7" s="36">
+        <v>0</v>
+      </c>
+      <c r="H7" s="36">
+        <v>0</v>
+      </c>
+      <c r="I7" s="36">
+        <v>0</v>
+      </c>
+      <c r="J7" s="36">
+        <v>0</v>
+      </c>
+      <c r="K7" s="36">
+        <v>0</v>
+      </c>
+      <c r="L7" s="36">
+        <v>0</v>
+      </c>
+      <c r="M7" s="36">
+        <v>0</v>
+      </c>
+      <c r="N7" s="36">
+        <v>0</v>
+      </c>
+      <c r="O7" s="36">
+        <v>0</v>
+      </c>
+      <c r="P7" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="36">
+        <v>0</v>
+      </c>
+      <c r="R7" s="36">
+        <v>0</v>
+      </c>
+      <c r="S7" s="36">
+        <v>0</v>
+      </c>
+      <c r="T7" s="36">
+        <v>0</v>
+      </c>
+      <c r="U7" s="36">
+        <v>0</v>
+      </c>
+      <c r="V7" s="36">
+        <v>0</v>
+      </c>
+      <c r="W7" s="36">
+        <v>0</v>
+      </c>
+      <c r="X7" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="36">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="36">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="36">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="36">
+        <v>0</v>
+      </c>
+      <c r="C8" s="36">
+        <v>0</v>
+      </c>
+      <c r="D8" s="36">
+        <v>0</v>
+      </c>
+      <c r="E8" s="36">
+        <v>0</v>
+      </c>
+      <c r="F8" s="36">
+        <v>0</v>
+      </c>
+      <c r="G8" s="36">
+        <v>0</v>
+      </c>
+      <c r="H8" s="36">
+        <v>0</v>
+      </c>
+      <c r="I8" s="36">
+        <v>0</v>
+      </c>
+      <c r="J8" s="36">
+        <v>0</v>
+      </c>
+      <c r="K8" s="36">
+        <v>0</v>
+      </c>
+      <c r="L8" s="36">
+        <v>0</v>
+      </c>
+      <c r="M8" s="36">
+        <v>0</v>
+      </c>
+      <c r="N8" s="36">
+        <v>0</v>
+      </c>
+      <c r="O8" s="36">
+        <v>0</v>
+      </c>
+      <c r="P8" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="36">
+        <v>0</v>
+      </c>
+      <c r="R8" s="36">
+        <v>0</v>
+      </c>
+      <c r="S8" s="36">
+        <v>0</v>
+      </c>
+      <c r="T8" s="36">
+        <v>0</v>
+      </c>
+      <c r="U8" s="36">
+        <v>0</v>
+      </c>
+      <c r="V8" s="36">
+        <v>0</v>
+      </c>
+      <c r="W8" s="36">
+        <v>0</v>
+      </c>
+      <c r="X8" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="36">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="36">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="36">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A9" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="36">
+        <v>0</v>
+      </c>
+      <c r="C9" s="36">
+        <v>0</v>
+      </c>
+      <c r="D9" s="36">
+        <v>0</v>
+      </c>
+      <c r="E9" s="36">
+        <v>0</v>
+      </c>
+      <c r="F9" s="36">
+        <v>0</v>
+      </c>
+      <c r="G9" s="36">
+        <v>0</v>
+      </c>
+      <c r="H9" s="36">
+        <v>0</v>
+      </c>
+      <c r="I9" s="36">
+        <v>0</v>
+      </c>
+      <c r="J9" s="36">
+        <v>0</v>
+      </c>
+      <c r="K9" s="36">
+        <v>0</v>
+      </c>
+      <c r="L9" s="36">
+        <v>0</v>
+      </c>
+      <c r="M9" s="36">
+        <v>0</v>
+      </c>
+      <c r="N9" s="36">
+        <v>0</v>
+      </c>
+      <c r="O9" s="36">
+        <v>0</v>
+      </c>
+      <c r="P9" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="36">
+        <v>0</v>
+      </c>
+      <c r="R9" s="36">
+        <v>0</v>
+      </c>
+      <c r="S9" s="36">
+        <v>0</v>
+      </c>
+      <c r="T9" s="36">
+        <v>0</v>
+      </c>
+      <c r="U9" s="36">
+        <v>0</v>
+      </c>
+      <c r="V9" s="36">
+        <v>0</v>
+      </c>
+      <c r="W9" s="36">
+        <v>0</v>
+      </c>
+      <c r="X9" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="36">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="36">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="36">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A10" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="36">
+        <v>0</v>
+      </c>
+      <c r="C10" s="36">
+        <v>0</v>
+      </c>
+      <c r="D10" s="36">
+        <v>0</v>
+      </c>
+      <c r="E10" s="36">
+        <v>0</v>
+      </c>
+      <c r="F10" s="36">
+        <v>0</v>
+      </c>
+      <c r="G10" s="36">
+        <v>0</v>
+      </c>
+      <c r="H10" s="36">
+        <v>0</v>
+      </c>
+      <c r="I10" s="36">
+        <v>0</v>
+      </c>
+      <c r="J10" s="36">
+        <v>0</v>
+      </c>
+      <c r="K10" s="36">
+        <v>0</v>
+      </c>
+      <c r="L10" s="36">
+        <v>0</v>
+      </c>
+      <c r="M10" s="36">
+        <v>0</v>
+      </c>
+      <c r="N10" s="36">
+        <v>0</v>
+      </c>
+      <c r="O10" s="36">
+        <v>0</v>
+      </c>
+      <c r="P10" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="36">
+        <v>0</v>
+      </c>
+      <c r="R10" s="36">
+        <v>0</v>
+      </c>
+      <c r="S10" s="36">
+        <v>0</v>
+      </c>
+      <c r="T10" s="36">
+        <v>0</v>
+      </c>
+      <c r="U10" s="36">
+        <v>0</v>
+      </c>
+      <c r="V10" s="36">
+        <v>0</v>
+      </c>
+      <c r="W10" s="36">
+        <v>0</v>
+      </c>
+      <c r="X10" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="36">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="36">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="36">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A11" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="36">
+        <f>'BLAPE-not Adjusted'!B20*'MEF Projections'!B5</f>
+        <v>2657335438205.1846</v>
+      </c>
+      <c r="C11" s="36">
+        <f>'BLAPE-not Adjusted'!C20*'MEF Projections'!C5</f>
+        <v>2521042302549.3887</v>
+      </c>
+      <c r="D11" s="36">
+        <f>'BLAPE-not Adjusted'!D20*'MEF Projections'!D5</f>
+        <v>2384749166893.5923</v>
+      </c>
+      <c r="E11" s="36">
+        <f>'BLAPE-not Adjusted'!E20*'MEF Projections'!E5</f>
+        <v>2248456031237.7964</v>
+      </c>
+      <c r="F11" s="36">
+        <f>'BLAPE-not Adjusted'!F20*'MEF Projections'!F5</f>
+        <v>2112162895582.0005</v>
+      </c>
+      <c r="G11" s="36">
+        <f>'BLAPE-not Adjusted'!G20*'MEF Projections'!G5</f>
+        <v>1975869759926.2046</v>
+      </c>
+      <c r="H11" s="36">
+        <f>'BLAPE-not Adjusted'!H20*'MEF Projections'!H5</f>
+        <v>1839576624270.4089</v>
+      </c>
+      <c r="I11" s="36">
+        <f>'BLAPE-not Adjusted'!I20*'MEF Projections'!I5</f>
+        <v>1703283488614.6125</v>
+      </c>
+      <c r="J11" s="36">
+        <f>'BLAPE-not Adjusted'!J20*'MEF Projections'!J5</f>
+        <v>1566990352958.8162</v>
+      </c>
+      <c r="K11" s="36">
+        <f>'BLAPE-not Adjusted'!K20*'MEF Projections'!K5</f>
+        <v>1430697217303.0205</v>
+      </c>
+      <c r="L11" s="36">
+        <f>'BLAPE-not Adjusted'!L20*'MEF Projections'!L5</f>
+        <v>1294404081647.2246</v>
+      </c>
+      <c r="M11" s="36">
+        <f>'BLAPE-not Adjusted'!M20*'MEF Projections'!M5</f>
+        <v>1187044684287.0723</v>
+      </c>
+      <c r="N11" s="36">
+        <f>'BLAPE-not Adjusted'!N20*'MEF Projections'!N5</f>
+        <v>1079685286926.9203</v>
+      </c>
+      <c r="O11" s="36">
+        <f>'BLAPE-not Adjusted'!O20*'MEF Projections'!O5</f>
+        <v>972325889566.76807</v>
+      </c>
+      <c r="P11" s="36">
+        <f>'BLAPE-not Adjusted'!P20*'MEF Projections'!P5</f>
+        <v>864966492206.61584</v>
+      </c>
+      <c r="Q11" s="36">
+        <f>'BLAPE-not Adjusted'!Q20*'MEF Projections'!Q5</f>
+        <v>757607094846.46362</v>
+      </c>
+      <c r="R11" s="36">
+        <f>'BLAPE-not Adjusted'!R20*'MEF Projections'!R5</f>
+        <v>650247697486.31177</v>
+      </c>
+      <c r="S11" s="36">
+        <f>'BLAPE-not Adjusted'!S20*'MEF Projections'!S5</f>
+        <v>542888300126.15942</v>
+      </c>
+      <c r="T11" s="36">
+        <f>'BLAPE-not Adjusted'!T20*'MEF Projections'!T5</f>
+        <v>435528902766.00726</v>
+      </c>
+      <c r="U11" s="36">
+        <f>'BLAPE-not Adjusted'!U20*'MEF Projections'!U5</f>
+        <v>328169505405.85522</v>
+      </c>
+      <c r="V11" s="36">
+        <f>'BLAPE-not Adjusted'!V20*'MEF Projections'!V5</f>
+        <v>220810108045.70303</v>
+      </c>
+      <c r="W11" s="36">
+        <f>'BLAPE-not Adjusted'!W20*'MEF Projections'!W5</f>
+        <v>115734953182.57538</v>
+      </c>
+      <c r="X11" s="36">
+        <f>'BLAPE-not Adjusted'!X20*'MEF Projections'!X5</f>
+        <v>10659798319.447721</v>
+      </c>
+      <c r="Y11" s="36">
+        <f>'BLAPE-not Adjusted'!Y20*'MEF Projections'!Y5</f>
+        <v>-94415356543.679947</v>
+      </c>
+      <c r="Z11" s="36">
+        <f>'BLAPE-not Adjusted'!Z20*'MEF Projections'!Z5</f>
+        <v>-199490511406.80759</v>
+      </c>
+      <c r="AA11" s="36">
+        <f>'BLAPE-not Adjusted'!AA20*'MEF Projections'!AA5</f>
+        <v>-304565666269.93518</v>
+      </c>
+      <c r="AB11" s="36">
+        <f>'BLAPE-not Adjusted'!AB20*'MEF Projections'!AB5</f>
+        <v>-409640821133.06293</v>
+      </c>
+      <c r="AC11" s="36">
+        <f>'BLAPE-not Adjusted'!AC20*'MEF Projections'!AC5</f>
+        <v>-514715975996.19055</v>
+      </c>
+      <c r="AD11" s="36">
+        <f>'BLAPE-not Adjusted'!AD20*'MEF Projections'!AD5</f>
+        <v>-619791130859.31812</v>
+      </c>
+      <c r="AE11" s="36">
+        <f>'BLAPE-not Adjusted'!AE20*'MEF Projections'!AE5</f>
+        <v>-724866285722.4458</v>
+      </c>
+      <c r="AF11" s="36">
+        <f>'BLAPE-not Adjusted'!AF20*'MEF Projections'!AF5</f>
+        <v>-829941440585.57349</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A12" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="36">
+        <f>'BLAPE-not Adjusted'!B21*'MEF Projections'!B5</f>
+        <v>176323252334.81686</v>
+      </c>
+      <c r="C12" s="36">
+        <f>'BLAPE-not Adjusted'!C21*'MEF Projections'!C5</f>
+        <v>167279738819.65005</v>
+      </c>
+      <c r="D12" s="36">
+        <f>'BLAPE-not Adjusted'!D21*'MEF Projections'!D5</f>
+        <v>158236225304.48322</v>
+      </c>
+      <c r="E12" s="36">
+        <f>'BLAPE-not Adjusted'!E21*'MEF Projections'!E5</f>
+        <v>149192711789.31641</v>
+      </c>
+      <c r="F12" s="36">
+        <f>'BLAPE-not Adjusted'!F21*'MEF Projections'!F5</f>
+        <v>140149198274.1496</v>
+      </c>
+      <c r="G12" s="36">
+        <f>'BLAPE-not Adjusted'!G21*'MEF Projections'!G5</f>
+        <v>131105684758.98276</v>
+      </c>
+      <c r="H12" s="36">
+        <f>'BLAPE-not Adjusted'!H21*'MEF Projections'!H5</f>
+        <v>122062171243.81595</v>
+      </c>
+      <c r="I12" s="36">
+        <f>'BLAPE-not Adjusted'!I21*'MEF Projections'!I5</f>
+        <v>113018657728.64912</v>
+      </c>
+      <c r="J12" s="36">
+        <f>'BLAPE-not Adjusted'!J21*'MEF Projections'!J5</f>
+        <v>103975144213.48228</v>
+      </c>
+      <c r="K12" s="36">
+        <f>'BLAPE-not Adjusted'!K21*'MEF Projections'!K5</f>
+        <v>94931630698.31546</v>
+      </c>
+      <c r="L12" s="36">
+        <f>'BLAPE-not Adjusted'!L21*'MEF Projections'!L5</f>
+        <v>85888117183.148651</v>
+      </c>
+      <c r="M12" s="36">
+        <f>'BLAPE-not Adjusted'!M21*'MEF Projections'!M5</f>
+        <v>78764455699.134537</v>
+      </c>
+      <c r="N12" s="36">
+        <f>'BLAPE-not Adjusted'!N21*'MEF Projections'!N5</f>
+        <v>71640794215.120438</v>
+      </c>
+      <c r="O12" s="36">
+        <f>'BLAPE-not Adjusted'!O21*'MEF Projections'!O5</f>
+        <v>64517132731.106339</v>
+      </c>
+      <c r="P12" s="36">
+        <f>'BLAPE-not Adjusted'!P21*'MEF Projections'!P5</f>
+        <v>57393471247.092247</v>
+      </c>
+      <c r="Q12" s="36">
+        <f>'BLAPE-not Adjusted'!Q21*'MEF Projections'!Q5</f>
+        <v>50269809763.078163</v>
+      </c>
+      <c r="R12" s="36">
+        <f>'BLAPE-not Adjusted'!R21*'MEF Projections'!R5</f>
+        <v>43146148279.064072</v>
+      </c>
+      <c r="S12" s="36">
+        <f>'BLAPE-not Adjusted'!S21*'MEF Projections'!S5</f>
+        <v>36022486795.049973</v>
+      </c>
+      <c r="T12" s="36">
+        <f>'BLAPE-not Adjusted'!T21*'MEF Projections'!T5</f>
+        <v>28898825311.035892</v>
+      </c>
+      <c r="U12" s="36">
+        <f>'BLAPE-not Adjusted'!U21*'MEF Projections'!U5</f>
+        <v>21775163827.021801</v>
+      </c>
+      <c r="V12" s="36">
+        <f>'BLAPE-not Adjusted'!V21*'MEF Projections'!V5</f>
+        <v>14651502343.007708</v>
+      </c>
+      <c r="W12" s="36">
+        <f>'BLAPE-not Adjusted'!W21*'MEF Projections'!W5</f>
+        <v>7679408124.6109362</v>
+      </c>
+      <c r="X12" s="36">
+        <f>'BLAPE-not Adjusted'!X21*'MEF Projections'!X5</f>
+        <v>707313906.21416438</v>
+      </c>
+      <c r="Y12" s="36">
+        <f>'BLAPE-not Adjusted'!Y21*'MEF Projections'!Y5</f>
+        <v>-6264780312.1826086</v>
+      </c>
+      <c r="Z12" s="36">
+        <f>'BLAPE-not Adjusted'!Z21*'MEF Projections'!Z5</f>
+        <v>-13236874530.579378</v>
+      </c>
+      <c r="AA12" s="36">
+        <f>'BLAPE-not Adjusted'!AA21*'MEF Projections'!AA5</f>
+        <v>-20208968748.976147</v>
+      </c>
+      <c r="AB12" s="36">
+        <f>'BLAPE-not Adjusted'!AB21*'MEF Projections'!AB5</f>
+        <v>-27181062967.372921</v>
+      </c>
+      <c r="AC12" s="36">
+        <f>'BLAPE-not Adjusted'!AC21*'MEF Projections'!AC5</f>
+        <v>-34153157185.769691</v>
+      </c>
+      <c r="AD12" s="36">
+        <f>'BLAPE-not Adjusted'!AD21*'MEF Projections'!AD5</f>
+        <v>-41125251404.166458</v>
+      </c>
+      <c r="AE12" s="36">
+        <f>'BLAPE-not Adjusted'!AE21*'MEF Projections'!AE5</f>
+        <v>-48097345622.563232</v>
+      </c>
+      <c r="AF12" s="36">
+        <f>'BLAPE-not Adjusted'!AF21*'MEF Projections'!AF5</f>
+        <v>-55069439840.959999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A13" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="36">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36">
+        <v>0</v>
+      </c>
+      <c r="D13" s="36">
+        <v>0</v>
+      </c>
+      <c r="E13" s="36">
+        <v>0</v>
+      </c>
+      <c r="F13" s="36">
+        <v>0</v>
+      </c>
+      <c r="G13" s="36">
+        <v>0</v>
+      </c>
+      <c r="H13" s="36">
+        <v>0</v>
+      </c>
+      <c r="I13" s="36">
+        <v>0</v>
+      </c>
+      <c r="J13" s="36">
+        <v>0</v>
+      </c>
+      <c r="K13" s="36">
+        <v>0</v>
+      </c>
+      <c r="L13" s="36">
+        <v>0</v>
+      </c>
+      <c r="M13" s="36">
+        <v>0</v>
+      </c>
+      <c r="N13" s="36">
+        <v>0</v>
+      </c>
+      <c r="O13" s="36">
+        <v>0</v>
+      </c>
+      <c r="P13" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="36">
+        <v>0</v>
+      </c>
+      <c r="R13" s="36">
+        <v>0</v>
+      </c>
+      <c r="S13" s="36">
+        <v>0</v>
+      </c>
+      <c r="T13" s="36">
+        <v>0</v>
+      </c>
+      <c r="U13" s="36">
+        <v>0</v>
+      </c>
+      <c r="V13" s="36">
+        <v>0</v>
+      </c>
+      <c r="W13" s="36">
+        <v>0</v>
+      </c>
+      <c r="X13" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="36">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="36">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="36">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="36">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A16" s="5"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="33"/>
+      <c r="AA16" s="33"/>
+      <c r="AB16" s="33"/>
+      <c r="AC16" s="33"/>
+      <c r="AD16" s="33"/>
+      <c r="AE16" s="33"/>
+      <c r="AF16" s="33"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="29"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="29"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
+++ b/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
@@ -1,24 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/land/BLAPE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9120A831-B2DA-C743-ACC8-7132375E1282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9228989A-591D-DD40-8520-C3C30B0BE105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4300" yWindow="780" windowWidth="29900" windowHeight="21360" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="UNFCCC" sheetId="5" r:id="rId2"/>
     <sheet name="Growth Rate" sheetId="6" r:id="rId3"/>
-    <sheet name="BLAPE-not Adjusted" sheetId="4" r:id="rId4"/>
-    <sheet name="MEF Projections" sheetId="8" r:id="rId5"/>
-    <sheet name="BLAPE" sheetId="7" r:id="rId6"/>
+    <sheet name="BLAPE" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>BLAPE BAU LULUCF Anthropogenic Pollutant Emissions</t>
   </si>
@@ -212,30 +210,6 @@
   </si>
   <si>
     <t>forestry sector</t>
-  </si>
-  <si>
-    <t>FOLU Emissions (Mt CO2e)</t>
-  </si>
-  <si>
-    <t>FOLU Emissions (g CO2e)</t>
-  </si>
-  <si>
-    <t>Mt CO2e to g CO2e</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Share of CO2 (g)</t>
-  </si>
-  <si>
-    <t>Share of CH4 (g)</t>
-  </si>
-  <si>
-    <t>Share of N2O (g)</t>
-  </si>
-  <si>
-    <t>FOLU Emissions-Adjusted (g CO2e)</t>
   </si>
 </sst>
 </file>
@@ -566,7 +540,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -640,28 +614,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -705,23 +657,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <bag type="Checkbox"/>
-  <bag type="XFControls">
-    <bagId k="CellControl">0</bagId>
-  </bag>
-  <bag type="XFComplement">
-    <bagId k="XFControls">1</bagId>
-  </bag>
-  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <a k="MappedFeaturePropertyBags">
-      <bagId>2</bagId>
-    </a>
-  </bag>
-</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1984,10 +1919,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="136" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="35" t="s">
         <v>41</v>
       </c>
       <c r="C1" s="7" t="s">
@@ -2037,28 +1972,28 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="41" t="s">
+      <c r="A2" s="34"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="42"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="38"/>
     </row>
     <row r="3" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="39" t="s">
         <v>54</v>
       </c>
       <c r="B3" s="31" t="s">
@@ -2111,7 +2046,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44"/>
+      <c r="A4" s="40"/>
       <c r="B4" s="32" t="s">
         <v>56</v>
       </c>
@@ -2162,7 +2097,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="45"/>
+      <c r="A5" s="41"/>
       <c r="B5" s="17" t="s">
         <v>39</v>
       </c>
@@ -2580,7 +2515,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
-    <tabColor theme="0"/>
+    <tabColor rgb="FF1F497D"/>
   </sheetPr>
   <dimension ref="A1:AF1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3958,538 +3893,24 @@
       </c>
     </row>
     <row r="14" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5"/>
-    </row>
+    <row r="15" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" s="33">
-        <f>SUM(B2:B13)</f>
-        <v>182817947544523.97</v>
-      </c>
-      <c r="C18" s="33">
-        <f t="shared" ref="C18:AF18" si="0">SUM(C2:C13)</f>
-        <v>186405810921847.34</v>
-      </c>
-      <c r="D18" s="33">
-        <f t="shared" si="0"/>
-        <v>188362827309478.31</v>
-      </c>
-      <c r="E18" s="33">
-        <f t="shared" si="0"/>
-        <v>190319843697109.5</v>
-      </c>
-      <c r="F18" s="33">
-        <f t="shared" si="0"/>
-        <v>192276860084740.5</v>
-      </c>
-      <c r="G18" s="33">
-        <f t="shared" si="0"/>
-        <v>194233876472371.53</v>
-      </c>
-      <c r="H18" s="33">
-        <f t="shared" si="0"/>
-        <v>196190892860002.53</v>
-      </c>
-      <c r="I18" s="33">
-        <f t="shared" si="0"/>
-        <v>198147909247633.59</v>
-      </c>
-      <c r="J18" s="33">
-        <f t="shared" si="0"/>
-        <v>200104925635264.59</v>
-      </c>
-      <c r="K18" s="33">
-        <f t="shared" si="0"/>
-        <v>202061942022895.59</v>
-      </c>
-      <c r="L18" s="33">
-        <f t="shared" si="0"/>
-        <v>204018958410526.59</v>
-      </c>
-      <c r="M18" s="33">
-        <f t="shared" si="0"/>
-        <v>205975974798157.62</v>
-      </c>
-      <c r="N18" s="33">
-        <f t="shared" si="0"/>
-        <v>207932991185788.66</v>
-      </c>
-      <c r="O18" s="33">
-        <f t="shared" si="0"/>
-        <v>209890007573419.69</v>
-      </c>
-      <c r="P18" s="33">
-        <f t="shared" si="0"/>
-        <v>211847023961050.72</v>
-      </c>
-      <c r="Q18" s="33">
-        <f t="shared" si="0"/>
-        <v>213804040348681.72</v>
-      </c>
-      <c r="R18" s="33">
-        <f t="shared" si="0"/>
-        <v>215761056736312.72</v>
-      </c>
-      <c r="S18" s="33">
-        <f t="shared" si="0"/>
-        <v>217718073123943.78</v>
-      </c>
-      <c r="T18" s="33">
-        <f t="shared" si="0"/>
-        <v>219675089511574.78</v>
-      </c>
-      <c r="U18" s="33">
-        <f t="shared" si="0"/>
-        <v>221632105899205.81</v>
-      </c>
-      <c r="V18" s="33">
-        <f t="shared" si="0"/>
-        <v>223589122286836.81</v>
-      </c>
-      <c r="W18" s="33">
-        <f t="shared" si="0"/>
-        <v>225546138674467.81</v>
-      </c>
-      <c r="X18" s="33">
-        <f t="shared" si="0"/>
-        <v>227503155062098.81</v>
-      </c>
-      <c r="Y18" s="33">
-        <f t="shared" si="0"/>
-        <v>229460171449729.88</v>
-      </c>
-      <c r="Z18" s="33">
-        <f t="shared" si="0"/>
-        <v>231417187837360.88</v>
-      </c>
-      <c r="AA18" s="33">
-        <f t="shared" si="0"/>
-        <v>233374204224991.91</v>
-      </c>
-      <c r="AB18" s="33">
-        <f t="shared" si="0"/>
-        <v>235331220612622.91</v>
-      </c>
-      <c r="AC18" s="33">
-        <f t="shared" si="0"/>
-        <v>237288237000253.91</v>
-      </c>
-      <c r="AD18" s="33">
-        <f t="shared" si="0"/>
-        <v>239245253387884.94</v>
-      </c>
-      <c r="AE18" s="33">
-        <f t="shared" si="0"/>
-        <v>241202269775515.97</v>
-      </c>
-      <c r="AF18" s="33">
-        <f t="shared" si="0"/>
-        <v>243159286163146.97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19">
-        <f>B2/B18</f>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="C19">
-        <f t="shared" ref="C19:AF19" si="1">C2/C18</f>
-        <v>0.98376126824905452</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905452</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905452</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905452</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905452</v>
-      </c>
-      <c r="L19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905452</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905452</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="O19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905452</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="R19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="S19">
-        <f t="shared" si="1"/>
-        <v>0.9837612682490543</v>
-      </c>
-      <c r="T19">
-        <f t="shared" si="1"/>
-        <v>0.9837612682490543</v>
-      </c>
-      <c r="U19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="V19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="W19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="X19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905452</v>
-      </c>
-      <c r="Y19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="Z19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="AA19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="AB19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="AC19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905452</v>
-      </c>
-      <c r="AD19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="AE19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-      <c r="AF19">
-        <f t="shared" si="1"/>
-        <v>0.98376126824905441</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20">
-        <f>B11/B18</f>
-        <v>1.5228283313496759E-2</v>
-      </c>
-      <c r="C20">
-        <f t="shared" ref="C20:AF20" si="2">C11/C18</f>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496759E-2</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496759E-2</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496757E-2</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496757E-2</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="L20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496759E-2</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="O20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496759E-2</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496757E-2</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496757E-2</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496762E-2</v>
-      </c>
-      <c r="S20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496759E-2</v>
-      </c>
-      <c r="T20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496759E-2</v>
-      </c>
-      <c r="U20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496759E-2</v>
-      </c>
-      <c r="V20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="W20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="X20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496762E-2</v>
-      </c>
-      <c r="Y20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496759E-2</v>
-      </c>
-      <c r="Z20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="AA20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496759E-2</v>
-      </c>
-      <c r="AB20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="AC20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="AD20">
-        <f t="shared" si="2"/>
-        <v>1.5228283313496759E-2</v>
-      </c>
-      <c r="AE20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-      <c r="AF20">
-        <f t="shared" si="2"/>
-        <v>1.522828331349676E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21">
-        <f>B12/B18</f>
-        <v>1.0104484374488072E-3</v>
-      </c>
-      <c r="C21">
-        <f t="shared" ref="C21:AF21" si="3">C12/C18</f>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488072E-3</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488076E-3</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="L21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488076E-3</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="O21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488072E-3</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488072E-3</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488072E-3</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="U21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="V21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="W21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="X21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="Y21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="Z21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="AA21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="AB21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="AC21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="AD21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="AE21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-      <c r="AF21">
-        <f t="shared" si="3"/>
-        <v>1.0104484374488074E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5462,1974 +4883,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1142EC34-7E3E-C64E-8A49-B83C16A04B23}">
-  <dimension ref="A1:AF9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="29.83203125" customWidth="1"/>
-    <col min="25" max="25" width="12.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="29">
-        <v>2020</v>
-      </c>
-      <c r="C1" s="29">
-        <v>2021</v>
-      </c>
-      <c r="D1" s="29">
-        <v>2022</v>
-      </c>
-      <c r="E1" s="29">
-        <v>2023</v>
-      </c>
-      <c r="F1" s="29">
-        <v>2024</v>
-      </c>
-      <c r="G1" s="29">
-        <v>2025</v>
-      </c>
-      <c r="H1" s="29">
-        <v>2026</v>
-      </c>
-      <c r="I1" s="29">
-        <v>2027</v>
-      </c>
-      <c r="J1" s="29">
-        <v>2028</v>
-      </c>
-      <c r="K1" s="29">
-        <v>2029</v>
-      </c>
-      <c r="L1" s="29">
-        <v>2030</v>
-      </c>
-      <c r="M1" s="29">
-        <v>2031</v>
-      </c>
-      <c r="N1" s="29">
-        <v>2032</v>
-      </c>
-      <c r="O1" s="29">
-        <v>2033</v>
-      </c>
-      <c r="P1" s="29">
-        <v>2034</v>
-      </c>
-      <c r="Q1" s="29">
-        <v>2035</v>
-      </c>
-      <c r="R1" s="29">
-        <v>2036</v>
-      </c>
-      <c r="S1" s="29">
-        <v>2037</v>
-      </c>
-      <c r="T1" s="29">
-        <v>2038</v>
-      </c>
-      <c r="U1" s="29">
-        <v>2039</v>
-      </c>
-      <c r="V1" s="29">
-        <v>2040</v>
-      </c>
-      <c r="W1" s="29">
-        <v>2041</v>
-      </c>
-      <c r="X1" s="29">
-        <v>2042</v>
-      </c>
-      <c r="Y1" s="29">
-        <v>2043</v>
-      </c>
-      <c r="Z1" s="29">
-        <v>2044</v>
-      </c>
-      <c r="AA1" s="29">
-        <v>2045</v>
-      </c>
-      <c r="AB1" s="29">
-        <v>2046</v>
-      </c>
-      <c r="AC1" s="29">
-        <v>2047</v>
-      </c>
-      <c r="AD1" s="29">
-        <v>2048</v>
-      </c>
-      <c r="AE1" s="29">
-        <v>2049</v>
-      </c>
-      <c r="AF1" s="29">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="2">
-        <v>349</v>
-      </c>
-      <c r="C2">
-        <f>$B$2+(($L$2-$B$2)/($L$1-$B$1))*(C1-$B$1)</f>
-        <v>331.1</v>
-      </c>
-      <c r="D2">
-        <f t="shared" ref="D2:K2" si="0">$B$2+(($L$2-$B$2)/($L$1-$B$1))*(D1-$B$1)</f>
-        <v>313.2</v>
-      </c>
-      <c r="E2">
-        <f t="shared" si="0"/>
-        <v>295.3</v>
-      </c>
-      <c r="F2">
-        <f t="shared" si="0"/>
-        <v>277.39999999999998</v>
-      </c>
-      <c r="G2">
-        <f t="shared" si="0"/>
-        <v>259.5</v>
-      </c>
-      <c r="H2">
-        <f t="shared" si="0"/>
-        <v>241.60000000000002</v>
-      </c>
-      <c r="I2">
-        <f t="shared" si="0"/>
-        <v>223.70000000000002</v>
-      </c>
-      <c r="J2">
-        <f t="shared" si="0"/>
-        <v>205.8</v>
-      </c>
-      <c r="K2">
-        <f t="shared" si="0"/>
-        <v>187.9</v>
-      </c>
-      <c r="L2" s="2">
-        <v>170</v>
-      </c>
-      <c r="M2">
-        <f>$L$2+(($V$2-$L$2)/($V$1-$L$1))*(M1-$L$1)</f>
-        <v>155.9</v>
-      </c>
-      <c r="N2">
-        <f t="shared" ref="N2:U2" si="1">$L$2+(($V$2-$L$2)/($V$1-$L$1))*(N1-$L$1)</f>
-        <v>141.80000000000001</v>
-      </c>
-      <c r="O2">
-        <f t="shared" si="1"/>
-        <v>127.7</v>
-      </c>
-      <c r="P2">
-        <f t="shared" si="1"/>
-        <v>113.6</v>
-      </c>
-      <c r="Q2">
-        <f t="shared" si="1"/>
-        <v>99.5</v>
-      </c>
-      <c r="R2">
-        <f t="shared" si="1"/>
-        <v>85.4</v>
-      </c>
-      <c r="S2">
-        <f t="shared" si="1"/>
-        <v>71.3</v>
-      </c>
-      <c r="T2">
-        <f t="shared" si="1"/>
-        <v>57.2</v>
-      </c>
-      <c r="U2">
-        <f t="shared" si="1"/>
-        <v>43.100000000000009</v>
-      </c>
-      <c r="V2">
-        <v>29</v>
-      </c>
-      <c r="W2">
-        <f>$V$2+(($AF$2-$V$2)/($AF$1-$V$1))*(W1-$V$1)</f>
-        <v>15.2</v>
-      </c>
-      <c r="X2">
-        <f t="shared" ref="X2:AE2" si="2">$V$2+(($AF$2-$V$2)/($AF$1-$V$1))*(X1-$V$1)</f>
-        <v>1.3999999999999986</v>
-      </c>
-      <c r="Y2">
-        <f t="shared" si="2"/>
-        <v>-12.400000000000006</v>
-      </c>
-      <c r="Z2">
-        <f t="shared" si="2"/>
-        <v>-26.200000000000003</v>
-      </c>
-      <c r="AA2">
-        <f t="shared" si="2"/>
-        <v>-40</v>
-      </c>
-      <c r="AB2">
-        <f t="shared" si="2"/>
-        <v>-53.800000000000011</v>
-      </c>
-      <c r="AC2">
-        <f t="shared" si="2"/>
-        <v>-67.600000000000009</v>
-      </c>
-      <c r="AD2">
-        <f t="shared" si="2"/>
-        <v>-81.400000000000006</v>
-      </c>
-      <c r="AE2">
-        <f t="shared" si="2"/>
-        <v>-95.2</v>
-      </c>
-      <c r="AF2">
-        <v>-109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3">
-        <f>B2*$B$4</f>
-        <v>349000000000000</v>
-      </c>
-      <c r="C3">
-        <f t="shared" ref="C3:AF3" si="3">C2*$B$4</f>
-        <v>331100000000000</v>
-      </c>
-      <c r="D3">
-        <f t="shared" si="3"/>
-        <v>313200000000000</v>
-      </c>
-      <c r="E3">
-        <f t="shared" si="3"/>
-        <v>295300000000000</v>
-      </c>
-      <c r="F3">
-        <f t="shared" si="3"/>
-        <v>277399999999999.97</v>
-      </c>
-      <c r="G3">
-        <f t="shared" si="3"/>
-        <v>259500000000000</v>
-      </c>
-      <c r="H3">
-        <f t="shared" si="3"/>
-        <v>241600000000000.03</v>
-      </c>
-      <c r="I3">
-        <f t="shared" si="3"/>
-        <v>223700000000000.03</v>
-      </c>
-      <c r="J3">
-        <f t="shared" si="3"/>
-        <v>205800000000000</v>
-      </c>
-      <c r="K3">
-        <f t="shared" si="3"/>
-        <v>187900000000000</v>
-      </c>
-      <c r="L3">
-        <f t="shared" si="3"/>
-        <v>170000000000000</v>
-      </c>
-      <c r="M3">
-        <f t="shared" si="3"/>
-        <v>155900000000000</v>
-      </c>
-      <c r="N3">
-        <f t="shared" si="3"/>
-        <v>141800000000000</v>
-      </c>
-      <c r="O3">
-        <f t="shared" si="3"/>
-        <v>127700000000000</v>
-      </c>
-      <c r="P3">
-        <f t="shared" si="3"/>
-        <v>113600000000000</v>
-      </c>
-      <c r="Q3">
-        <f t="shared" si="3"/>
-        <v>99500000000000</v>
-      </c>
-      <c r="R3">
-        <f t="shared" si="3"/>
-        <v>85400000000000</v>
-      </c>
-      <c r="S3">
-        <f t="shared" si="3"/>
-        <v>71300000000000</v>
-      </c>
-      <c r="T3">
-        <f t="shared" si="3"/>
-        <v>57200000000000</v>
-      </c>
-      <c r="U3">
-        <f t="shared" si="3"/>
-        <v>43100000000000.008</v>
-      </c>
-      <c r="V3">
-        <f t="shared" si="3"/>
-        <v>29000000000000</v>
-      </c>
-      <c r="W3">
-        <f t="shared" si="3"/>
-        <v>15200000000000</v>
-      </c>
-      <c r="X3">
-        <f t="shared" si="3"/>
-        <v>1399999999999.9985</v>
-      </c>
-      <c r="Y3">
-        <f t="shared" si="3"/>
-        <v>-12400000000000.006</v>
-      </c>
-      <c r="Z3">
-        <f t="shared" si="3"/>
-        <v>-26200000000000.004</v>
-      </c>
-      <c r="AA3">
-        <f t="shared" si="3"/>
-        <v>-40000000000000</v>
-      </c>
-      <c r="AB3">
-        <f t="shared" si="3"/>
-        <v>-53800000000000.008</v>
-      </c>
-      <c r="AC3">
-        <f t="shared" si="3"/>
-        <v>-67600000000000.008</v>
-      </c>
-      <c r="AD3">
-        <f t="shared" si="3"/>
-        <v>-81400000000000</v>
-      </c>
-      <c r="AE3">
-        <f t="shared" si="3"/>
-        <v>-95200000000000</v>
-      </c>
-      <c r="AF3">
-        <f t="shared" si="3"/>
-        <v>-109000000000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4">
-        <v>1000000000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5">
-        <f>B3/2</f>
-        <v>174500000000000</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ref="C5:AF5" si="4">C3/2</f>
-        <v>165550000000000</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="4"/>
-        <v>156600000000000</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="4"/>
-        <v>147650000000000</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="4"/>
-        <v>138699999999999.98</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="4"/>
-        <v>129750000000000</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="4"/>
-        <v>120800000000000.02</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="4"/>
-        <v>111850000000000.02</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="4"/>
-        <v>102900000000000</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="4"/>
-        <v>93950000000000</v>
-      </c>
-      <c r="L5">
-        <f t="shared" si="4"/>
-        <v>85000000000000</v>
-      </c>
-      <c r="M5">
-        <f t="shared" si="4"/>
-        <v>77950000000000</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="4"/>
-        <v>70900000000000</v>
-      </c>
-      <c r="O5">
-        <f t="shared" si="4"/>
-        <v>63850000000000</v>
-      </c>
-      <c r="P5">
-        <f t="shared" si="4"/>
-        <v>56800000000000</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" si="4"/>
-        <v>49750000000000</v>
-      </c>
-      <c r="R5">
-        <f t="shared" si="4"/>
-        <v>42700000000000</v>
-      </c>
-      <c r="S5">
-        <f t="shared" si="4"/>
-        <v>35650000000000</v>
-      </c>
-      <c r="T5">
-        <f t="shared" si="4"/>
-        <v>28600000000000</v>
-      </c>
-      <c r="U5">
-        <f t="shared" si="4"/>
-        <v>21550000000000.004</v>
-      </c>
-      <c r="V5">
-        <f t="shared" si="4"/>
-        <v>14500000000000</v>
-      </c>
-      <c r="W5">
-        <f t="shared" si="4"/>
-        <v>7600000000000</v>
-      </c>
-      <c r="X5">
-        <f t="shared" si="4"/>
-        <v>699999999999.99927</v>
-      </c>
-      <c r="Y5">
-        <f t="shared" si="4"/>
-        <v>-6200000000000.0029</v>
-      </c>
-      <c r="Z5">
-        <f t="shared" si="4"/>
-        <v>-13100000000000.002</v>
-      </c>
-      <c r="AA5">
-        <f t="shared" si="4"/>
-        <v>-20000000000000</v>
-      </c>
-      <c r="AB5">
-        <f t="shared" si="4"/>
-        <v>-26900000000000.004</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" si="4"/>
-        <v>-33800000000000.004</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" si="4"/>
-        <v>-40700000000000</v>
-      </c>
-      <c r="AE5">
-        <f t="shared" si="4"/>
-        <v>-47600000000000</v>
-      </c>
-      <c r="AF5">
-        <f t="shared" si="4"/>
-        <v>-54500000000000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="33"/>
-      <c r="AC8" s="33"/>
-      <c r="AD8" s="33"/>
-      <c r="AE8" s="33"/>
-      <c r="AF8" s="33"/>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="Y9" s="33"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F60411-ADAC-D94F-9CA3-BD5BA5358F0E}">
-  <sheetPr>
-    <tabColor rgb="FF002060"/>
-  </sheetPr>
-  <dimension ref="A1:AF24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="34">
-        <v>2020</v>
-      </c>
-      <c r="C1" s="34">
-        <v>2021</v>
-      </c>
-      <c r="D1" s="34">
-        <v>2022</v>
-      </c>
-      <c r="E1" s="34">
-        <v>2023</v>
-      </c>
-      <c r="F1" s="34">
-        <v>2024</v>
-      </c>
-      <c r="G1" s="34">
-        <v>2025</v>
-      </c>
-      <c r="H1" s="34">
-        <v>2026</v>
-      </c>
-      <c r="I1" s="34">
-        <v>2027</v>
-      </c>
-      <c r="J1" s="34">
-        <v>2028</v>
-      </c>
-      <c r="K1" s="34">
-        <v>2029</v>
-      </c>
-      <c r="L1" s="34">
-        <v>2030</v>
-      </c>
-      <c r="M1" s="34">
-        <v>2031</v>
-      </c>
-      <c r="N1" s="34">
-        <v>2032</v>
-      </c>
-      <c r="O1" s="34">
-        <v>2033</v>
-      </c>
-      <c r="P1" s="34">
-        <v>2034</v>
-      </c>
-      <c r="Q1" s="34">
-        <v>2035</v>
-      </c>
-      <c r="R1" s="34">
-        <v>2036</v>
-      </c>
-      <c r="S1" s="34">
-        <v>2037</v>
-      </c>
-      <c r="T1" s="34">
-        <v>2038</v>
-      </c>
-      <c r="U1" s="34">
-        <v>2039</v>
-      </c>
-      <c r="V1" s="34">
-        <v>2040</v>
-      </c>
-      <c r="W1" s="34">
-        <v>2041</v>
-      </c>
-      <c r="X1" s="34">
-        <v>2042</v>
-      </c>
-      <c r="Y1" s="34">
-        <v>2043</v>
-      </c>
-      <c r="Z1" s="34">
-        <v>2044</v>
-      </c>
-      <c r="AA1" s="34">
-        <v>2045</v>
-      </c>
-      <c r="AB1" s="34">
-        <v>2046</v>
-      </c>
-      <c r="AC1" s="34">
-        <v>2047</v>
-      </c>
-      <c r="AD1" s="34">
-        <v>2048</v>
-      </c>
-      <c r="AE1" s="34">
-        <v>2049</v>
-      </c>
-      <c r="AF1" s="34">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A2" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="36">
-        <f>'BLAPE-not Adjusted'!B19*'MEF Projections'!B5</f>
-        <v>171666341309460</v>
-      </c>
-      <c r="C2" s="36">
-        <f>'BLAPE-not Adjusted'!C19*'MEF Projections'!C5</f>
-        <v>162861677958630.97</v>
-      </c>
-      <c r="D2" s="36">
-        <f>'BLAPE-not Adjusted'!D19*'MEF Projections'!D5</f>
-        <v>154057014607801.91</v>
-      </c>
-      <c r="E2" s="36">
-        <f>'BLAPE-not Adjusted'!E19*'MEF Projections'!E5</f>
-        <v>145252351256972.88</v>
-      </c>
-      <c r="F2" s="36">
-        <f>'BLAPE-not Adjusted'!F19*'MEF Projections'!F5</f>
-        <v>136447687906143.84</v>
-      </c>
-      <c r="G2" s="36">
-        <f>'BLAPE-not Adjusted'!G19*'MEF Projections'!G5</f>
-        <v>127643024555314.83</v>
-      </c>
-      <c r="H2" s="36">
-        <f>'BLAPE-not Adjusted'!H19*'MEF Projections'!H5</f>
-        <v>118838361204485.8</v>
-      </c>
-      <c r="I2" s="36">
-        <f>'BLAPE-not Adjusted'!I19*'MEF Projections'!I5</f>
-        <v>110033697853656.75</v>
-      </c>
-      <c r="J2" s="36">
-        <f>'BLAPE-not Adjusted'!J19*'MEF Projections'!J5</f>
-        <v>101229034502827.7</v>
-      </c>
-      <c r="K2" s="36">
-        <f>'BLAPE-not Adjusted'!K19*'MEF Projections'!K5</f>
-        <v>92424371151998.672</v>
-      </c>
-      <c r="L2" s="36">
-        <f>'BLAPE-not Adjusted'!L19*'MEF Projections'!L5</f>
-        <v>83619707801169.641</v>
-      </c>
-      <c r="M2" s="36">
-        <f>'BLAPE-not Adjusted'!M19*'MEF Projections'!M5</f>
-        <v>76684190860013.797</v>
-      </c>
-      <c r="N2" s="36">
-        <f>'BLAPE-not Adjusted'!N19*'MEF Projections'!N5</f>
-        <v>69748673918857.961</v>
-      </c>
-      <c r="O2" s="36">
-        <f>'BLAPE-not Adjusted'!O19*'MEF Projections'!O5</f>
-        <v>62813156977702.133</v>
-      </c>
-      <c r="P2" s="36">
-        <f>'BLAPE-not Adjusted'!P19*'MEF Projections'!P5</f>
-        <v>55877640036546.289</v>
-      </c>
-      <c r="Q2" s="36">
-        <f>'BLAPE-not Adjusted'!Q19*'MEF Projections'!Q5</f>
-        <v>48942123095390.453</v>
-      </c>
-      <c r="R2" s="36">
-        <f>'BLAPE-not Adjusted'!R19*'MEF Projections'!R5</f>
-        <v>42006606154234.625</v>
-      </c>
-      <c r="S2" s="36">
-        <f>'BLAPE-not Adjusted'!S19*'MEF Projections'!S5</f>
-        <v>35071089213078.785</v>
-      </c>
-      <c r="T2" s="36">
-        <f>'BLAPE-not Adjusted'!T19*'MEF Projections'!T5</f>
-        <v>28135572271922.953</v>
-      </c>
-      <c r="U2" s="36">
-        <f>'BLAPE-not Adjusted'!U19*'MEF Projections'!U5</f>
-        <v>21200055330767.125</v>
-      </c>
-      <c r="V2" s="36">
-        <f>'BLAPE-not Adjusted'!V19*'MEF Projections'!V5</f>
-        <v>14264538389611.289</v>
-      </c>
-      <c r="W2" s="36">
-        <f>'BLAPE-not Adjusted'!W19*'MEF Projections'!W5</f>
-        <v>7476585638692.8135</v>
-      </c>
-      <c r="X2" s="36">
-        <f>'BLAPE-not Adjusted'!X19*'MEF Projections'!X5</f>
-        <v>688632887774.3374</v>
-      </c>
-      <c r="Y2" s="36">
-        <f>'BLAPE-not Adjusted'!Y19*'MEF Projections'!Y5</f>
-        <v>-6099319863144.1406</v>
-      </c>
-      <c r="Z2" s="36">
-        <f>'BLAPE-not Adjusted'!Z19*'MEF Projections'!Z5</f>
-        <v>-12887272614062.615</v>
-      </c>
-      <c r="AA2" s="36">
-        <f>'BLAPE-not Adjusted'!AA19*'MEF Projections'!AA5</f>
-        <v>-19675225364981.09</v>
-      </c>
-      <c r="AB2" s="36">
-        <f>'BLAPE-not Adjusted'!AB19*'MEF Projections'!AB5</f>
-        <v>-26463178115899.566</v>
-      </c>
-      <c r="AC2" s="36">
-        <f>'BLAPE-not Adjusted'!AC19*'MEF Projections'!AC5</f>
-        <v>-33251130866818.047</v>
-      </c>
-      <c r="AD2" s="36">
-        <f>'BLAPE-not Adjusted'!AD19*'MEF Projections'!AD5</f>
-        <v>-40039083617736.516</v>
-      </c>
-      <c r="AE2" s="36">
-        <f>'BLAPE-not Adjusted'!AE19*'MEF Projections'!AE5</f>
-        <v>-46827036368654.992</v>
-      </c>
-      <c r="AF2" s="36">
-        <f>'BLAPE-not Adjusted'!AF19*'MEF Projections'!AF5</f>
-        <v>-53614989119573.469</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="36">
-        <v>0</v>
-      </c>
-      <c r="C3" s="36">
-        <v>0</v>
-      </c>
-      <c r="D3" s="36">
-        <v>0</v>
-      </c>
-      <c r="E3" s="36">
-        <v>0</v>
-      </c>
-      <c r="F3" s="36">
-        <v>0</v>
-      </c>
-      <c r="G3" s="36">
-        <v>0</v>
-      </c>
-      <c r="H3" s="36">
-        <v>0</v>
-      </c>
-      <c r="I3" s="36">
-        <v>0</v>
-      </c>
-      <c r="J3" s="36">
-        <v>0</v>
-      </c>
-      <c r="K3" s="36">
-        <v>0</v>
-      </c>
-      <c r="L3" s="36">
-        <v>0</v>
-      </c>
-      <c r="M3" s="36">
-        <v>0</v>
-      </c>
-      <c r="N3" s="36">
-        <v>0</v>
-      </c>
-      <c r="O3" s="36">
-        <v>0</v>
-      </c>
-      <c r="P3" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="36">
-        <v>0</v>
-      </c>
-      <c r="R3" s="36">
-        <v>0</v>
-      </c>
-      <c r="S3" s="36">
-        <v>0</v>
-      </c>
-      <c r="T3" s="36">
-        <v>0</v>
-      </c>
-      <c r="U3" s="36">
-        <v>0</v>
-      </c>
-      <c r="V3" s="36">
-        <v>0</v>
-      </c>
-      <c r="W3" s="36">
-        <v>0</v>
-      </c>
-      <c r="X3" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="36">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="36">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="36">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A4" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="36">
-        <v>0</v>
-      </c>
-      <c r="C4" s="36">
-        <v>0</v>
-      </c>
-      <c r="D4" s="36">
-        <v>0</v>
-      </c>
-      <c r="E4" s="36">
-        <v>0</v>
-      </c>
-      <c r="F4" s="36">
-        <v>0</v>
-      </c>
-      <c r="G4" s="36">
-        <v>0</v>
-      </c>
-      <c r="H4" s="36">
-        <v>0</v>
-      </c>
-      <c r="I4" s="36">
-        <v>0</v>
-      </c>
-      <c r="J4" s="36">
-        <v>0</v>
-      </c>
-      <c r="K4" s="36">
-        <v>0</v>
-      </c>
-      <c r="L4" s="36">
-        <v>0</v>
-      </c>
-      <c r="M4" s="36">
-        <v>0</v>
-      </c>
-      <c r="N4" s="36">
-        <v>0</v>
-      </c>
-      <c r="O4" s="36">
-        <v>0</v>
-      </c>
-      <c r="P4" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="36">
-        <v>0</v>
-      </c>
-      <c r="R4" s="36">
-        <v>0</v>
-      </c>
-      <c r="S4" s="36">
-        <v>0</v>
-      </c>
-      <c r="T4" s="36">
-        <v>0</v>
-      </c>
-      <c r="U4" s="36">
-        <v>0</v>
-      </c>
-      <c r="V4" s="36">
-        <v>0</v>
-      </c>
-      <c r="W4" s="36">
-        <v>0</v>
-      </c>
-      <c r="X4" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A5" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="36">
-        <v>0</v>
-      </c>
-      <c r="C5" s="36">
-        <v>0</v>
-      </c>
-      <c r="D5" s="36">
-        <v>0</v>
-      </c>
-      <c r="E5" s="36">
-        <v>0</v>
-      </c>
-      <c r="F5" s="36">
-        <v>0</v>
-      </c>
-      <c r="G5" s="36">
-        <v>0</v>
-      </c>
-      <c r="H5" s="36">
-        <v>0</v>
-      </c>
-      <c r="I5" s="36">
-        <v>0</v>
-      </c>
-      <c r="J5" s="36">
-        <v>0</v>
-      </c>
-      <c r="K5" s="36">
-        <v>0</v>
-      </c>
-      <c r="L5" s="36">
-        <v>0</v>
-      </c>
-      <c r="M5" s="36">
-        <v>0</v>
-      </c>
-      <c r="N5" s="36">
-        <v>0</v>
-      </c>
-      <c r="O5" s="36">
-        <v>0</v>
-      </c>
-      <c r="P5" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="36">
-        <v>0</v>
-      </c>
-      <c r="R5" s="36">
-        <v>0</v>
-      </c>
-      <c r="S5" s="36">
-        <v>0</v>
-      </c>
-      <c r="T5" s="36">
-        <v>0</v>
-      </c>
-      <c r="U5" s="36">
-        <v>0</v>
-      </c>
-      <c r="V5" s="36">
-        <v>0</v>
-      </c>
-      <c r="W5" s="36">
-        <v>0</v>
-      </c>
-      <c r="X5" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="36">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="36">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="36">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A6" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="36">
-        <v>0</v>
-      </c>
-      <c r="C6" s="36">
-        <v>0</v>
-      </c>
-      <c r="D6" s="36">
-        <v>0</v>
-      </c>
-      <c r="E6" s="36">
-        <v>0</v>
-      </c>
-      <c r="F6" s="36">
-        <v>0</v>
-      </c>
-      <c r="G6" s="36">
-        <v>0</v>
-      </c>
-      <c r="H6" s="36">
-        <v>0</v>
-      </c>
-      <c r="I6" s="36">
-        <v>0</v>
-      </c>
-      <c r="J6" s="36">
-        <v>0</v>
-      </c>
-      <c r="K6" s="36">
-        <v>0</v>
-      </c>
-      <c r="L6" s="36">
-        <v>0</v>
-      </c>
-      <c r="M6" s="36">
-        <v>0</v>
-      </c>
-      <c r="N6" s="36">
-        <v>0</v>
-      </c>
-      <c r="O6" s="36">
-        <v>0</v>
-      </c>
-      <c r="P6" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="36">
-        <v>0</v>
-      </c>
-      <c r="R6" s="36">
-        <v>0</v>
-      </c>
-      <c r="S6" s="36">
-        <v>0</v>
-      </c>
-      <c r="T6" s="36">
-        <v>0</v>
-      </c>
-      <c r="U6" s="36">
-        <v>0</v>
-      </c>
-      <c r="V6" s="36">
-        <v>0</v>
-      </c>
-      <c r="W6" s="36">
-        <v>0</v>
-      </c>
-      <c r="X6" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="36">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="36">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="36">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A7" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="36">
-        <v>0</v>
-      </c>
-      <c r="C7" s="36">
-        <v>0</v>
-      </c>
-      <c r="D7" s="36">
-        <v>0</v>
-      </c>
-      <c r="E7" s="36">
-        <v>0</v>
-      </c>
-      <c r="F7" s="36">
-        <v>0</v>
-      </c>
-      <c r="G7" s="36">
-        <v>0</v>
-      </c>
-      <c r="H7" s="36">
-        <v>0</v>
-      </c>
-      <c r="I7" s="36">
-        <v>0</v>
-      </c>
-      <c r="J7" s="36">
-        <v>0</v>
-      </c>
-      <c r="K7" s="36">
-        <v>0</v>
-      </c>
-      <c r="L7" s="36">
-        <v>0</v>
-      </c>
-      <c r="M7" s="36">
-        <v>0</v>
-      </c>
-      <c r="N7" s="36">
-        <v>0</v>
-      </c>
-      <c r="O7" s="36">
-        <v>0</v>
-      </c>
-      <c r="P7" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="36">
-        <v>0</v>
-      </c>
-      <c r="R7" s="36">
-        <v>0</v>
-      </c>
-      <c r="S7" s="36">
-        <v>0</v>
-      </c>
-      <c r="T7" s="36">
-        <v>0</v>
-      </c>
-      <c r="U7" s="36">
-        <v>0</v>
-      </c>
-      <c r="V7" s="36">
-        <v>0</v>
-      </c>
-      <c r="W7" s="36">
-        <v>0</v>
-      </c>
-      <c r="X7" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="36">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="36">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="36">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A8" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="36">
-        <v>0</v>
-      </c>
-      <c r="C8" s="36">
-        <v>0</v>
-      </c>
-      <c r="D8" s="36">
-        <v>0</v>
-      </c>
-      <c r="E8" s="36">
-        <v>0</v>
-      </c>
-      <c r="F8" s="36">
-        <v>0</v>
-      </c>
-      <c r="G8" s="36">
-        <v>0</v>
-      </c>
-      <c r="H8" s="36">
-        <v>0</v>
-      </c>
-      <c r="I8" s="36">
-        <v>0</v>
-      </c>
-      <c r="J8" s="36">
-        <v>0</v>
-      </c>
-      <c r="K8" s="36">
-        <v>0</v>
-      </c>
-      <c r="L8" s="36">
-        <v>0</v>
-      </c>
-      <c r="M8" s="36">
-        <v>0</v>
-      </c>
-      <c r="N8" s="36">
-        <v>0</v>
-      </c>
-      <c r="O8" s="36">
-        <v>0</v>
-      </c>
-      <c r="P8" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="36">
-        <v>0</v>
-      </c>
-      <c r="R8" s="36">
-        <v>0</v>
-      </c>
-      <c r="S8" s="36">
-        <v>0</v>
-      </c>
-      <c r="T8" s="36">
-        <v>0</v>
-      </c>
-      <c r="U8" s="36">
-        <v>0</v>
-      </c>
-      <c r="V8" s="36">
-        <v>0</v>
-      </c>
-      <c r="W8" s="36">
-        <v>0</v>
-      </c>
-      <c r="X8" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="36">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="36">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="36">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A9" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="36">
-        <v>0</v>
-      </c>
-      <c r="C9" s="36">
-        <v>0</v>
-      </c>
-      <c r="D9" s="36">
-        <v>0</v>
-      </c>
-      <c r="E9" s="36">
-        <v>0</v>
-      </c>
-      <c r="F9" s="36">
-        <v>0</v>
-      </c>
-      <c r="G9" s="36">
-        <v>0</v>
-      </c>
-      <c r="H9" s="36">
-        <v>0</v>
-      </c>
-      <c r="I9" s="36">
-        <v>0</v>
-      </c>
-      <c r="J9" s="36">
-        <v>0</v>
-      </c>
-      <c r="K9" s="36">
-        <v>0</v>
-      </c>
-      <c r="L9" s="36">
-        <v>0</v>
-      </c>
-      <c r="M9" s="36">
-        <v>0</v>
-      </c>
-      <c r="N9" s="36">
-        <v>0</v>
-      </c>
-      <c r="O9" s="36">
-        <v>0</v>
-      </c>
-      <c r="P9" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="36">
-        <v>0</v>
-      </c>
-      <c r="R9" s="36">
-        <v>0</v>
-      </c>
-      <c r="S9" s="36">
-        <v>0</v>
-      </c>
-      <c r="T9" s="36">
-        <v>0</v>
-      </c>
-      <c r="U9" s="36">
-        <v>0</v>
-      </c>
-      <c r="V9" s="36">
-        <v>0</v>
-      </c>
-      <c r="W9" s="36">
-        <v>0</v>
-      </c>
-      <c r="X9" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="36">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="36">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="36">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A10" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="36">
-        <v>0</v>
-      </c>
-      <c r="C10" s="36">
-        <v>0</v>
-      </c>
-      <c r="D10" s="36">
-        <v>0</v>
-      </c>
-      <c r="E10" s="36">
-        <v>0</v>
-      </c>
-      <c r="F10" s="36">
-        <v>0</v>
-      </c>
-      <c r="G10" s="36">
-        <v>0</v>
-      </c>
-      <c r="H10" s="36">
-        <v>0</v>
-      </c>
-      <c r="I10" s="36">
-        <v>0</v>
-      </c>
-      <c r="J10" s="36">
-        <v>0</v>
-      </c>
-      <c r="K10" s="36">
-        <v>0</v>
-      </c>
-      <c r="L10" s="36">
-        <v>0</v>
-      </c>
-      <c r="M10" s="36">
-        <v>0</v>
-      </c>
-      <c r="N10" s="36">
-        <v>0</v>
-      </c>
-      <c r="O10" s="36">
-        <v>0</v>
-      </c>
-      <c r="P10" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="36">
-        <v>0</v>
-      </c>
-      <c r="R10" s="36">
-        <v>0</v>
-      </c>
-      <c r="S10" s="36">
-        <v>0</v>
-      </c>
-      <c r="T10" s="36">
-        <v>0</v>
-      </c>
-      <c r="U10" s="36">
-        <v>0</v>
-      </c>
-      <c r="V10" s="36">
-        <v>0</v>
-      </c>
-      <c r="W10" s="36">
-        <v>0</v>
-      </c>
-      <c r="X10" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="36">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="36">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="36">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A11" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="36">
-        <f>'BLAPE-not Adjusted'!B20*'MEF Projections'!B5</f>
-        <v>2657335438205.1846</v>
-      </c>
-      <c r="C11" s="36">
-        <f>'BLAPE-not Adjusted'!C20*'MEF Projections'!C5</f>
-        <v>2521042302549.3887</v>
-      </c>
-      <c r="D11" s="36">
-        <f>'BLAPE-not Adjusted'!D20*'MEF Projections'!D5</f>
-        <v>2384749166893.5923</v>
-      </c>
-      <c r="E11" s="36">
-        <f>'BLAPE-not Adjusted'!E20*'MEF Projections'!E5</f>
-        <v>2248456031237.7964</v>
-      </c>
-      <c r="F11" s="36">
-        <f>'BLAPE-not Adjusted'!F20*'MEF Projections'!F5</f>
-        <v>2112162895582.0005</v>
-      </c>
-      <c r="G11" s="36">
-        <f>'BLAPE-not Adjusted'!G20*'MEF Projections'!G5</f>
-        <v>1975869759926.2046</v>
-      </c>
-      <c r="H11" s="36">
-        <f>'BLAPE-not Adjusted'!H20*'MEF Projections'!H5</f>
-        <v>1839576624270.4089</v>
-      </c>
-      <c r="I11" s="36">
-        <f>'BLAPE-not Adjusted'!I20*'MEF Projections'!I5</f>
-        <v>1703283488614.6125</v>
-      </c>
-      <c r="J11" s="36">
-        <f>'BLAPE-not Adjusted'!J20*'MEF Projections'!J5</f>
-        <v>1566990352958.8162</v>
-      </c>
-      <c r="K11" s="36">
-        <f>'BLAPE-not Adjusted'!K20*'MEF Projections'!K5</f>
-        <v>1430697217303.0205</v>
-      </c>
-      <c r="L11" s="36">
-        <f>'BLAPE-not Adjusted'!L20*'MEF Projections'!L5</f>
-        <v>1294404081647.2246</v>
-      </c>
-      <c r="M11" s="36">
-        <f>'BLAPE-not Adjusted'!M20*'MEF Projections'!M5</f>
-        <v>1187044684287.0723</v>
-      </c>
-      <c r="N11" s="36">
-        <f>'BLAPE-not Adjusted'!N20*'MEF Projections'!N5</f>
-        <v>1079685286926.9203</v>
-      </c>
-      <c r="O11" s="36">
-        <f>'BLAPE-not Adjusted'!O20*'MEF Projections'!O5</f>
-        <v>972325889566.76807</v>
-      </c>
-      <c r="P11" s="36">
-        <f>'BLAPE-not Adjusted'!P20*'MEF Projections'!P5</f>
-        <v>864966492206.61584</v>
-      </c>
-      <c r="Q11" s="36">
-        <f>'BLAPE-not Adjusted'!Q20*'MEF Projections'!Q5</f>
-        <v>757607094846.46362</v>
-      </c>
-      <c r="R11" s="36">
-        <f>'BLAPE-not Adjusted'!R20*'MEF Projections'!R5</f>
-        <v>650247697486.31177</v>
-      </c>
-      <c r="S11" s="36">
-        <f>'BLAPE-not Adjusted'!S20*'MEF Projections'!S5</f>
-        <v>542888300126.15942</v>
-      </c>
-      <c r="T11" s="36">
-        <f>'BLAPE-not Adjusted'!T20*'MEF Projections'!T5</f>
-        <v>435528902766.00726</v>
-      </c>
-      <c r="U11" s="36">
-        <f>'BLAPE-not Adjusted'!U20*'MEF Projections'!U5</f>
-        <v>328169505405.85522</v>
-      </c>
-      <c r="V11" s="36">
-        <f>'BLAPE-not Adjusted'!V20*'MEF Projections'!V5</f>
-        <v>220810108045.70303</v>
-      </c>
-      <c r="W11" s="36">
-        <f>'BLAPE-not Adjusted'!W20*'MEF Projections'!W5</f>
-        <v>115734953182.57538</v>
-      </c>
-      <c r="X11" s="36">
-        <f>'BLAPE-not Adjusted'!X20*'MEF Projections'!X5</f>
-        <v>10659798319.447721</v>
-      </c>
-      <c r="Y11" s="36">
-        <f>'BLAPE-not Adjusted'!Y20*'MEF Projections'!Y5</f>
-        <v>-94415356543.679947</v>
-      </c>
-      <c r="Z11" s="36">
-        <f>'BLAPE-not Adjusted'!Z20*'MEF Projections'!Z5</f>
-        <v>-199490511406.80759</v>
-      </c>
-      <c r="AA11" s="36">
-        <f>'BLAPE-not Adjusted'!AA20*'MEF Projections'!AA5</f>
-        <v>-304565666269.93518</v>
-      </c>
-      <c r="AB11" s="36">
-        <f>'BLAPE-not Adjusted'!AB20*'MEF Projections'!AB5</f>
-        <v>-409640821133.06293</v>
-      </c>
-      <c r="AC11" s="36">
-        <f>'BLAPE-not Adjusted'!AC20*'MEF Projections'!AC5</f>
-        <v>-514715975996.19055</v>
-      </c>
-      <c r="AD11" s="36">
-        <f>'BLAPE-not Adjusted'!AD20*'MEF Projections'!AD5</f>
-        <v>-619791130859.31812</v>
-      </c>
-      <c r="AE11" s="36">
-        <f>'BLAPE-not Adjusted'!AE20*'MEF Projections'!AE5</f>
-        <v>-724866285722.4458</v>
-      </c>
-      <c r="AF11" s="36">
-        <f>'BLAPE-not Adjusted'!AF20*'MEF Projections'!AF5</f>
-        <v>-829941440585.57349</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A12" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="36">
-        <f>'BLAPE-not Adjusted'!B21*'MEF Projections'!B5</f>
-        <v>176323252334.81686</v>
-      </c>
-      <c r="C12" s="36">
-        <f>'BLAPE-not Adjusted'!C21*'MEF Projections'!C5</f>
-        <v>167279738819.65005</v>
-      </c>
-      <c r="D12" s="36">
-        <f>'BLAPE-not Adjusted'!D21*'MEF Projections'!D5</f>
-        <v>158236225304.48322</v>
-      </c>
-      <c r="E12" s="36">
-        <f>'BLAPE-not Adjusted'!E21*'MEF Projections'!E5</f>
-        <v>149192711789.31641</v>
-      </c>
-      <c r="F12" s="36">
-        <f>'BLAPE-not Adjusted'!F21*'MEF Projections'!F5</f>
-        <v>140149198274.1496</v>
-      </c>
-      <c r="G12" s="36">
-        <f>'BLAPE-not Adjusted'!G21*'MEF Projections'!G5</f>
-        <v>131105684758.98276</v>
-      </c>
-      <c r="H12" s="36">
-        <f>'BLAPE-not Adjusted'!H21*'MEF Projections'!H5</f>
-        <v>122062171243.81595</v>
-      </c>
-      <c r="I12" s="36">
-        <f>'BLAPE-not Adjusted'!I21*'MEF Projections'!I5</f>
-        <v>113018657728.64912</v>
-      </c>
-      <c r="J12" s="36">
-        <f>'BLAPE-not Adjusted'!J21*'MEF Projections'!J5</f>
-        <v>103975144213.48228</v>
-      </c>
-      <c r="K12" s="36">
-        <f>'BLAPE-not Adjusted'!K21*'MEF Projections'!K5</f>
-        <v>94931630698.31546</v>
-      </c>
-      <c r="L12" s="36">
-        <f>'BLAPE-not Adjusted'!L21*'MEF Projections'!L5</f>
-        <v>85888117183.148651</v>
-      </c>
-      <c r="M12" s="36">
-        <f>'BLAPE-not Adjusted'!M21*'MEF Projections'!M5</f>
-        <v>78764455699.134537</v>
-      </c>
-      <c r="N12" s="36">
-        <f>'BLAPE-not Adjusted'!N21*'MEF Projections'!N5</f>
-        <v>71640794215.120438</v>
-      </c>
-      <c r="O12" s="36">
-        <f>'BLAPE-not Adjusted'!O21*'MEF Projections'!O5</f>
-        <v>64517132731.106339</v>
-      </c>
-      <c r="P12" s="36">
-        <f>'BLAPE-not Adjusted'!P21*'MEF Projections'!P5</f>
-        <v>57393471247.092247</v>
-      </c>
-      <c r="Q12" s="36">
-        <f>'BLAPE-not Adjusted'!Q21*'MEF Projections'!Q5</f>
-        <v>50269809763.078163</v>
-      </c>
-      <c r="R12" s="36">
-        <f>'BLAPE-not Adjusted'!R21*'MEF Projections'!R5</f>
-        <v>43146148279.064072</v>
-      </c>
-      <c r="S12" s="36">
-        <f>'BLAPE-not Adjusted'!S21*'MEF Projections'!S5</f>
-        <v>36022486795.049973</v>
-      </c>
-      <c r="T12" s="36">
-        <f>'BLAPE-not Adjusted'!T21*'MEF Projections'!T5</f>
-        <v>28898825311.035892</v>
-      </c>
-      <c r="U12" s="36">
-        <f>'BLAPE-not Adjusted'!U21*'MEF Projections'!U5</f>
-        <v>21775163827.021801</v>
-      </c>
-      <c r="V12" s="36">
-        <f>'BLAPE-not Adjusted'!V21*'MEF Projections'!V5</f>
-        <v>14651502343.007708</v>
-      </c>
-      <c r="W12" s="36">
-        <f>'BLAPE-not Adjusted'!W21*'MEF Projections'!W5</f>
-        <v>7679408124.6109362</v>
-      </c>
-      <c r="X12" s="36">
-        <f>'BLAPE-not Adjusted'!X21*'MEF Projections'!X5</f>
-        <v>707313906.21416438</v>
-      </c>
-      <c r="Y12" s="36">
-        <f>'BLAPE-not Adjusted'!Y21*'MEF Projections'!Y5</f>
-        <v>-6264780312.1826086</v>
-      </c>
-      <c r="Z12" s="36">
-        <f>'BLAPE-not Adjusted'!Z21*'MEF Projections'!Z5</f>
-        <v>-13236874530.579378</v>
-      </c>
-      <c r="AA12" s="36">
-        <f>'BLAPE-not Adjusted'!AA21*'MEF Projections'!AA5</f>
-        <v>-20208968748.976147</v>
-      </c>
-      <c r="AB12" s="36">
-        <f>'BLAPE-not Adjusted'!AB21*'MEF Projections'!AB5</f>
-        <v>-27181062967.372921</v>
-      </c>
-      <c r="AC12" s="36">
-        <f>'BLAPE-not Adjusted'!AC21*'MEF Projections'!AC5</f>
-        <v>-34153157185.769691</v>
-      </c>
-      <c r="AD12" s="36">
-        <f>'BLAPE-not Adjusted'!AD21*'MEF Projections'!AD5</f>
-        <v>-41125251404.166458</v>
-      </c>
-      <c r="AE12" s="36">
-        <f>'BLAPE-not Adjusted'!AE21*'MEF Projections'!AE5</f>
-        <v>-48097345622.563232</v>
-      </c>
-      <c r="AF12" s="36">
-        <f>'BLAPE-not Adjusted'!AF21*'MEF Projections'!AF5</f>
-        <v>-55069439840.959999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A13" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="36">
-        <v>0</v>
-      </c>
-      <c r="C13" s="36">
-        <v>0</v>
-      </c>
-      <c r="D13" s="36">
-        <v>0</v>
-      </c>
-      <c r="E13" s="36">
-        <v>0</v>
-      </c>
-      <c r="F13" s="36">
-        <v>0</v>
-      </c>
-      <c r="G13" s="36">
-        <v>0</v>
-      </c>
-      <c r="H13" s="36">
-        <v>0</v>
-      </c>
-      <c r="I13" s="36">
-        <v>0</v>
-      </c>
-      <c r="J13" s="36">
-        <v>0</v>
-      </c>
-      <c r="K13" s="36">
-        <v>0</v>
-      </c>
-      <c r="L13" s="36">
-        <v>0</v>
-      </c>
-      <c r="M13" s="36">
-        <v>0</v>
-      </c>
-      <c r="N13" s="36">
-        <v>0</v>
-      </c>
-      <c r="O13" s="36">
-        <v>0</v>
-      </c>
-      <c r="P13" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="36">
-        <v>0</v>
-      </c>
-      <c r="R13" s="36">
-        <v>0</v>
-      </c>
-      <c r="S13" s="36">
-        <v>0</v>
-      </c>
-      <c r="T13" s="36">
-        <v>0</v>
-      </c>
-      <c r="U13" s="36">
-        <v>0</v>
-      </c>
-      <c r="V13" s="36">
-        <v>0</v>
-      </c>
-      <c r="W13" s="36">
-        <v>0</v>
-      </c>
-      <c r="X13" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="36">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="36">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="36">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="36">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="36">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A16" s="5"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="33"/>
-      <c r="V16" s="33"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="33"/>
-      <c r="Y16" s="33"/>
-      <c r="Z16" s="33"/>
-      <c r="AA16" s="33"/>
-      <c r="AB16" s="33"/>
-      <c r="AC16" s="33"/>
-      <c r="AD16" s="33"/>
-      <c r="AE16" s="33"/>
-      <c r="AF16" s="33"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="29"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="29"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
+++ b/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
@@ -1,26 +1,81 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/land/BLAPE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96814494-ED35-684F-A129-67412A41895D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2ADC5A-3F89-4A44-BCFC-E9F0833CC9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="UNFCCC" sheetId="5" r:id="rId2"/>
     <sheet name="Share of Pollutants" sheetId="4" r:id="rId3"/>
-    <sheet name="Global Watch Data" sheetId="8" r:id="rId4"/>
-    <sheet name="Stata-1" sheetId="9" r:id="rId5"/>
-    <sheet name="Stata-2" sheetId="10" r:id="rId6"/>
-    <sheet name="BLAPE" sheetId="7" r:id="rId7"/>
+    <sheet name="GWF-Smoothing " sheetId="11" r:id="rId4"/>
+    <sheet name="Global Watch Data" sheetId="8" r:id="rId5"/>
+    <sheet name="Stata-1" sheetId="9" r:id="rId6"/>
+    <sheet name="Stata-2" sheetId="10" r:id="rId7"/>
+    <sheet name="BLAPE" sheetId="7" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">BLAPE!$A$1</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">BLAPE!$A$10</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">BLAPE!$A$7</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">BLAPE!$A$8</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">BLAPE!$A$9</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">BLAPE!$B$10:$AZ$10</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">BLAPE!$B$11:$AZ$11</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">BLAPE!$B$12:$AZ$12</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">BLAPE!$B$13:$AZ$13</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">BLAPE!$B$1:$AZ$1</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">BLAPE!$B$2:$AZ$2</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">BLAPE!$B$3:$AZ$3</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">BLAPE!$A$11</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">BLAPE!$B$4:$AZ$4</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">BLAPE!$B$5:$AZ$5</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">BLAPE!$B$6:$AZ$6</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">BLAPE!$B$7:$AZ$7</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">BLAPE!$B$8:$AZ$8</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">BLAPE!$B$9:$AZ$9</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">BLAPE!$A$1</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">BLAPE!$A$10</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">BLAPE!$A$11</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">BLAPE!$A$12</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">BLAPE!$A$12</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">BLAPE!$A$13</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">BLAPE!$A$2</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">BLAPE!$A$3</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">BLAPE!$A$4</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">BLAPE!$A$5</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">BLAPE!$A$6</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">BLAPE!$A$7</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">BLAPE!$A$8</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">BLAPE!$A$9</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">BLAPE!$B$10:$AZ$10</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">BLAPE!$A$13</definedName>
+    <definedName name="_xlchart.v1.40" hidden="1">BLAPE!$B$11:$AZ$11</definedName>
+    <definedName name="_xlchart.v1.41" hidden="1">BLAPE!$B$12:$AZ$12</definedName>
+    <definedName name="_xlchart.v1.42" hidden="1">BLAPE!$B$13:$AZ$13</definedName>
+    <definedName name="_xlchart.v1.43" hidden="1">BLAPE!$B$1:$AZ$1</definedName>
+    <definedName name="_xlchart.v1.44" hidden="1">BLAPE!$B$2:$AZ$2</definedName>
+    <definedName name="_xlchart.v1.45" hidden="1">BLAPE!$B$3:$AZ$3</definedName>
+    <definedName name="_xlchart.v1.46" hidden="1">BLAPE!$B$4:$AZ$4</definedName>
+    <definedName name="_xlchart.v1.47" hidden="1">BLAPE!$B$5:$AZ$5</definedName>
+    <definedName name="_xlchart.v1.48" hidden="1">BLAPE!$B$6:$AZ$6</definedName>
+    <definedName name="_xlchart.v1.49" hidden="1">BLAPE!$B$7:$AZ$7</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">BLAPE!$A$2</definedName>
+    <definedName name="_xlchart.v1.50" hidden="1">BLAPE!$B$8:$AZ$8</definedName>
+    <definedName name="_xlchart.v1.51" hidden="1">BLAPE!$B$9:$AZ$9</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">BLAPE!$A$3</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">BLAPE!$A$4</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">BLAPE!$A$5</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">BLAPE!$A$6</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
   <si>
     <t>BLAPE BAU LULUCF Anthropogenic Pollutant Emissions</t>
   </si>
@@ -270,6 +325,9 @@
   </si>
   <si>
     <t>Net Emissions</t>
+  </si>
+  <si>
+    <t>Smoothing</t>
   </si>
 </sst>
 </file>
@@ -532,7 +590,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -621,6 +679,9 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -644,6 +705,18 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="11" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1948,10 +2021,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="136" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>38</v>
       </c>
       <c r="C1" s="7" t="s">
@@ -1998,27 +2071,27 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="42" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
     </row>
     <row r="3" spans="1:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="44" t="s">
         <v>61</v>
       </c>
       <c r="B3" s="22" t="s">
@@ -2068,7 +2141,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44"/>
+      <c r="A4" s="45"/>
       <c r="B4" s="23" t="s">
         <v>48</v>
       </c>
@@ -2116,7 +2189,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="45"/>
+      <c r="A5" s="46"/>
       <c r="B5" s="14" t="s">
         <v>36</v>
       </c>
@@ -4173,6 +4246,855 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4158561-B7DA-5C4D-8B0E-0E975AC052C2}">
+  <dimension ref="A1:BS52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A1" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="47">
+        <v>2001</v>
+      </c>
+      <c r="C1" s="47">
+        <v>2002</v>
+      </c>
+      <c r="D1" s="47">
+        <v>2003</v>
+      </c>
+      <c r="E1" s="47">
+        <v>2004</v>
+      </c>
+      <c r="F1" s="47">
+        <v>2005</v>
+      </c>
+      <c r="G1" s="47">
+        <v>2006</v>
+      </c>
+      <c r="H1" s="47">
+        <v>2007</v>
+      </c>
+      <c r="I1" s="47">
+        <v>2008</v>
+      </c>
+      <c r="J1" s="47">
+        <v>2009</v>
+      </c>
+      <c r="K1" s="47">
+        <v>2010</v>
+      </c>
+      <c r="L1" s="47">
+        <v>2011</v>
+      </c>
+      <c r="M1" s="47">
+        <v>2012</v>
+      </c>
+      <c r="N1" s="47">
+        <v>2013</v>
+      </c>
+      <c r="O1" s="47">
+        <v>2014</v>
+      </c>
+      <c r="P1" s="47">
+        <v>2015</v>
+      </c>
+      <c r="Q1" s="47">
+        <v>2016</v>
+      </c>
+      <c r="R1" s="47">
+        <v>2017</v>
+      </c>
+      <c r="S1" s="47">
+        <v>2018</v>
+      </c>
+      <c r="T1" s="47">
+        <v>2019</v>
+      </c>
+      <c r="U1" s="47">
+        <v>2020</v>
+      </c>
+      <c r="V1" s="47">
+        <v>2021</v>
+      </c>
+      <c r="W1" s="47">
+        <v>2022</v>
+      </c>
+      <c r="X1" s="47">
+        <v>2023</v>
+      </c>
+      <c r="Y1" s="32">
+        <v>2024</v>
+      </c>
+      <c r="Z1" s="32">
+        <v>2025</v>
+      </c>
+      <c r="AA1" s="32">
+        <v>2026</v>
+      </c>
+      <c r="AB1" s="32">
+        <v>2027</v>
+      </c>
+      <c r="AC1" s="32">
+        <v>2028</v>
+      </c>
+      <c r="AD1" s="32">
+        <v>2029</v>
+      </c>
+      <c r="AE1" s="32">
+        <v>2030</v>
+      </c>
+      <c r="AF1" s="32">
+        <v>2031</v>
+      </c>
+      <c r="AG1" s="32">
+        <v>2032</v>
+      </c>
+      <c r="AH1" s="32">
+        <v>2033</v>
+      </c>
+      <c r="AI1" s="32">
+        <v>2034</v>
+      </c>
+      <c r="AJ1" s="32">
+        <v>2035</v>
+      </c>
+      <c r="AK1" s="32">
+        <v>2036</v>
+      </c>
+      <c r="AL1" s="32">
+        <v>2037</v>
+      </c>
+      <c r="AM1" s="32">
+        <v>2038</v>
+      </c>
+      <c r="AN1" s="32">
+        <v>2039</v>
+      </c>
+      <c r="AO1" s="32">
+        <v>2040</v>
+      </c>
+      <c r="AP1" s="32">
+        <v>2041</v>
+      </c>
+      <c r="AQ1" s="32">
+        <v>2042</v>
+      </c>
+      <c r="AR1" s="32">
+        <v>2043</v>
+      </c>
+      <c r="AS1" s="32">
+        <v>2044</v>
+      </c>
+      <c r="AT1" s="32">
+        <v>2045</v>
+      </c>
+      <c r="AU1" s="32">
+        <v>2046</v>
+      </c>
+      <c r="AV1" s="32">
+        <v>2047</v>
+      </c>
+      <c r="AW1" s="32">
+        <v>2048</v>
+      </c>
+      <c r="AX1" s="32">
+        <v>2049</v>
+      </c>
+      <c r="AY1" s="32">
+        <v>2050</v>
+      </c>
+      <c r="AZ1" s="32">
+        <v>2051</v>
+      </c>
+      <c r="BA1" s="32">
+        <v>2052</v>
+      </c>
+      <c r="BB1" s="32">
+        <v>2053</v>
+      </c>
+      <c r="BC1" s="32">
+        <v>2054</v>
+      </c>
+      <c r="BD1" s="32">
+        <v>2055</v>
+      </c>
+      <c r="BE1" s="32">
+        <v>2056</v>
+      </c>
+      <c r="BF1" s="32">
+        <v>2057</v>
+      </c>
+      <c r="BG1" s="32">
+        <v>2058</v>
+      </c>
+      <c r="BH1" s="32">
+        <v>2059</v>
+      </c>
+      <c r="BI1" s="32">
+        <v>2060</v>
+      </c>
+      <c r="BJ1" s="32">
+        <v>2061</v>
+      </c>
+      <c r="BK1" s="32">
+        <v>2062</v>
+      </c>
+      <c r="BL1" s="32">
+        <v>2063</v>
+      </c>
+      <c r="BM1" s="32">
+        <v>2064</v>
+      </c>
+      <c r="BN1" s="32">
+        <v>2065</v>
+      </c>
+      <c r="BO1" s="32">
+        <v>2066</v>
+      </c>
+      <c r="BP1" s="32">
+        <v>2067</v>
+      </c>
+      <c r="BQ1" s="32">
+        <v>2068</v>
+      </c>
+      <c r="BR1" s="32">
+        <v>2069</v>
+      </c>
+      <c r="BS1" s="32">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A2" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="50">
+        <v>487112043.833933</v>
+      </c>
+      <c r="C2" s="50">
+        <v>622211848.97139394</v>
+      </c>
+      <c r="D2" s="50">
+        <v>425249021.43136698</v>
+      </c>
+      <c r="E2" s="50">
+        <v>968726366.71286404</v>
+      </c>
+      <c r="F2" s="50">
+        <v>936152482.18395102</v>
+      </c>
+      <c r="G2" s="50">
+        <v>1011574573.61526</v>
+      </c>
+      <c r="H2" s="50">
+        <v>1145561681.9501901</v>
+      </c>
+      <c r="I2" s="50">
+        <v>1017426049.27597</v>
+      </c>
+      <c r="J2" s="50">
+        <v>1390891486.2902701</v>
+      </c>
+      <c r="K2" s="50">
+        <v>1018245685.5022</v>
+      </c>
+      <c r="L2" s="50">
+        <v>1211492988.0069599</v>
+      </c>
+      <c r="M2" s="50">
+        <v>1746946112.55408</v>
+      </c>
+      <c r="N2" s="50">
+        <v>854040060.67016602</v>
+      </c>
+      <c r="O2" s="50">
+        <v>1384924175.98224</v>
+      </c>
+      <c r="P2" s="50">
+        <v>1243010935.67065</v>
+      </c>
+      <c r="Q2" s="50">
+        <v>1770724294.7464199</v>
+      </c>
+      <c r="R2" s="50">
+        <v>823226714.26742995</v>
+      </c>
+      <c r="S2" s="50">
+        <v>759612569.31596601</v>
+      </c>
+      <c r="T2" s="50">
+        <v>737282810.694085</v>
+      </c>
+      <c r="U2" s="50">
+        <v>591141108.38426197</v>
+      </c>
+      <c r="V2" s="50">
+        <v>509468798.90482098</v>
+      </c>
+      <c r="W2" s="50">
+        <v>542697155.05498004</v>
+      </c>
+      <c r="X2" s="50">
+        <v>843375900.38146496</v>
+      </c>
+      <c r="Y2" s="48">
+        <f>AVERAGE(B2:X2)</f>
+        <v>958308472.36525762</v>
+      </c>
+      <c r="Z2" s="48">
+        <f>AVERAGE(C2:Y2)</f>
+        <v>978795273.60575008</v>
+      </c>
+      <c r="AA2" s="48">
+        <f>AVERAGE(D2:Z2)</f>
+        <v>994298900.76376557</v>
+      </c>
+      <c r="AB2" s="48">
+        <f>AVERAGE(E2:AA2)</f>
+        <v>1019040199.8651743</v>
+      </c>
+      <c r="AC2" s="48">
+        <f>AVERAGE(F2:AB2)</f>
+        <v>1021227757.828318</v>
+      </c>
+      <c r="AD2" s="48">
+        <f>AVERAGE(G2:AC2)</f>
+        <v>1024926682.8563342</v>
+      </c>
+      <c r="AE2" s="48">
+        <f>AVERAGE(H2:AD2)</f>
+        <v>1025507209.3450763</v>
+      </c>
+      <c r="AF2" s="48">
+        <f>AVERAGE(I2:AE2)</f>
+        <v>1020287449.6665933</v>
+      </c>
+      <c r="AG2" s="48">
+        <f>AVERAGE(J2:AF2)</f>
+        <v>1020411858.3792288</v>
+      </c>
+      <c r="AH2" s="48">
+        <f>AVERAGE(K2:AG2)</f>
+        <v>1004304048.4700533</v>
+      </c>
+      <c r="AI2" s="48">
+        <f>AVERAGE(L2:AH2)</f>
+        <v>1003697890.3382208</v>
+      </c>
+      <c r="AJ2" s="48">
+        <f>AVERAGE(M2:AI2)</f>
+        <v>994663320.87436259</v>
+      </c>
+      <c r="AK2" s="48">
+        <f>AVERAGE(N2:AJ2)</f>
+        <v>961955373.41002703</v>
+      </c>
+      <c r="AL2" s="48">
+        <f>AVERAGE(O2:AK2)</f>
+        <v>966647343.52915156</v>
+      </c>
+      <c r="AM2" s="48">
+        <f>AVERAGE(P2:AL2)</f>
+        <v>948461394.29206073</v>
+      </c>
+      <c r="AN2" s="48">
+        <f>AVERAGE(Q2:AM2)</f>
+        <v>935654892.49299145</v>
+      </c>
+      <c r="AO2" s="48">
+        <f>AVERAGE(R2:AN2)</f>
+        <v>899347527.17762494</v>
+      </c>
+      <c r="AP2" s="48">
+        <f>AVERAGE(S2:AO2)</f>
+        <v>902657127.73893774</v>
+      </c>
+      <c r="AQ2" s="48">
+        <f>AVERAGE(T2:AP2)</f>
+        <v>908876456.3660233</v>
+      </c>
+      <c r="AR2" s="48">
+        <f>AVERAGE(U2:AQ2)</f>
+        <v>916337049.65610766</v>
+      </c>
+      <c r="AS2" s="48">
+        <f>AVERAGE(V2:AR2)</f>
+        <v>930476003.6244489</v>
+      </c>
+      <c r="AT2" s="48">
+        <f>AVERAGE(W2:AS2)</f>
+        <v>948780664.69921541</v>
+      </c>
+      <c r="AU2" s="48">
+        <f>AVERAGE(X2:AT2)</f>
+        <v>966436469.46635604</v>
+      </c>
+      <c r="AV2" s="48">
+        <f>AVERAGE(Y2:AU2)</f>
+        <v>971786928.99178624</v>
+      </c>
+      <c r="AW2" s="48">
+        <f>AVERAGE(Z2:AV2)</f>
+        <v>972372948.84511352</v>
+      </c>
+      <c r="AX2" s="48">
+        <f>AVERAGE(AA2:AW2)</f>
+        <v>972093717.33378136</v>
+      </c>
+      <c r="AY2" s="48">
+        <f>AVERAGE(AB2:AX2)</f>
+        <v>971128274.57595599</v>
+      </c>
+      <c r="AZ2" s="48">
+        <f>AVERAGE(AC2:AY2)</f>
+        <v>969045147.38946819</v>
+      </c>
+      <c r="BA2" s="48">
+        <f>AVERAGE(AD2:AZ2)</f>
+        <v>966776338.23995304</v>
+      </c>
+      <c r="BB2" s="48">
+        <f>AVERAGE(AE2:BA2)</f>
+        <v>964248062.38706684</v>
+      </c>
+      <c r="BC2" s="48">
+        <f>AVERAGE(AF2:BB2)</f>
+        <v>961584621.21497941</v>
+      </c>
+      <c r="BD2" s="48">
+        <f>AVERAGE(AG2:BC2)</f>
+        <v>959032324.32577896</v>
+      </c>
+      <c r="BE2" s="48">
+        <f>AVERAGE(AH2:BD2)</f>
+        <v>956363648.93215084</v>
+      </c>
+      <c r="BF2" s="48">
+        <f>AVERAGE(AI2:BE2)</f>
+        <v>954279283.73485065</v>
+      </c>
+      <c r="BG2" s="48">
+        <f>AVERAGE(AJ2:BF2)</f>
+        <v>952130648.66513896</v>
+      </c>
+      <c r="BH2" s="48">
+        <f>AVERAGE(AK2:BG2)</f>
+        <v>950281402.04734647</v>
+      </c>
+      <c r="BI2" s="48">
+        <f>AVERAGE(AL2:BH2)</f>
+        <v>949773838.0750562</v>
+      </c>
+      <c r="BJ2" s="48">
+        <f>AVERAGE(AM2:BI2)</f>
+        <v>949040207.403139</v>
+      </c>
+      <c r="BK2" s="48">
+        <f>AVERAGE(AN2:BJ2)</f>
+        <v>949065373.19057691</v>
+      </c>
+      <c r="BL2" s="48">
+        <f>AVERAGE(AO2:BK2)</f>
+        <v>949648437.56873286</v>
+      </c>
+      <c r="BM2" s="48">
+        <f>AVERAGE(AP2:BL2)</f>
+        <v>951835433.67269397</v>
+      </c>
+      <c r="BN2" s="48">
+        <f>AVERAGE(AQ2:BM2)</f>
+        <v>953973620.88720524</v>
+      </c>
+      <c r="BO2" s="48">
+        <f>AVERAGE(AR2:BN2)</f>
+        <v>955934367.17073488</v>
+      </c>
+      <c r="BP2" s="48">
+        <f>AVERAGE(AS2:BO2)</f>
+        <v>957655989.67137098</v>
+      </c>
+      <c r="BQ2" s="48">
+        <f>AVERAGE(AT2:BP2)</f>
+        <v>958837728.19515014</v>
+      </c>
+      <c r="BR2" s="48">
+        <f>AVERAGE(AU2:BQ2)</f>
+        <v>959274991.8254081</v>
+      </c>
+      <c r="BS2" s="48">
+        <f>AVERAGE(AV2:BR2)</f>
+        <v>958963623.23232341</v>
+      </c>
+    </row>
+    <row r="3" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A3" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="49">
+        <v>556000000</v>
+      </c>
+      <c r="C3" s="49">
+        <v>514000000</v>
+      </c>
+      <c r="D3" s="49">
+        <v>685000000</v>
+      </c>
+      <c r="E3" s="49">
+        <v>833000000</v>
+      </c>
+      <c r="F3" s="49">
+        <v>973000000</v>
+      </c>
+      <c r="G3" s="49">
+        <v>1050000000</v>
+      </c>
+      <c r="H3" s="49">
+        <v>1060000000</v>
+      </c>
+      <c r="I3" s="49">
+        <v>1190000000</v>
+      </c>
+      <c r="J3" s="49">
+        <v>1160000000</v>
+      </c>
+      <c r="K3" s="49">
+        <v>1180000000</v>
+      </c>
+      <c r="L3" s="49">
+        <v>1380000000</v>
+      </c>
+      <c r="M3" s="49">
+        <v>1270000000</v>
+      </c>
+      <c r="N3" s="49">
+        <v>1270000000</v>
+      </c>
+      <c r="O3" s="49">
+        <v>1210000000</v>
+      </c>
+      <c r="P3" s="49">
+        <v>1480000000</v>
+      </c>
+      <c r="Q3" s="49">
+        <v>1280000000</v>
+      </c>
+      <c r="R3" s="49">
+        <v>1010000000</v>
+      </c>
+      <c r="S3" s="49">
+        <v>765000000</v>
+      </c>
+      <c r="T3" s="49">
+        <v>684000000</v>
+      </c>
+      <c r="U3" s="49">
+        <v>592000000</v>
+      </c>
+      <c r="V3" s="49">
+        <v>541000000</v>
+      </c>
+      <c r="W3" s="49">
+        <v>654000000</v>
+      </c>
+      <c r="X3" s="49">
+        <v>821000000</v>
+      </c>
+      <c r="Y3" s="49">
+        <v>940000000</v>
+      </c>
+      <c r="Z3" s="49">
+        <v>980000000</v>
+      </c>
+      <c r="AA3" s="49">
+        <v>1000000000</v>
+      </c>
+      <c r="AB3" s="49">
+        <v>1010000000</v>
+      </c>
+      <c r="AC3" s="49">
+        <v>1020000000</v>
+      </c>
+      <c r="AD3" s="49">
+        <v>1020000000</v>
+      </c>
+      <c r="AE3" s="49">
+        <v>1020000000</v>
+      </c>
+      <c r="AF3" s="49">
+        <v>1020000000</v>
+      </c>
+      <c r="AG3" s="49">
+        <v>1010000000</v>
+      </c>
+      <c r="AH3" s="49">
+        <v>1010000000</v>
+      </c>
+      <c r="AI3" s="49">
+        <v>1000000000</v>
+      </c>
+      <c r="AJ3" s="49">
+        <v>984000000</v>
+      </c>
+      <c r="AK3" s="49">
+        <v>971000000</v>
+      </c>
+      <c r="AL3" s="49">
+        <v>958000000</v>
+      </c>
+      <c r="AM3" s="49">
+        <v>948000000</v>
+      </c>
+      <c r="AN3" s="49">
+        <v>924000000</v>
+      </c>
+      <c r="AO3" s="49">
+        <v>909000000</v>
+      </c>
+      <c r="AP3" s="49">
+        <v>904000000</v>
+      </c>
+      <c r="AQ3" s="49">
+        <v>910000000</v>
+      </c>
+      <c r="AR3" s="49">
+        <v>920000000</v>
+      </c>
+      <c r="AS3" s="49">
+        <v>935000000</v>
+      </c>
+      <c r="AT3" s="49">
+        <v>952000000</v>
+      </c>
+      <c r="AU3" s="49">
+        <v>965000000</v>
+      </c>
+      <c r="AV3" s="49">
+        <v>971000000</v>
+      </c>
+      <c r="AW3" s="49">
+        <v>972000000</v>
+      </c>
+      <c r="AX3" s="49">
+        <v>972000000</v>
+      </c>
+      <c r="AY3" s="49">
+        <v>971000000</v>
+      </c>
+      <c r="AZ3" s="49">
+        <v>969000000</v>
+      </c>
+      <c r="BA3" s="49">
+        <v>966000000</v>
+      </c>
+      <c r="BB3" s="49">
+        <v>964000000</v>
+      </c>
+      <c r="BC3" s="49">
+        <v>961000000</v>
+      </c>
+      <c r="BD3" s="49">
+        <v>959000000</v>
+      </c>
+      <c r="BE3" s="49">
+        <v>956000000</v>
+      </c>
+      <c r="BF3" s="49">
+        <v>954000000</v>
+      </c>
+      <c r="BG3" s="49">
+        <v>952000000</v>
+      </c>
+      <c r="BH3" s="49">
+        <v>950000000</v>
+      </c>
+      <c r="BI3" s="49">
+        <v>950000000</v>
+      </c>
+      <c r="BJ3" s="49">
+        <v>949000000</v>
+      </c>
+      <c r="BK3" s="49">
+        <v>949000000</v>
+      </c>
+      <c r="BL3" s="49">
+        <v>950000000</v>
+      </c>
+      <c r="BM3" s="49">
+        <v>952000000</v>
+      </c>
+      <c r="BN3" s="49">
+        <v>954000000</v>
+      </c>
+      <c r="BO3" s="49">
+        <v>956000000</v>
+      </c>
+      <c r="BP3" s="49">
+        <v>958000000</v>
+      </c>
+      <c r="BQ3" s="49">
+        <v>959000000</v>
+      </c>
+      <c r="BR3" s="49">
+        <v>959000000</v>
+      </c>
+      <c r="BS3" s="49">
+        <v>959000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A4" s="35"/>
+    </row>
+    <row r="5" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A5" s="35"/>
+    </row>
+    <row r="6" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A6" s="35"/>
+    </row>
+    <row r="7" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A7" s="35"/>
+    </row>
+    <row r="8" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A8" s="35"/>
+    </row>
+    <row r="9" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A9" s="35"/>
+    </row>
+    <row r="10" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A10" s="35"/>
+    </row>
+    <row r="11" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A11" s="35"/>
+    </row>
+    <row r="12" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A12" s="35"/>
+    </row>
+    <row r="13" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A13" s="35"/>
+    </row>
+    <row r="14" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A14" s="35"/>
+    </row>
+    <row r="15" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A15" s="35"/>
+    </row>
+    <row r="16" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A16" s="35"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="35"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="35"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="35"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="35"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="35"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="35"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="35"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="35"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="35"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="35"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="35"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="35"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="35"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="35"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="35"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="35"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="35"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="35"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="35"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="35"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="35"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" s="35"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" s="35"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" s="35"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" s="35"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" s="35"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" s="35"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" s="35"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" s="35"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" s="35"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" s="35"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" s="35"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="35"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" s="35"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" s="35"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" s="35"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1142EC34-7E3E-C64E-8A49-B83C16A04B23}">
   <dimension ref="A1:BW52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4486,262 +5408,285 @@
       <c r="A3" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="28">
-        <v>487112043.833933</v>
-      </c>
-      <c r="C3" s="28">
-        <v>622211848.97139394</v>
-      </c>
-      <c r="D3" s="28">
-        <v>425249021.43136698</v>
-      </c>
-      <c r="E3" s="28">
-        <v>968726366.71286404</v>
-      </c>
-      <c r="F3" s="28">
-        <v>936152482.18395102</v>
-      </c>
-      <c r="G3" s="28">
-        <v>1011574573.61526</v>
-      </c>
-      <c r="H3" s="28">
-        <v>1145561681.9501901</v>
-      </c>
-      <c r="I3" s="28">
-        <v>1017426049.27597</v>
-      </c>
-      <c r="J3" s="28">
-        <v>1390891486.2902701</v>
-      </c>
-      <c r="K3" s="28">
-        <v>1018245685.5022</v>
-      </c>
-      <c r="L3" s="28">
-        <v>1211492988.0069599</v>
-      </c>
-      <c r="M3" s="28">
-        <v>1746946112.55408</v>
-      </c>
-      <c r="N3" s="28">
-        <v>854040060.67016602</v>
-      </c>
-      <c r="O3" s="28">
-        <v>1384924175.98224</v>
-      </c>
-      <c r="P3" s="28">
-        <v>1243010935.67065</v>
-      </c>
-      <c r="Q3" s="28">
-        <v>1770724294.7464199</v>
-      </c>
-      <c r="R3" s="28">
-        <v>823226714.26742995</v>
-      </c>
-      <c r="S3" s="28">
-        <v>759612569.31596601</v>
-      </c>
-      <c r="T3" s="28">
-        <v>737282810.694085</v>
-      </c>
-      <c r="U3" s="28">
-        <v>591141108.38426197</v>
-      </c>
-      <c r="V3" s="28">
-        <v>509468798.90482098</v>
-      </c>
-      <c r="W3" s="28">
-        <v>542697155.05498004</v>
-      </c>
-      <c r="X3" s="28">
-        <v>843375900.38146496</v>
-      </c>
-      <c r="Y3" s="29">
-        <f>AVERAGE(B3:X3)</f>
-        <v>958308472.36525762</v>
-      </c>
-      <c r="Z3" s="29">
-        <f t="shared" ref="Z3:BS3" si="0">AVERAGE(C3:Y3)</f>
-        <v>978795273.60575008</v>
-      </c>
-      <c r="AA3" s="29">
-        <f t="shared" si="0"/>
-        <v>994298900.76376557</v>
-      </c>
-      <c r="AB3" s="29">
-        <f t="shared" si="0"/>
-        <v>1019040199.8651743</v>
-      </c>
-      <c r="AC3" s="29">
-        <f t="shared" si="0"/>
-        <v>1021227757.828318</v>
-      </c>
-      <c r="AD3" s="29">
-        <f t="shared" si="0"/>
-        <v>1024926682.8563342</v>
-      </c>
-      <c r="AE3" s="29">
-        <f t="shared" si="0"/>
-        <v>1025507209.3450763</v>
-      </c>
-      <c r="AF3" s="29">
-        <f t="shared" si="0"/>
-        <v>1020287449.6665933</v>
-      </c>
-      <c r="AG3" s="29">
-        <f t="shared" si="0"/>
-        <v>1020411858.3792288</v>
-      </c>
-      <c r="AH3" s="29">
-        <f t="shared" si="0"/>
-        <v>1004304048.4700533</v>
-      </c>
-      <c r="AI3" s="29">
-        <f t="shared" si="0"/>
-        <v>1003697890.3382208</v>
-      </c>
-      <c r="AJ3" s="29">
-        <f t="shared" si="0"/>
-        <v>994663320.87436259</v>
-      </c>
-      <c r="AK3" s="29">
-        <f t="shared" si="0"/>
-        <v>961955373.41002703</v>
-      </c>
-      <c r="AL3" s="29">
-        <f t="shared" si="0"/>
-        <v>966647343.52915156</v>
-      </c>
-      <c r="AM3" s="29">
-        <f t="shared" si="0"/>
-        <v>948461394.29206073</v>
-      </c>
-      <c r="AN3" s="29">
-        <f t="shared" si="0"/>
-        <v>935654892.49299145</v>
-      </c>
-      <c r="AO3" s="29">
-        <f t="shared" si="0"/>
-        <v>899347527.17762494</v>
-      </c>
-      <c r="AP3" s="29">
-        <f t="shared" si="0"/>
-        <v>902657127.73893774</v>
-      </c>
-      <c r="AQ3" s="29">
-        <f t="shared" si="0"/>
-        <v>908876456.3660233</v>
-      </c>
-      <c r="AR3" s="29">
-        <f t="shared" si="0"/>
-        <v>916337049.65610766</v>
-      </c>
-      <c r="AS3" s="29">
-        <f t="shared" si="0"/>
-        <v>930476003.6244489</v>
-      </c>
-      <c r="AT3" s="29">
-        <f t="shared" si="0"/>
-        <v>948780664.69921541</v>
-      </c>
-      <c r="AU3" s="29">
-        <f t="shared" si="0"/>
-        <v>966436469.46635604</v>
-      </c>
-      <c r="AV3" s="29">
-        <f t="shared" si="0"/>
-        <v>971786928.99178624</v>
-      </c>
-      <c r="AW3" s="29">
-        <f t="shared" si="0"/>
-        <v>972372948.84511352</v>
-      </c>
-      <c r="AX3" s="29">
-        <f t="shared" si="0"/>
-        <v>972093717.33378136</v>
-      </c>
-      <c r="AY3" s="29">
-        <f t="shared" si="0"/>
-        <v>971128274.57595599</v>
-      </c>
-      <c r="AZ3" s="29">
-        <f t="shared" si="0"/>
-        <v>969045147.38946819</v>
-      </c>
-      <c r="BA3" s="29">
-        <f t="shared" si="0"/>
-        <v>966776338.23995304</v>
-      </c>
-      <c r="BB3" s="29">
-        <f t="shared" si="0"/>
-        <v>964248062.38706684</v>
-      </c>
-      <c r="BC3" s="29">
-        <f t="shared" si="0"/>
-        <v>961584621.21497941</v>
-      </c>
-      <c r="BD3" s="29">
-        <f t="shared" si="0"/>
-        <v>959032324.32577896</v>
-      </c>
-      <c r="BE3" s="29">
-        <f t="shared" si="0"/>
-        <v>956363648.93215084</v>
-      </c>
-      <c r="BF3" s="29">
-        <f t="shared" si="0"/>
-        <v>954279283.73485065</v>
-      </c>
-      <c r="BG3" s="29">
-        <f t="shared" si="0"/>
-        <v>952130648.66513896</v>
-      </c>
-      <c r="BH3" s="29">
-        <f t="shared" si="0"/>
-        <v>950281402.04734647</v>
-      </c>
-      <c r="BI3" s="29">
-        <f t="shared" si="0"/>
-        <v>949773838.0750562</v>
-      </c>
-      <c r="BJ3" s="29">
-        <f t="shared" si="0"/>
-        <v>949040207.403139</v>
-      </c>
-      <c r="BK3" s="29">
-        <f t="shared" si="0"/>
-        <v>949065373.19057691</v>
-      </c>
-      <c r="BL3" s="29">
-        <f t="shared" si="0"/>
-        <v>949648437.56873286</v>
-      </c>
-      <c r="BM3" s="29">
-        <f t="shared" si="0"/>
-        <v>951835433.67269397</v>
-      </c>
-      <c r="BN3" s="29">
-        <f t="shared" si="0"/>
-        <v>953973620.88720524</v>
-      </c>
-      <c r="BO3" s="29">
-        <f t="shared" si="0"/>
-        <v>955934367.17073488</v>
-      </c>
-      <c r="BP3" s="29">
-        <f t="shared" si="0"/>
-        <v>957655989.67137098</v>
-      </c>
-      <c r="BQ3" s="29">
-        <f t="shared" si="0"/>
-        <v>958837728.19515014</v>
-      </c>
-      <c r="BR3" s="29">
-        <f t="shared" si="0"/>
-        <v>959274991.8254081</v>
-      </c>
-      <c r="BS3" s="29">
-        <f t="shared" si="0"/>
-        <v>958963623.23232341</v>
+      <c r="B3" s="37">
+        <f>'GWF-Smoothing '!B3</f>
+        <v>556000000</v>
+      </c>
+      <c r="C3" s="37">
+        <f>'GWF-Smoothing '!C3</f>
+        <v>514000000</v>
+      </c>
+      <c r="D3" s="37">
+        <f>'GWF-Smoothing '!D3</f>
+        <v>685000000</v>
+      </c>
+      <c r="E3" s="37">
+        <f>'GWF-Smoothing '!E3</f>
+        <v>833000000</v>
+      </c>
+      <c r="F3" s="37">
+        <f>'GWF-Smoothing '!F3</f>
+        <v>973000000</v>
+      </c>
+      <c r="G3" s="37">
+        <f>'GWF-Smoothing '!G3</f>
+        <v>1050000000</v>
+      </c>
+      <c r="H3" s="37">
+        <f>'GWF-Smoothing '!H3</f>
+        <v>1060000000</v>
+      </c>
+      <c r="I3" s="37">
+        <f>'GWF-Smoothing '!I3</f>
+        <v>1190000000</v>
+      </c>
+      <c r="J3" s="37">
+        <f>'GWF-Smoothing '!J3</f>
+        <v>1160000000</v>
+      </c>
+      <c r="K3" s="37">
+        <f>'GWF-Smoothing '!K3</f>
+        <v>1180000000</v>
+      </c>
+      <c r="L3" s="37">
+        <f>'GWF-Smoothing '!L3</f>
+        <v>1380000000</v>
+      </c>
+      <c r="M3" s="37">
+        <f>'GWF-Smoothing '!M3</f>
+        <v>1270000000</v>
+      </c>
+      <c r="N3" s="37">
+        <f>'GWF-Smoothing '!N3</f>
+        <v>1270000000</v>
+      </c>
+      <c r="O3" s="37">
+        <f>'GWF-Smoothing '!O3</f>
+        <v>1210000000</v>
+      </c>
+      <c r="P3" s="37">
+        <f>'GWF-Smoothing '!P3</f>
+        <v>1480000000</v>
+      </c>
+      <c r="Q3" s="37">
+        <f>'GWF-Smoothing '!Q3</f>
+        <v>1280000000</v>
+      </c>
+      <c r="R3" s="37">
+        <f>'GWF-Smoothing '!R3</f>
+        <v>1010000000</v>
+      </c>
+      <c r="S3" s="37">
+        <f>'GWF-Smoothing '!S3</f>
+        <v>765000000</v>
+      </c>
+      <c r="T3" s="37">
+        <f>'GWF-Smoothing '!T3</f>
+        <v>684000000</v>
+      </c>
+      <c r="U3" s="37">
+        <f>'GWF-Smoothing '!U3</f>
+        <v>592000000</v>
+      </c>
+      <c r="V3" s="37">
+        <f>'GWF-Smoothing '!V3</f>
+        <v>541000000</v>
+      </c>
+      <c r="W3" s="37">
+        <f>'GWF-Smoothing '!W3</f>
+        <v>654000000</v>
+      </c>
+      <c r="X3" s="37">
+        <f>'GWF-Smoothing '!X3</f>
+        <v>821000000</v>
+      </c>
+      <c r="Y3" s="37">
+        <f>'GWF-Smoothing '!Y3</f>
+        <v>940000000</v>
+      </c>
+      <c r="Z3" s="37">
+        <f>'GWF-Smoothing '!Z3</f>
+        <v>980000000</v>
+      </c>
+      <c r="AA3" s="37">
+        <f>'GWF-Smoothing '!AA3</f>
+        <v>1000000000</v>
+      </c>
+      <c r="AB3" s="37">
+        <f>'GWF-Smoothing '!AB3</f>
+        <v>1010000000</v>
+      </c>
+      <c r="AC3" s="37">
+        <f>'GWF-Smoothing '!AC3</f>
+        <v>1020000000</v>
+      </c>
+      <c r="AD3" s="37">
+        <f>'GWF-Smoothing '!AD3</f>
+        <v>1020000000</v>
+      </c>
+      <c r="AE3" s="37">
+        <f>'GWF-Smoothing '!AE3</f>
+        <v>1020000000</v>
+      </c>
+      <c r="AF3" s="37">
+        <f>'GWF-Smoothing '!AF3</f>
+        <v>1020000000</v>
+      </c>
+      <c r="AG3" s="37">
+        <f>'GWF-Smoothing '!AG3</f>
+        <v>1010000000</v>
+      </c>
+      <c r="AH3" s="37">
+        <f>'GWF-Smoothing '!AH3</f>
+        <v>1010000000</v>
+      </c>
+      <c r="AI3" s="37">
+        <f>'GWF-Smoothing '!AI3</f>
+        <v>1000000000</v>
+      </c>
+      <c r="AJ3" s="37">
+        <f>'GWF-Smoothing '!AJ3</f>
+        <v>984000000</v>
+      </c>
+      <c r="AK3" s="37">
+        <f>'GWF-Smoothing '!AK3</f>
+        <v>971000000</v>
+      </c>
+      <c r="AL3" s="37">
+        <f>'GWF-Smoothing '!AL3</f>
+        <v>958000000</v>
+      </c>
+      <c r="AM3" s="37">
+        <f>'GWF-Smoothing '!AM3</f>
+        <v>948000000</v>
+      </c>
+      <c r="AN3" s="37">
+        <f>'GWF-Smoothing '!AN3</f>
+        <v>924000000</v>
+      </c>
+      <c r="AO3" s="37">
+        <f>'GWF-Smoothing '!AO3</f>
+        <v>909000000</v>
+      </c>
+      <c r="AP3" s="37">
+        <f>'GWF-Smoothing '!AP3</f>
+        <v>904000000</v>
+      </c>
+      <c r="AQ3" s="37">
+        <f>'GWF-Smoothing '!AQ3</f>
+        <v>910000000</v>
+      </c>
+      <c r="AR3" s="37">
+        <f>'GWF-Smoothing '!AR3</f>
+        <v>920000000</v>
+      </c>
+      <c r="AS3" s="37">
+        <f>'GWF-Smoothing '!AS3</f>
+        <v>935000000</v>
+      </c>
+      <c r="AT3" s="37">
+        <f>'GWF-Smoothing '!AT3</f>
+        <v>952000000</v>
+      </c>
+      <c r="AU3" s="37">
+        <f>'GWF-Smoothing '!AU3</f>
+        <v>965000000</v>
+      </c>
+      <c r="AV3" s="37">
+        <f>'GWF-Smoothing '!AV3</f>
+        <v>971000000</v>
+      </c>
+      <c r="AW3" s="37">
+        <f>'GWF-Smoothing '!AW3</f>
+        <v>972000000</v>
+      </c>
+      <c r="AX3" s="37">
+        <f>'GWF-Smoothing '!AX3</f>
+        <v>972000000</v>
+      </c>
+      <c r="AY3" s="37">
+        <f>'GWF-Smoothing '!AY3</f>
+        <v>971000000</v>
+      </c>
+      <c r="AZ3" s="37">
+        <f>'GWF-Smoothing '!AZ3</f>
+        <v>969000000</v>
+      </c>
+      <c r="BA3" s="37">
+        <f>'GWF-Smoothing '!BA3</f>
+        <v>966000000</v>
+      </c>
+      <c r="BB3" s="37">
+        <f>'GWF-Smoothing '!BB3</f>
+        <v>964000000</v>
+      </c>
+      <c r="BC3" s="37">
+        <f>'GWF-Smoothing '!BC3</f>
+        <v>961000000</v>
+      </c>
+      <c r="BD3" s="37">
+        <f>'GWF-Smoothing '!BD3</f>
+        <v>959000000</v>
+      </c>
+      <c r="BE3" s="37">
+        <f>'GWF-Smoothing '!BE3</f>
+        <v>956000000</v>
+      </c>
+      <c r="BF3" s="37">
+        <f>'GWF-Smoothing '!BF3</f>
+        <v>954000000</v>
+      </c>
+      <c r="BG3" s="37">
+        <f>'GWF-Smoothing '!BG3</f>
+        <v>952000000</v>
+      </c>
+      <c r="BH3" s="37">
+        <f>'GWF-Smoothing '!BH3</f>
+        <v>950000000</v>
+      </c>
+      <c r="BI3" s="37">
+        <f>'GWF-Smoothing '!BI3</f>
+        <v>950000000</v>
+      </c>
+      <c r="BJ3" s="37">
+        <f>'GWF-Smoothing '!BJ3</f>
+        <v>949000000</v>
+      </c>
+      <c r="BK3" s="37">
+        <f>'GWF-Smoothing '!BK3</f>
+        <v>949000000</v>
+      </c>
+      <c r="BL3" s="37">
+        <f>'GWF-Smoothing '!BL3</f>
+        <v>950000000</v>
+      </c>
+      <c r="BM3" s="37">
+        <f>'GWF-Smoothing '!BM3</f>
+        <v>952000000</v>
+      </c>
+      <c r="BN3" s="37">
+        <f>'GWF-Smoothing '!BN3</f>
+        <v>954000000</v>
+      </c>
+      <c r="BO3" s="37">
+        <f>'GWF-Smoothing '!BO3</f>
+        <v>956000000</v>
+      </c>
+      <c r="BP3" s="37">
+        <f>'GWF-Smoothing '!BP3</f>
+        <v>958000000</v>
+      </c>
+      <c r="BQ3" s="37">
+        <f>'GWF-Smoothing '!BQ3</f>
+        <v>959000000</v>
+      </c>
+      <c r="BR3" s="37">
+        <f>'GWF-Smoothing '!BR3</f>
+        <v>959000000</v>
+      </c>
+      <c r="BS3" s="37">
+        <f>'GWF-Smoothing '!BS3</f>
+        <v>959000000</v>
       </c>
     </row>
     <row r="4" spans="1:75" x14ac:dyDescent="0.2">
@@ -4905,283 +5850,283 @@
       </c>
       <c r="B6" s="37">
         <f>B3-$B$5</f>
-        <v>-129887956.166067</v>
+        <v>-61000000</v>
       </c>
       <c r="C6" s="37">
-        <f t="shared" ref="C6:BN6" si="1">C3-$B$5</f>
-        <v>5211848.9713939428</v>
+        <f t="shared" ref="C6:BN6" si="0">C3-$B$5</f>
+        <v>-103000000</v>
       </c>
       <c r="D6" s="37">
+        <f t="shared" si="0"/>
+        <v>68000000</v>
+      </c>
+      <c r="E6" s="37">
+        <f t="shared" si="0"/>
+        <v>216000000</v>
+      </c>
+      <c r="F6" s="37">
+        <f t="shared" si="0"/>
+        <v>356000000</v>
+      </c>
+      <c r="G6" s="37">
+        <f t="shared" si="0"/>
+        <v>433000000</v>
+      </c>
+      <c r="H6" s="37">
+        <f t="shared" si="0"/>
+        <v>443000000</v>
+      </c>
+      <c r="I6" s="37">
+        <f t="shared" si="0"/>
+        <v>573000000</v>
+      </c>
+      <c r="J6" s="37">
+        <f t="shared" si="0"/>
+        <v>543000000</v>
+      </c>
+      <c r="K6" s="37">
+        <f t="shared" si="0"/>
+        <v>563000000</v>
+      </c>
+      <c r="L6" s="37">
+        <f t="shared" si="0"/>
+        <v>763000000</v>
+      </c>
+      <c r="M6" s="37">
+        <f t="shared" si="0"/>
+        <v>653000000</v>
+      </c>
+      <c r="N6" s="37">
+        <f t="shared" si="0"/>
+        <v>653000000</v>
+      </c>
+      <c r="O6" s="37">
+        <f t="shared" si="0"/>
+        <v>593000000</v>
+      </c>
+      <c r="P6" s="37">
+        <f t="shared" si="0"/>
+        <v>863000000</v>
+      </c>
+      <c r="Q6" s="37">
+        <f t="shared" si="0"/>
+        <v>663000000</v>
+      </c>
+      <c r="R6" s="37">
+        <f t="shared" si="0"/>
+        <v>393000000</v>
+      </c>
+      <c r="S6" s="37">
+        <f t="shared" si="0"/>
+        <v>148000000</v>
+      </c>
+      <c r="T6" s="37">
+        <f t="shared" si="0"/>
+        <v>67000000</v>
+      </c>
+      <c r="U6" s="37">
+        <f t="shared" si="0"/>
+        <v>-25000000</v>
+      </c>
+      <c r="V6" s="37">
+        <f t="shared" si="0"/>
+        <v>-76000000</v>
+      </c>
+      <c r="W6" s="37">
+        <f t="shared" si="0"/>
+        <v>37000000</v>
+      </c>
+      <c r="X6" s="37">
+        <f t="shared" si="0"/>
+        <v>204000000</v>
+      </c>
+      <c r="Y6" s="37">
+        <f t="shared" si="0"/>
+        <v>323000000</v>
+      </c>
+      <c r="Z6" s="37">
+        <f t="shared" si="0"/>
+        <v>363000000</v>
+      </c>
+      <c r="AA6" s="37">
+        <f t="shared" si="0"/>
+        <v>383000000</v>
+      </c>
+      <c r="AB6" s="37">
+        <f t="shared" si="0"/>
+        <v>393000000</v>
+      </c>
+      <c r="AC6" s="37">
+        <f t="shared" si="0"/>
+        <v>403000000</v>
+      </c>
+      <c r="AD6" s="37">
+        <f t="shared" si="0"/>
+        <v>403000000</v>
+      </c>
+      <c r="AE6" s="37">
+        <f t="shared" si="0"/>
+        <v>403000000</v>
+      </c>
+      <c r="AF6" s="37">
+        <f t="shared" si="0"/>
+        <v>403000000</v>
+      </c>
+      <c r="AG6" s="37">
+        <f t="shared" si="0"/>
+        <v>393000000</v>
+      </c>
+      <c r="AH6" s="37">
+        <f t="shared" si="0"/>
+        <v>393000000</v>
+      </c>
+      <c r="AI6" s="37">
+        <f t="shared" si="0"/>
+        <v>383000000</v>
+      </c>
+      <c r="AJ6" s="37">
+        <f t="shared" si="0"/>
+        <v>367000000</v>
+      </c>
+      <c r="AK6" s="37">
+        <f t="shared" si="0"/>
+        <v>354000000</v>
+      </c>
+      <c r="AL6" s="37">
+        <f t="shared" si="0"/>
+        <v>341000000</v>
+      </c>
+      <c r="AM6" s="37">
+        <f t="shared" si="0"/>
+        <v>331000000</v>
+      </c>
+      <c r="AN6" s="37">
+        <f t="shared" si="0"/>
+        <v>307000000</v>
+      </c>
+      <c r="AO6" s="37">
+        <f t="shared" si="0"/>
+        <v>292000000</v>
+      </c>
+      <c r="AP6" s="37">
+        <f t="shared" si="0"/>
+        <v>287000000</v>
+      </c>
+      <c r="AQ6" s="37">
+        <f t="shared" si="0"/>
+        <v>293000000</v>
+      </c>
+      <c r="AR6" s="37">
+        <f t="shared" si="0"/>
+        <v>303000000</v>
+      </c>
+      <c r="AS6" s="37">
+        <f t="shared" si="0"/>
+        <v>318000000</v>
+      </c>
+      <c r="AT6" s="37">
+        <f t="shared" si="0"/>
+        <v>335000000</v>
+      </c>
+      <c r="AU6" s="37">
+        <f t="shared" si="0"/>
+        <v>348000000</v>
+      </c>
+      <c r="AV6" s="37">
+        <f t="shared" si="0"/>
+        <v>354000000</v>
+      </c>
+      <c r="AW6" s="37">
+        <f t="shared" si="0"/>
+        <v>355000000</v>
+      </c>
+      <c r="AX6" s="37">
+        <f t="shared" si="0"/>
+        <v>355000000</v>
+      </c>
+      <c r="AY6" s="37">
+        <f t="shared" si="0"/>
+        <v>354000000</v>
+      </c>
+      <c r="AZ6" s="37">
+        <f t="shared" si="0"/>
+        <v>352000000</v>
+      </c>
+      <c r="BA6" s="37">
+        <f t="shared" si="0"/>
+        <v>349000000</v>
+      </c>
+      <c r="BB6" s="37">
+        <f t="shared" si="0"/>
+        <v>347000000</v>
+      </c>
+      <c r="BC6" s="37">
+        <f t="shared" si="0"/>
+        <v>344000000</v>
+      </c>
+      <c r="BD6" s="37">
+        <f t="shared" si="0"/>
+        <v>342000000</v>
+      </c>
+      <c r="BE6" s="37">
+        <f t="shared" si="0"/>
+        <v>339000000</v>
+      </c>
+      <c r="BF6" s="37">
+        <f t="shared" si="0"/>
+        <v>337000000</v>
+      </c>
+      <c r="BG6" s="37">
+        <f t="shared" si="0"/>
+        <v>335000000</v>
+      </c>
+      <c r="BH6" s="37">
+        <f t="shared" si="0"/>
+        <v>333000000</v>
+      </c>
+      <c r="BI6" s="37">
+        <f t="shared" si="0"/>
+        <v>333000000</v>
+      </c>
+      <c r="BJ6" s="37">
+        <f t="shared" si="0"/>
+        <v>332000000</v>
+      </c>
+      <c r="BK6" s="37">
+        <f t="shared" si="0"/>
+        <v>332000000</v>
+      </c>
+      <c r="BL6" s="37">
+        <f t="shared" si="0"/>
+        <v>333000000</v>
+      </c>
+      <c r="BM6" s="37">
+        <f t="shared" si="0"/>
+        <v>335000000</v>
+      </c>
+      <c r="BN6" s="37">
+        <f t="shared" si="0"/>
+        <v>337000000</v>
+      </c>
+      <c r="BO6" s="37">
+        <f t="shared" ref="BO6:BS6" si="1">BO3-$B$5</f>
+        <v>339000000</v>
+      </c>
+      <c r="BP6" s="37">
         <f t="shared" si="1"/>
-        <v>-191750978.56863302</v>
-      </c>
-      <c r="E6" s="37">
+        <v>341000000</v>
+      </c>
+      <c r="BQ6" s="37">
         <f t="shared" si="1"/>
-        <v>351726366.71286404</v>
-      </c>
-      <c r="F6" s="37">
+        <v>342000000</v>
+      </c>
+      <c r="BR6" s="37">
         <f t="shared" si="1"/>
-        <v>319152482.18395102</v>
-      </c>
-      <c r="G6" s="37">
+        <v>342000000</v>
+      </c>
+      <c r="BS6" s="37">
         <f t="shared" si="1"/>
-        <v>394574573.61526</v>
-      </c>
-      <c r="H6" s="37">
-        <f t="shared" si="1"/>
-        <v>528561681.95019007</v>
-      </c>
-      <c r="I6" s="37">
-        <f t="shared" si="1"/>
-        <v>400426049.27596998</v>
-      </c>
-      <c r="J6" s="37">
-        <f t="shared" si="1"/>
-        <v>773891486.29027009</v>
-      </c>
-      <c r="K6" s="37">
-        <f t="shared" si="1"/>
-        <v>401245685.50220001</v>
-      </c>
-      <c r="L6" s="37">
-        <f t="shared" si="1"/>
-        <v>594492988.00695992</v>
-      </c>
-      <c r="M6" s="37">
-        <f t="shared" si="1"/>
-        <v>1129946112.55408</v>
-      </c>
-      <c r="N6" s="37">
-        <f t="shared" si="1"/>
-        <v>237040060.67016602</v>
-      </c>
-      <c r="O6" s="37">
-        <f t="shared" si="1"/>
-        <v>767924175.98223996</v>
-      </c>
-      <c r="P6" s="37">
-        <f t="shared" si="1"/>
-        <v>626010935.67065001</v>
-      </c>
-      <c r="Q6" s="37">
-        <f t="shared" si="1"/>
-        <v>1153724294.7464199</v>
-      </c>
-      <c r="R6" s="37">
-        <f t="shared" si="1"/>
-        <v>206226714.26742995</v>
-      </c>
-      <c r="S6" s="37">
-        <f t="shared" si="1"/>
-        <v>142612569.31596601</v>
-      </c>
-      <c r="T6" s="37">
-        <f t="shared" si="1"/>
-        <v>120282810.694085</v>
-      </c>
-      <c r="U6" s="37">
-        <f t="shared" si="1"/>
-        <v>-25858891.615738034</v>
-      </c>
-      <c r="V6" s="37">
-        <f t="shared" si="1"/>
-        <v>-107531201.09517902</v>
-      </c>
-      <c r="W6" s="37">
-        <f t="shared" si="1"/>
-        <v>-74302844.94501996</v>
-      </c>
-      <c r="X6" s="37">
-        <f t="shared" si="1"/>
-        <v>226375900.38146496</v>
-      </c>
-      <c r="Y6" s="37">
-        <f t="shared" si="1"/>
-        <v>341308472.36525762</v>
-      </c>
-      <c r="Z6" s="37">
-        <f t="shared" si="1"/>
-        <v>361795273.60575008</v>
-      </c>
-      <c r="AA6" s="37">
-        <f t="shared" si="1"/>
-        <v>377298900.76376557</v>
-      </c>
-      <c r="AB6" s="37">
-        <f t="shared" si="1"/>
-        <v>402040199.86517429</v>
-      </c>
-      <c r="AC6" s="37">
-        <f t="shared" si="1"/>
-        <v>404227757.828318</v>
-      </c>
-      <c r="AD6" s="37">
-        <f t="shared" si="1"/>
-        <v>407926682.85633421</v>
-      </c>
-      <c r="AE6" s="37">
-        <f t="shared" si="1"/>
-        <v>408507209.34507632</v>
-      </c>
-      <c r="AF6" s="37">
-        <f t="shared" si="1"/>
-        <v>403287449.66659331</v>
-      </c>
-      <c r="AG6" s="37">
-        <f t="shared" si="1"/>
-        <v>403411858.37922883</v>
-      </c>
-      <c r="AH6" s="37">
-        <f t="shared" si="1"/>
-        <v>387304048.47005332</v>
-      </c>
-      <c r="AI6" s="37">
-        <f t="shared" si="1"/>
-        <v>386697890.33822083</v>
-      </c>
-      <c r="AJ6" s="37">
-        <f t="shared" si="1"/>
-        <v>377663320.87436259</v>
-      </c>
-      <c r="AK6" s="37">
-        <f t="shared" si="1"/>
-        <v>344955373.41002703</v>
-      </c>
-      <c r="AL6" s="37">
-        <f t="shared" si="1"/>
-        <v>349647343.52915156</v>
-      </c>
-      <c r="AM6" s="37">
-        <f t="shared" si="1"/>
-        <v>331461394.29206073</v>
-      </c>
-      <c r="AN6" s="37">
-        <f t="shared" si="1"/>
-        <v>318654892.49299145</v>
-      </c>
-      <c r="AO6" s="37">
-        <f t="shared" si="1"/>
-        <v>282347527.17762494</v>
-      </c>
-      <c r="AP6" s="37">
-        <f t="shared" si="1"/>
-        <v>285657127.73893774</v>
-      </c>
-      <c r="AQ6" s="37">
-        <f t="shared" si="1"/>
-        <v>291876456.3660233</v>
-      </c>
-      <c r="AR6" s="37">
-        <f t="shared" si="1"/>
-        <v>299337049.65610766</v>
-      </c>
-      <c r="AS6" s="37">
-        <f t="shared" si="1"/>
-        <v>313476003.6244489</v>
-      </c>
-      <c r="AT6" s="37">
-        <f t="shared" si="1"/>
-        <v>331780664.69921541</v>
-      </c>
-      <c r="AU6" s="37">
-        <f t="shared" si="1"/>
-        <v>349436469.46635604</v>
-      </c>
-      <c r="AV6" s="37">
-        <f t="shared" si="1"/>
-        <v>354786928.99178624</v>
-      </c>
-      <c r="AW6" s="37">
-        <f t="shared" si="1"/>
-        <v>355372948.84511352</v>
-      </c>
-      <c r="AX6" s="37">
-        <f t="shared" si="1"/>
-        <v>355093717.33378136</v>
-      </c>
-      <c r="AY6" s="37">
-        <f t="shared" si="1"/>
-        <v>354128274.57595599</v>
-      </c>
-      <c r="AZ6" s="37">
-        <f t="shared" si="1"/>
-        <v>352045147.38946819</v>
-      </c>
-      <c r="BA6" s="37">
-        <f t="shared" si="1"/>
-        <v>349776338.23995304</v>
-      </c>
-      <c r="BB6" s="37">
-        <f t="shared" si="1"/>
-        <v>347248062.38706684</v>
-      </c>
-      <c r="BC6" s="37">
-        <f t="shared" si="1"/>
-        <v>344584621.21497941</v>
-      </c>
-      <c r="BD6" s="37">
-        <f t="shared" si="1"/>
-        <v>342032324.32577896</v>
-      </c>
-      <c r="BE6" s="37">
-        <f t="shared" si="1"/>
-        <v>339363648.93215084</v>
-      </c>
-      <c r="BF6" s="37">
-        <f t="shared" si="1"/>
-        <v>337279283.73485065</v>
-      </c>
-      <c r="BG6" s="37">
-        <f t="shared" si="1"/>
-        <v>335130648.66513896</v>
-      </c>
-      <c r="BH6" s="37">
-        <f t="shared" si="1"/>
-        <v>333281402.04734647</v>
-      </c>
-      <c r="BI6" s="37">
-        <f t="shared" si="1"/>
-        <v>332773838.0750562</v>
-      </c>
-      <c r="BJ6" s="37">
-        <f t="shared" si="1"/>
-        <v>332040207.403139</v>
-      </c>
-      <c r="BK6" s="37">
-        <f t="shared" si="1"/>
-        <v>332065373.19057691</v>
-      </c>
-      <c r="BL6" s="37">
-        <f t="shared" si="1"/>
-        <v>332648437.56873286</v>
-      </c>
-      <c r="BM6" s="37">
-        <f t="shared" si="1"/>
-        <v>334835433.67269397</v>
-      </c>
-      <c r="BN6" s="37">
-        <f t="shared" si="1"/>
-        <v>336973620.88720524</v>
-      </c>
-      <c r="BO6" s="37">
-        <f t="shared" ref="BO6:BS6" si="2">BO3-$B$5</f>
-        <v>338934367.17073488</v>
-      </c>
-      <c r="BP6" s="37">
-        <f t="shared" si="2"/>
-        <v>340655989.67137098</v>
-      </c>
-      <c r="BQ6" s="37">
-        <f t="shared" si="2"/>
-        <v>341837728.19515014</v>
-      </c>
-      <c r="BR6" s="37">
-        <f t="shared" si="2"/>
-        <v>342274991.8254081</v>
-      </c>
-      <c r="BS6" s="37">
-        <f t="shared" si="2"/>
-        <v>341963623.23232341</v>
+        <v>342000000</v>
       </c>
     </row>
     <row r="7" spans="1:75" x14ac:dyDescent="0.2">
@@ -5190,283 +6135,283 @@
       </c>
       <c r="B7" s="29">
         <f>B6*'Share of Pollutants'!$B$19</f>
-        <v>-76152966.391934305</v>
+        <v>-35764139.239890337</v>
       </c>
       <c r="C7" s="29">
         <f>C6*'Share of Pollutants'!$B$19</f>
-        <v>3055693.3165608556</v>
+        <v>-60388628.55260171</v>
       </c>
       <c r="D7" s="29">
         <f>D6*'Share of Pollutants'!$B$19</f>
-        <v>-112423093.39202981</v>
+        <v>39868220.792008899</v>
       </c>
       <c r="E7" s="29">
         <f>E6*'Share of Pollutants'!$B$19</f>
-        <v>206216241.8599934</v>
+        <v>126640230.75108708</v>
       </c>
       <c r="F7" s="29">
         <f>F6*'Share of Pollutants'!$B$19</f>
-        <v>187118259.20628595</v>
+        <v>208721861.79345834</v>
       </c>
       <c r="G7" s="29">
         <f>G6*'Share of Pollutants'!$B$19</f>
-        <v>231338032.64420521</v>
+        <v>253866758.86676252</v>
       </c>
       <c r="H7" s="29">
         <f>H6*'Share of Pollutants'!$B$19</f>
-        <v>309894321.14979059</v>
+        <v>259729732.5126462</v>
       </c>
       <c r="I7" s="29">
         <f>I6*'Share of Pollutants'!$B$19</f>
-        <v>234768737.40303242</v>
+        <v>335948389.90913379</v>
       </c>
       <c r="J7" s="29">
         <f>J6*'Share of Pollutants'!$B$19</f>
-        <v>453730538.889359</v>
+        <v>318359468.97148281</v>
       </c>
       <c r="K7" s="29">
         <f>K6*'Share of Pollutants'!$B$19</f>
-        <v>235249287.96239224</v>
+        <v>330085416.26325011</v>
       </c>
       <c r="L7" s="29">
         <f>L6*'Share of Pollutants'!$B$19</f>
-        <v>348549672.13474375</v>
+        <v>447344889.18092334</v>
       </c>
       <c r="M7" s="29">
         <f>M6*'Share of Pollutants'!$B$19</f>
-        <v>662484427.91732645</v>
+        <v>382852179.07620305</v>
       </c>
       <c r="N7" s="29">
         <f>N6*'Share of Pollutants'!$B$19</f>
-        <v>138975962.87278476</v>
+        <v>382852179.07620305</v>
       </c>
       <c r="O7" s="29">
         <f>O6*'Share of Pollutants'!$B$19</f>
-        <v>450231920.58207995</v>
+        <v>347674337.20090109</v>
       </c>
       <c r="P7" s="29">
         <f>P6*'Share of Pollutants'!$B$19</f>
-        <v>367028561.78719932</v>
+        <v>505974625.63975996</v>
       </c>
       <c r="Q7" s="29">
         <f>Q6*'Share of Pollutants'!$B$19</f>
-        <v>676425513.47139728</v>
+        <v>388715152.72208673</v>
       </c>
       <c r="R7" s="29">
         <f>R6*'Share of Pollutants'!$B$19</f>
-        <v>120910179.08271219</v>
+        <v>230414864.28322789</v>
       </c>
       <c r="S7" s="29">
         <f>S6*'Share of Pollutants'!$B$19</f>
-        <v>83613373.547126561</v>
+        <v>86772009.959078193</v>
       </c>
       <c r="T7" s="29">
         <f>T6*'Share of Pollutants'!$B$19</f>
-        <v>70521494.915223375</v>
+        <v>39281923.427420527</v>
       </c>
       <c r="U7" s="29">
         <f>U6*'Share of Pollutants'!$B$19</f>
-        <v>-15161000.005483406</v>
+        <v>-14657434.114709154</v>
       </c>
       <c r="V7" s="29">
         <f>V6*'Share of Pollutants'!$B$19</f>
-        <v>-63045259.813125089</v>
+        <v>-44558599.708715826</v>
       </c>
       <c r="W7" s="29">
         <f>W6*'Share of Pollutants'!$B$19</f>
-        <v>-43563562.172683202</v>
+        <v>21693002.489769548</v>
       </c>
       <c r="X7" s="29">
         <f>X6*'Share of Pollutants'!$B$19</f>
-        <v>132723593.79997142</v>
+        <v>119604662.37602669</v>
       </c>
       <c r="Y7" s="29">
         <f>Y6*'Share of Pollutants'!$B$19</f>
-        <v>200108257.85943174</v>
+        <v>189374048.76204225</v>
       </c>
       <c r="Z7" s="29">
         <f>Z6*'Share of Pollutants'!$B$19</f>
-        <v>212119615.43557814</v>
+        <v>212825943.34557691</v>
       </c>
       <c r="AA7" s="29">
         <f>AA6*'Share of Pollutants'!$B$19</f>
-        <v>221209351.17988324</v>
+        <v>224551890.63734421</v>
       </c>
       <c r="AB7" s="29">
         <f>AB6*'Share of Pollutants'!$B$19</f>
-        <v>235715109.63953167</v>
+        <v>230414864.28322789</v>
       </c>
       <c r="AC7" s="29">
         <f>AC6*'Share of Pollutants'!$B$19</f>
-        <v>236997669.10820714</v>
+        <v>236277837.92911154</v>
       </c>
       <c r="AD7" s="29">
         <f>AD6*'Share of Pollutants'!$B$19</f>
-        <v>239166339.10394299</v>
+        <v>236277837.92911154</v>
       </c>
       <c r="AE7" s="29">
         <f>AE6*'Share of Pollutants'!$B$19</f>
-        <v>239506700.25436622</v>
+        <v>236277837.92911154</v>
       </c>
       <c r="AF7" s="29">
         <f>AF6*'Share of Pollutants'!$B$19</f>
-        <v>236446368.91108701</v>
+        <v>236277837.92911154</v>
       </c>
       <c r="AG7" s="29">
         <f>AG6*'Share of Pollutants'!$B$19</f>
-        <v>236519309.41143703</v>
+        <v>230414864.28322789</v>
       </c>
       <c r="AH7" s="29">
         <f>AH6*'Share of Pollutants'!$B$19</f>
-        <v>227075342.91239709</v>
+        <v>230414864.28322789</v>
       </c>
       <c r="AI7" s="29">
         <f>AI6*'Share of Pollutants'!$B$19</f>
-        <v>226719953.9971799</v>
+        <v>224551890.63734421</v>
       </c>
       <c r="AJ7" s="29">
         <f>AJ6*'Share of Pollutants'!$B$19</f>
-        <v>221423009.73032928</v>
+        <v>215171132.80393037</v>
       </c>
       <c r="AK7" s="29">
         <f>AK6*'Share of Pollutants'!$B$19</f>
-        <v>202246426.33089459</v>
+        <v>207549267.06428161</v>
       </c>
       <c r="AL7" s="29">
         <f>AL6*'Share of Pollutants'!$B$19</f>
-        <v>204997316.04646468</v>
+        <v>199927401.32463285</v>
       </c>
       <c r="AM7" s="29">
         <f>AM6*'Share of Pollutants'!$B$19</f>
-        <v>194334941.9362205</v>
+        <v>194064427.67874917</v>
       </c>
       <c r="AN7" s="29">
         <f>AN6*'Share of Pollutants'!$B$19</f>
-        <v>186826523.68183002</v>
+        <v>179993290.92862839</v>
       </c>
       <c r="AO7" s="29">
         <f>AO6*'Share of Pollutants'!$B$19</f>
-        <v>165539611.08228359</v>
+        <v>171198830.4598029</v>
       </c>
       <c r="AP7" s="29">
         <f>AP6*'Share of Pollutants'!$B$19</f>
-        <v>167480021.16922146</v>
+        <v>168267343.63686109</v>
       </c>
       <c r="AQ7" s="29">
         <f>AQ6*'Share of Pollutants'!$B$19</f>
-        <v>171126397.1527907</v>
+        <v>171785127.82439128</v>
       </c>
       <c r="AR7" s="29">
         <f>AR6*'Share of Pollutants'!$B$19</f>
-        <v>175500523.33703279</v>
+        <v>177648101.47027493</v>
       </c>
       <c r="AS7" s="29">
         <f>AS6*'Share of Pollutants'!$B$19</f>
-        <v>183790154.78670749</v>
+        <v>186442561.93910041</v>
       </c>
       <c r="AT7" s="29">
         <f>AT6*'Share of Pollutants'!$B$19</f>
-        <v>194522129.33452636</v>
+        <v>196409617.13710266</v>
       </c>
       <c r="AU7" s="29">
         <f>AU6*'Share of Pollutants'!$B$19</f>
-        <v>204873681.1391876</v>
+        <v>204031482.87675142</v>
       </c>
       <c r="AV7" s="29">
         <f>AV6*'Share of Pollutants'!$B$19</f>
-        <v>208010641.45828405</v>
+        <v>207549267.06428161</v>
       </c>
       <c r="AW7" s="29">
         <f>AW6*'Share of Pollutants'!$B$19</f>
-        <v>208354223.35388631</v>
+        <v>208135564.42886996</v>
       </c>
       <c r="AX7" s="29">
         <f>AX6*'Share of Pollutants'!$B$19</f>
-        <v>208190510.65468222</v>
+        <v>208135564.42886996</v>
       </c>
       <c r="AY7" s="29">
         <f>AY6*'Share of Pollutants'!$B$19</f>
-        <v>207624474.11010829</v>
+        <v>207549267.06428161</v>
       </c>
       <c r="AZ7" s="29">
         <f>AZ6*'Share of Pollutants'!$B$19</f>
-        <v>206403142.13056812</v>
+        <v>206376672.33510488</v>
       </c>
       <c r="BA7" s="29">
         <f>BA6*'Share of Pollutants'!$B$19</f>
-        <v>205072945.30545342</v>
+        <v>204617780.24133977</v>
       </c>
       <c r="BB7" s="29">
         <f>BB6*'Share of Pollutants'!$B$19</f>
-        <v>203590623.83595383</v>
+        <v>203445185.51216304</v>
       </c>
       <c r="BC7" s="29">
         <f>BC6*'Share of Pollutants'!$B$19</f>
-        <v>202029055.29602283</v>
+        <v>201686293.41839793</v>
       </c>
       <c r="BD7" s="29">
         <f>BD6*'Share of Pollutants'!$B$19</f>
-        <v>200532650.3562375</v>
+        <v>200513698.6892212</v>
       </c>
       <c r="BE7" s="29">
         <f>BE6*'Share of Pollutants'!$B$19</f>
-        <v>198968013.00601152</v>
+        <v>198754806.59545612</v>
       </c>
       <c r="BF7" s="29">
         <f>BF6*'Share of Pollutants'!$B$19</f>
-        <v>197745955.18399471</v>
+        <v>197582211.86627939</v>
       </c>
       <c r="BG7" s="29">
         <f>BG6*'Share of Pollutants'!$B$19</f>
-        <v>196486216.10516062</v>
+        <v>196409617.13710266</v>
       </c>
       <c r="BH7" s="29">
         <f>BH6*'Share of Pollutants'!$B$19</f>
-        <v>195402007.68667492</v>
+        <v>195237022.4079259</v>
       </c>
       <c r="BI7" s="29">
         <f>BI6*'Share of Pollutants'!$B$19</f>
-        <v>195104424.26736113</v>
+        <v>195237022.4079259</v>
       </c>
       <c r="BJ7" s="29">
         <f>BJ6*'Share of Pollutants'!$B$19</f>
-        <v>194674298.53783488</v>
+        <v>194650725.04333755</v>
       </c>
       <c r="BK7" s="29">
         <f>BK6*'Share of Pollutants'!$B$19</f>
-        <v>194689053.17268753</v>
+        <v>194650725.04333755</v>
       </c>
       <c r="BL7" s="29">
         <f>BL6*'Share of Pollutants'!$B$19</f>
-        <v>195030902.28098571</v>
+        <v>195237022.4079259</v>
       </c>
       <c r="BM7" s="29">
         <f>BM6*'Share of Pollutants'!$B$19</f>
-        <v>196313132.33310315</v>
+        <v>196409617.13710266</v>
       </c>
       <c r="BN7" s="29">
         <f>BN6*'Share of Pollutants'!$B$19</f>
-        <v>197566745.86196762</v>
+        <v>197582211.86627939</v>
       </c>
       <c r="BO7" s="29">
         <f>BO6*'Share of Pollutants'!$B$19</f>
-        <v>198716326.2406275</v>
+        <v>198754806.59545612</v>
       </c>
       <c r="BP7" s="29">
         <f>BP6*'Share of Pollutants'!$B$19</f>
-        <v>199725708.97556648</v>
+        <v>199927401.32463285</v>
       </c>
       <c r="BQ7" s="29">
         <f>BQ6*'Share of Pollutants'!$B$19</f>
-        <v>200418559.15769073</v>
+        <v>200513698.6892212</v>
       </c>
       <c r="BR7" s="29">
         <f>BR6*'Share of Pollutants'!$B$19</f>
-        <v>200674925.67174134</v>
+        <v>200513698.6892212</v>
       </c>
       <c r="BS7" s="29">
         <f>BS6*'Share of Pollutants'!$B$19</f>
-        <v>200492371.08620018</v>
+        <v>200513698.6892212</v>
       </c>
     </row>
     <row r="8" spans="1:75" x14ac:dyDescent="0.2">
@@ -5475,283 +6420,283 @@
       </c>
       <c r="B8" s="29">
         <f>B6*'Share of Pollutants'!$B$20</f>
-        <v>-33007002.38424867</v>
+        <v>-15501261.278335312</v>
       </c>
       <c r="C8" s="29">
         <f>C6*'Share of Pollutants'!$B$20</f>
-        <v>1324430.0434229616</v>
+        <v>-26174260.847025201</v>
       </c>
       <c r="D8" s="29">
         <f>D6*'Share of Pollutants'!$B$20</f>
-        <v>-48727574.084735334</v>
+        <v>17280094.539783627</v>
       </c>
       <c r="E8" s="29">
         <f>E6*'Share of Pollutants'!$B$20</f>
-        <v>89380365.719601408</v>
+        <v>54889712.067547992</v>
       </c>
       <c r="F8" s="29">
         <f>F6*'Share of Pollutants'!$B$20</f>
-        <v>81102721.540371805</v>
+        <v>90466377.296514273</v>
       </c>
       <c r="G8" s="29">
         <f>G6*'Share of Pollutants'!$B$20</f>
-        <v>100268910.80980158</v>
+        <v>110033543.17244574</v>
       </c>
       <c r="H8" s="29">
         <f>H6*'Share of Pollutants'!$B$20</f>
-        <v>134317585.79715189</v>
+        <v>112574733.54594333</v>
       </c>
       <c r="I8" s="29">
         <f>I6*'Share of Pollutants'!$B$20</f>
-        <v>101755882.17177674</v>
+        <v>145610208.40141204</v>
       </c>
       <c r="J8" s="29">
         <f>J6*'Share of Pollutants'!$B$20</f>
-        <v>196660559.50925782</v>
+        <v>137986637.28091925</v>
       </c>
       <c r="K8" s="29">
         <f>K6*'Share of Pollutants'!$B$20</f>
-        <v>101964167.3405633</v>
+        <v>143069018.02791443</v>
       </c>
       <c r="L8" s="29">
         <f>L6*'Share of Pollutants'!$B$20</f>
-        <v>151071985.82351062</v>
+        <v>193892825.49786627</v>
       </c>
       <c r="M8" s="29">
         <f>M6*'Share of Pollutants'!$B$20</f>
-        <v>287140818.37934548</v>
+        <v>165939731.38939276</v>
       </c>
       <c r="N8" s="29">
         <f>N6*'Share of Pollutants'!$B$20</f>
-        <v>60236392.030831106</v>
+        <v>165939731.38939276</v>
       </c>
       <c r="O8" s="29">
         <f>O6*'Share of Pollutants'!$B$20</f>
-        <v>195144152.3582139</v>
+        <v>150692589.14840722</v>
       </c>
       <c r="P8" s="29">
         <f>P6*'Share of Pollutants'!$B$20</f>
-        <v>159081296.34304762</v>
+        <v>219304729.23284221</v>
       </c>
       <c r="Q8" s="29">
         <f>Q6*'Share of Pollutants'!$B$20</f>
-        <v>293183307.14799011</v>
+        <v>168480921.76289037</v>
       </c>
       <c r="R8" s="29">
         <f>R6*'Share of Pollutants'!$B$20</f>
-        <v>52406134.10544315</v>
+        <v>99868781.678455368</v>
       </c>
       <c r="S8" s="29">
         <f>S6*'Share of Pollutants'!$B$20</f>
-        <v>36240568.828549094</v>
+        <v>37609617.527764365</v>
       </c>
       <c r="T8" s="29">
         <f>T6*'Share of Pollutants'!$B$20</f>
-        <v>30566152.063304204</v>
+        <v>17025975.502433866</v>
       </c>
       <c r="U8" s="29">
         <f>U6*'Share of Pollutants'!$B$20</f>
-        <v>-6571236.6443231087</v>
+        <v>-6352975.9337439807</v>
       </c>
       <c r="V8" s="29">
         <f>V6*'Share of Pollutants'!$B$20</f>
-        <v>-27325725.307370268</v>
+        <v>-19313046.8385817</v>
       </c>
       <c r="W8" s="29">
         <f>W6*'Share of Pollutants'!$B$20</f>
-        <v>-18881767.429776896</v>
+        <v>9402404.3819410913</v>
       </c>
       <c r="X8" s="29">
         <f>X6*'Share of Pollutants'!$B$20</f>
-        <v>57526425.884122863</v>
+        <v>51840283.61935088</v>
       </c>
       <c r="Y8" s="29">
         <f>Y6*'Share of Pollutants'!$B$20</f>
-        <v>86732980.436776161</v>
+        <v>82080449.06397222</v>
       </c>
       <c r="Z8" s="29">
         <f>Z6*'Share of Pollutants'!$B$20</f>
-        <v>91939066.646385953</v>
+        <v>92245210.557962596</v>
       </c>
       <c r="AA8" s="29">
         <f>AA6*'Share of Pollutants'!$B$20</f>
-        <v>95878833.455210432</v>
+        <v>97327591.304957777</v>
       </c>
       <c r="AB8" s="29">
         <f>AB6*'Share of Pollutants'!$B$20</f>
-        <v>102166068.56564288</v>
+        <v>99868781.678455368</v>
       </c>
       <c r="AC8" s="29">
         <f>AC6*'Share of Pollutants'!$B$20</f>
-        <v>102721968.68938376</v>
+        <v>102409972.05195296</v>
       </c>
       <c r="AD8" s="29">
         <f>AD6*'Share of Pollutants'!$B$20</f>
-        <v>103661935.95673217</v>
+        <v>102409972.05195296</v>
       </c>
       <c r="AE8" s="29">
         <f>AE6*'Share of Pollutants'!$B$20</f>
-        <v>103809458.78920735</v>
+        <v>102409972.05195296</v>
       </c>
       <c r="AF8" s="29">
         <f>AF6*'Share of Pollutants'!$B$20</f>
-        <v>102483018.48451416</v>
+        <v>102409972.05195296</v>
       </c>
       <c r="AG8" s="29">
         <f>AG6*'Share of Pollutants'!$B$20</f>
-        <v>102514633.10680702</v>
+        <v>99868781.678455368</v>
       </c>
       <c r="AH8" s="29">
         <f>AH6*'Share of Pollutants'!$B$20</f>
-        <v>98421331.958874434</v>
+        <v>99868781.678455368</v>
       </c>
       <c r="AI8" s="29">
         <f>AI6*'Share of Pollutants'!$B$20</f>
-        <v>98267295.637931436</v>
+        <v>97327591.304957777</v>
       </c>
       <c r="AJ8" s="29">
         <f>AJ6*'Share of Pollutants'!$B$20</f>
-        <v>95971439.54290624</v>
+        <v>93261686.707361639</v>
       </c>
       <c r="AK8" s="29">
         <f>AK6*'Share of Pollutants'!$B$20</f>
-        <v>87659727.419582799</v>
+        <v>89958139.221814767</v>
       </c>
       <c r="AL8" s="29">
         <f>AL6*'Share of Pollutants'!$B$20</f>
-        <v>88852046.349528551</v>
+        <v>86654591.736267895</v>
       </c>
       <c r="AM8" s="29">
         <f>AM6*'Share of Pollutants'!$B$20</f>
-        <v>84230650.436107442</v>
+        <v>84113401.362770304</v>
       </c>
       <c r="AN8" s="29">
         <f>AN6*'Share of Pollutants'!$B$20</f>
-        <v>80976274.527109995</v>
+        <v>78014544.466376081</v>
       </c>
       <c r="AO8" s="29">
         <f>AO6*'Share of Pollutants'!$B$20</f>
-        <v>71749881.804463029</v>
+        <v>74202758.906129688</v>
       </c>
       <c r="AP8" s="29">
         <f>AP6*'Share of Pollutants'!$B$20</f>
-        <v>72590914.313116059</v>
+        <v>72932163.7193809</v>
       </c>
       <c r="AQ8" s="29">
         <f>AQ6*'Share of Pollutants'!$B$20</f>
-        <v>74171364.116792843</v>
+        <v>74456877.943479449</v>
       </c>
       <c r="AR8" s="29">
         <f>AR6*'Share of Pollutants'!$B$20</f>
-        <v>76067242.901727155</v>
+        <v>76998068.316977039</v>
       </c>
       <c r="AS8" s="29">
         <f>AS6*'Share of Pollutants'!$B$20</f>
-        <v>79660220.273294583</v>
+        <v>80809853.877223432</v>
       </c>
       <c r="AT8" s="29">
         <f>AT6*'Share of Pollutants'!$B$20</f>
-        <v>84311783.124627858</v>
+        <v>85129877.512169331</v>
       </c>
       <c r="AU8" s="29">
         <f>AU6*'Share of Pollutants'!$B$20</f>
-        <v>88798459.235688925</v>
+        <v>88433424.997716203</v>
       </c>
       <c r="AV8" s="29">
         <f>AV6*'Share of Pollutants'!$B$20</f>
-        <v>90158112.859670103</v>
+        <v>89958139.221814767</v>
       </c>
       <c r="AW8" s="29">
         <f>AW6*'Share of Pollutants'!$B$20</f>
-        <v>90307031.660665467</v>
+        <v>90212258.259164527</v>
       </c>
       <c r="AX8" s="29">
         <f>AX6*'Share of Pollutants'!$B$20</f>
-        <v>90236073.617808029</v>
+        <v>90212258.259164527</v>
       </c>
       <c r="AY8" s="29">
         <f>AY6*'Share of Pollutants'!$B$20</f>
-        <v>89990736.233573139</v>
+        <v>89958139.221814767</v>
       </c>
       <c r="AZ8" s="29">
         <f>AZ6*'Share of Pollutants'!$B$20</f>
-        <v>89461373.958265752</v>
+        <v>89449901.147115245</v>
       </c>
       <c r="BA8" s="29">
         <f>BA6*'Share of Pollutants'!$B$20</f>
-        <v>88884826.361260638</v>
+        <v>88687544.035065964</v>
       </c>
       <c r="BB8" s="29">
         <f>BB6*'Share of Pollutants'!$B$20</f>
-        <v>88242343.335370556</v>
+        <v>88179305.960366443</v>
       </c>
       <c r="BC8" s="29">
         <f>BC6*'Share of Pollutants'!$B$20</f>
-        <v>87565512.228681982</v>
+        <v>87416948.848317176</v>
       </c>
       <c r="BD8" s="29">
         <f>BD6*'Share of Pollutants'!$B$20</f>
-        <v>86916925.000167578</v>
+        <v>86908710.773617655</v>
       </c>
       <c r="BE8" s="29">
         <f>BE6*'Share of Pollutants'!$B$20</f>
-        <v>86238763.778139815</v>
+        <v>86146353.661568373</v>
       </c>
       <c r="BF8" s="29">
         <f>BF6*'Share of Pollutants'!$B$20</f>
-        <v>85709086.900716543</v>
+        <v>85638115.586868852</v>
       </c>
       <c r="BG8" s="29">
         <f>BG6*'Share of Pollutants'!$B$20</f>
-        <v>85163077.825185478</v>
+        <v>85129877.512169331</v>
       </c>
       <c r="BH8" s="29">
         <f>BH6*'Share of Pollutants'!$B$20</f>
-        <v>84693149.054849759</v>
+        <v>84621639.437469825</v>
       </c>
       <c r="BI8" s="29">
         <f>BI6*'Share of Pollutants'!$B$20</f>
-        <v>84564167.386817932</v>
+        <v>84621639.437469825</v>
       </c>
       <c r="BJ8" s="29">
         <f>BJ6*'Share of Pollutants'!$B$20</f>
-        <v>84377737.866700068</v>
+        <v>84367520.400120065</v>
       </c>
       <c r="BK8" s="29">
         <f>BK6*'Share of Pollutants'!$B$20</f>
-        <v>84384132.972377941</v>
+        <v>84367520.400120065</v>
       </c>
       <c r="BL8" s="29">
         <f>BL6*'Share of Pollutants'!$B$20</f>
-        <v>84532300.730867878</v>
+        <v>84621639.437469825</v>
       </c>
       <c r="BM8" s="29">
         <f>BM6*'Share of Pollutants'!$B$20</f>
-        <v>85088058.07549414</v>
+        <v>85129877.512169331</v>
       </c>
       <c r="BN8" s="29">
         <f>BN6*'Share of Pollutants'!$B$20</f>
-        <v>85631412.152119309</v>
+        <v>85638115.586868852</v>
       </c>
       <c r="BO8" s="29">
         <f>BO6*'Share of Pollutants'!$B$20</f>
-        <v>86129675.11017698</v>
+        <v>86146353.661568373</v>
       </c>
       <c r="BP8" s="29">
         <f>BP6*'Share of Pollutants'!$B$20</f>
-        <v>86567172.162718311</v>
+        <v>86654591.736267895</v>
       </c>
       <c r="BQ8" s="29">
         <f>BQ6*'Share of Pollutants'!$B$20</f>
-        <v>86867474.418780193</v>
+        <v>86908710.773617655</v>
       </c>
       <c r="BR8" s="29">
         <f>BR6*'Share of Pollutants'!$B$20</f>
-        <v>86978591.431569412</v>
+        <v>86908710.773617655</v>
       </c>
       <c r="BS8" s="29">
         <f>BS6*'Share of Pollutants'!$B$20</f>
-        <v>86899466.744433776</v>
+        <v>86908710.773617655</v>
       </c>
     </row>
     <row r="9" spans="1:75" x14ac:dyDescent="0.2">
@@ -5760,283 +6705,283 @@
       </c>
       <c r="B9" s="29">
         <f>B6*'Share of Pollutants'!$B$21</f>
-        <v>-20727987.389884025</v>
+        <v>-9734599.4817743506</v>
       </c>
       <c r="C9" s="29">
         <f>C6*'Share of Pollutants'!$B$21</f>
-        <v>831725.61141012562</v>
+        <v>-16437110.600373086</v>
       </c>
       <c r="D9" s="29">
         <f>D6*'Share of Pollutants'!$B$21</f>
-        <v>-30600311.091867864</v>
+        <v>10851684.668207474</v>
       </c>
       <c r="E9" s="29">
         <f>E6*'Share of Pollutants'!$B$21</f>
-        <v>56129759.133269206</v>
+        <v>34470057.181364916</v>
       </c>
       <c r="F9" s="29">
         <f>F6*'Share of Pollutants'!$B$21</f>
-        <v>50931501.437293239</v>
+        <v>56811760.910027362</v>
       </c>
       <c r="G9" s="29">
         <f>G6*'Share of Pollutants'!$B$21</f>
-        <v>62967630.161253206</v>
+        <v>69099697.960791707</v>
       </c>
       <c r="H9" s="29">
         <f>H6*'Share of Pollutants'!$B$21</f>
-        <v>84349775.003247529</v>
+        <v>70695533.941410452</v>
       </c>
       <c r="I9" s="29">
         <f>I6*'Share of Pollutants'!$B$21</f>
-        <v>63901429.701160789</v>
+        <v>91441401.689454153</v>
       </c>
       <c r="J9" s="29">
         <f>J6*'Share of Pollutants'!$B$21</f>
-        <v>123500387.89165321</v>
+        <v>86653893.747597918</v>
       </c>
       <c r="K9" s="29">
         <f>K6*'Share of Pollutants'!$B$21</f>
-        <v>64032230.199244432</v>
+        <v>89845565.708835408</v>
       </c>
       <c r="L9" s="29">
         <f>L6*'Share of Pollutants'!$B$21</f>
-        <v>94871330.048705533</v>
+        <v>121762285.32121032</v>
       </c>
       <c r="M9" s="29">
         <f>M6*'Share of Pollutants'!$B$21</f>
-        <v>180320866.25740802</v>
+        <v>104208089.53440411</v>
       </c>
       <c r="N9" s="29">
         <f>N6*'Share of Pollutants'!$B$21</f>
-        <v>37827705.766550146</v>
+        <v>104208089.53440411</v>
       </c>
       <c r="O9" s="29">
         <f>O6*'Share of Pollutants'!$B$21</f>
-        <v>122548103.04194604</v>
+        <v>94633073.650691643</v>
       </c>
       <c r="P9" s="29">
         <f>P6*'Share of Pollutants'!$B$21</f>
-        <v>99901077.540403053</v>
+        <v>137720645.12739778</v>
       </c>
       <c r="Q9" s="29">
         <f>Q6*'Share of Pollutants'!$B$21</f>
-        <v>184115474.12703243</v>
+        <v>105803925.51502286</v>
       </c>
       <c r="R9" s="29">
         <f>R6*'Share of Pollutants'!$B$21</f>
-        <v>32910401.079274602</v>
+        <v>62716354.038316719</v>
       </c>
       <c r="S9" s="29">
         <f>S6*'Share of Pollutants'!$B$21</f>
-        <v>22758626.94029035</v>
+        <v>23618372.513157442</v>
       </c>
       <c r="T9" s="29">
         <f>T6*'Share of Pollutants'!$B$21</f>
-        <v>19195163.715557415</v>
+        <v>10692101.0701456</v>
       </c>
       <c r="U9" s="29">
         <f>U6*'Share of Pollutants'!$B$21</f>
-        <v>-4126654.9659315175</v>
+        <v>-3989589.951546865</v>
       </c>
       <c r="V9" s="29">
         <f>V6*'Share of Pollutants'!$B$21</f>
-        <v>-17160215.974683661</v>
+        <v>-12128353.45270247</v>
       </c>
       <c r="W9" s="29">
         <f>W6*'Share of Pollutants'!$B$21</f>
-        <v>-11857515.342559857</v>
+        <v>5904593.1282893606</v>
       </c>
       <c r="X9" s="29">
         <f>X6*'Share of Pollutants'!$B$21</f>
-        <v>36125880.697370671</v>
+        <v>32555054.004622422</v>
       </c>
       <c r="Y9" s="29">
         <f>Y6*'Share of Pollutants'!$B$21</f>
-        <v>54467234.069049709</v>
+        <v>51545502.173985496</v>
       </c>
       <c r="Z9" s="29">
         <f>Z6*'Share of Pollutants'!$B$21</f>
-        <v>57736591.523785971</v>
+        <v>57928846.096460484</v>
       </c>
       <c r="AA9" s="29">
         <f>AA6*'Share of Pollutants'!$B$21</f>
-        <v>60210716.128671877</v>
+        <v>61120518.057697974</v>
       </c>
       <c r="AB9" s="29">
         <f>AB6*'Share of Pollutants'!$B$21</f>
-        <v>64159021.659999706</v>
+        <v>62716354.038316719</v>
       </c>
       <c r="AC9" s="29">
         <f>AC6*'Share of Pollutants'!$B$21</f>
-        <v>64508120.030727088</v>
+        <v>64312190.018935464</v>
       </c>
       <c r="AD9" s="29">
         <f>AD6*'Share of Pollutants'!$B$21</f>
-        <v>65098407.795659035</v>
+        <v>64312190.018935464</v>
       </c>
       <c r="AE9" s="29">
         <f>AE6*'Share of Pollutants'!$B$21</f>
-        <v>65191050.301502727</v>
+        <v>64312190.018935464</v>
       </c>
       <c r="AF9" s="29">
         <f>AF6*'Share of Pollutants'!$B$21</f>
-        <v>64358062.270992115</v>
+        <v>64312190.018935464</v>
       </c>
       <c r="AG9" s="29">
         <f>AG6*'Share of Pollutants'!$B$21</f>
-        <v>64377915.860984735</v>
+        <v>62716354.038316719</v>
       </c>
       <c r="AH9" s="29">
         <f>AH6*'Share of Pollutants'!$B$21</f>
-        <v>61807373.598781787</v>
+        <v>62716354.038316719</v>
       </c>
       <c r="AI9" s="29">
         <f>AI6*'Share of Pollutants'!$B$21</f>
-        <v>61710640.703109495</v>
+        <v>61120518.057697974</v>
       </c>
       <c r="AJ9" s="29">
         <f>AJ6*'Share of Pollutants'!$B$21</f>
-        <v>60268871.601127058</v>
+        <v>58567180.488707982</v>
       </c>
       <c r="AK9" s="29">
         <f>AK6*'Share of Pollutants'!$B$21</f>
-        <v>55049219.659549624</v>
+        <v>56492593.713903613</v>
       </c>
       <c r="AL9" s="29">
         <f>AL6*'Share of Pollutants'!$B$21</f>
-        <v>55797981.133158319</v>
+        <v>54418006.939099245</v>
       </c>
       <c r="AM9" s="29">
         <f>AM6*'Share of Pollutants'!$B$21</f>
-        <v>52895801.919732757</v>
+        <v>52822170.958480492</v>
       </c>
       <c r="AN9" s="29">
         <f>AN6*'Share of Pollutants'!$B$21</f>
-        <v>50852094.284051411</v>
+        <v>48992164.604995504</v>
       </c>
       <c r="AO9" s="29">
         <f>AO6*'Share of Pollutants'!$B$21</f>
-        <v>45058034.290878318</v>
+        <v>46598410.634067386</v>
       </c>
       <c r="AP9" s="29">
         <f>AP6*'Share of Pollutants'!$B$21</f>
-        <v>45586192.256600209</v>
+        <v>45800492.643758014</v>
       </c>
       <c r="AQ9" s="29">
         <f>AQ6*'Share of Pollutants'!$B$21</f>
-        <v>46578695.096439749</v>
+        <v>46757994.232129261</v>
       </c>
       <c r="AR9" s="29">
         <f>AR6*'Share of Pollutants'!$B$21</f>
-        <v>47769283.417347685</v>
+        <v>48353830.212748006</v>
       </c>
       <c r="AS9" s="29">
         <f>AS6*'Share of Pollutants'!$B$21</f>
-        <v>50025628.564446799</v>
+        <v>50747584.183676124</v>
       </c>
       <c r="AT9" s="29">
         <f>AT6*'Share of Pollutants'!$B$21</f>
-        <v>52946752.240061179</v>
+        <v>53460505.350727998</v>
       </c>
       <c r="AU9" s="29">
         <f>AU6*'Share of Pollutants'!$B$21</f>
-        <v>55764329.09147948</v>
+        <v>55535092.125532366</v>
       </c>
       <c r="AV9" s="29">
         <f>AV6*'Share of Pollutants'!$B$21</f>
-        <v>56618174.673832066</v>
+        <v>56492593.713903613</v>
       </c>
       <c r="AW9" s="29">
         <f>AW6*'Share of Pollutants'!$B$21</f>
-        <v>56711693.83056172</v>
+        <v>56652177.311965488</v>
       </c>
       <c r="AX9" s="29">
         <f>AX6*'Share of Pollutants'!$B$21</f>
-        <v>56667133.061291084</v>
+        <v>56652177.311965488</v>
       </c>
       <c r="AY9" s="29">
         <f>AY6*'Share of Pollutants'!$B$21</f>
-        <v>56513064.232274532</v>
+        <v>56492593.713903613</v>
       </c>
       <c r="AZ9" s="29">
         <f>AZ6*'Share of Pollutants'!$B$21</f>
-        <v>56180631.300634295</v>
+        <v>56173426.517779864</v>
       </c>
       <c r="BA9" s="29">
         <f>BA6*'Share of Pollutants'!$B$21</f>
-        <v>55818566.573238969</v>
+        <v>55694675.723594241</v>
       </c>
       <c r="BB9" s="29">
         <f>BB6*'Share of Pollutants'!$B$21</f>
-        <v>55415095.215742432</v>
+        <v>55375508.527470492</v>
       </c>
       <c r="BC9" s="29">
         <f>BC6*'Share of Pollutants'!$B$21</f>
-        <v>54990053.690274581</v>
+        <v>54896757.733284868</v>
       </c>
       <c r="BD9" s="29">
         <f>BD6*'Share of Pollutants'!$B$21</f>
-        <v>54582748.969373845</v>
+        <v>54577590.537161119</v>
       </c>
       <c r="BE9" s="29">
         <f>BE6*'Share of Pollutants'!$B$21</f>
-        <v>54156872.14799948</v>
+        <v>54098839.742975496</v>
       </c>
       <c r="BF9" s="29">
         <f>BF6*'Share of Pollutants'!$B$21</f>
-        <v>53824241.650139369</v>
+        <v>53779672.546851747</v>
       </c>
       <c r="BG9" s="29">
         <f>BG6*'Share of Pollutants'!$B$21</f>
-        <v>53481354.734792851</v>
+        <v>53460505.350727998</v>
       </c>
       <c r="BH9" s="29">
         <f>BH6*'Share of Pollutants'!$B$21</f>
-        <v>53186245.305821776</v>
+        <v>53141338.154604249</v>
       </c>
       <c r="BI9" s="29">
         <f>BI6*'Share of Pollutants'!$B$21</f>
-        <v>53105246.420877114</v>
+        <v>53141338.154604249</v>
       </c>
       <c r="BJ9" s="29">
         <f>BJ6*'Share of Pollutants'!$B$21</f>
-        <v>52988170.998604015</v>
+        <v>52981754.556542367</v>
       </c>
       <c r="BK9" s="29">
         <f>BK6*'Share of Pollutants'!$B$21</f>
-        <v>52992187.045511417</v>
+        <v>52981754.556542367</v>
       </c>
       <c r="BL9" s="29">
         <f>BL6*'Share of Pollutants'!$B$21</f>
-        <v>53085234.556879252</v>
+        <v>53141338.154604249</v>
       </c>
       <c r="BM9" s="29">
         <f>BM6*'Share of Pollutants'!$B$21</f>
-        <v>53434243.26409667</v>
+        <v>53460505.350727998</v>
       </c>
       <c r="BN9" s="29">
         <f>BN6*'Share of Pollutants'!$B$21</f>
-        <v>53775462.873118274</v>
+        <v>53779672.546851747</v>
       </c>
       <c r="BO9" s="29">
         <f>BO6*'Share of Pollutants'!$B$21</f>
-        <v>54088365.819930382</v>
+        <v>54098839.742975496</v>
       </c>
       <c r="BP9" s="29">
         <f>BP6*'Share of Pollutants'!$B$21</f>
-        <v>54363108.533086173</v>
+        <v>54418006.939099245</v>
       </c>
       <c r="BQ9" s="29">
         <f>BQ6*'Share of Pollutants'!$B$21</f>
-        <v>54551694.618679181</v>
+        <v>54577590.537161119</v>
       </c>
       <c r="BR9" s="29">
         <f>BR6*'Share of Pollutants'!$B$21</f>
-        <v>54621474.722097345</v>
+        <v>54577590.537161119</v>
       </c>
       <c r="BS9" s="29">
         <f>BS6*'Share of Pollutants'!$B$21</f>
-        <v>54571785.401689425</v>
+        <v>54577590.537161119</v>
       </c>
     </row>
     <row r="10" spans="1:75" x14ac:dyDescent="0.2">
@@ -6268,283 +7213,283 @@
       </c>
       <c r="B13" s="29">
         <f>B7*$B$10</f>
-        <v>-76152966391934.312</v>
+        <v>-35764139239890.336</v>
       </c>
       <c r="C13" s="29">
-        <f t="shared" ref="C13:BN14" si="3">C7*$B$10</f>
-        <v>3055693316560.8555</v>
+        <f t="shared" ref="C13:BN14" si="2">C7*$B$10</f>
+        <v>-60388628552601.711</v>
       </c>
       <c r="D13" s="29">
+        <f t="shared" si="2"/>
+        <v>39868220792008.898</v>
+      </c>
+      <c r="E13" s="29">
+        <f t="shared" si="2"/>
+        <v>126640230751087.08</v>
+      </c>
+      <c r="F13" s="29">
+        <f t="shared" si="2"/>
+        <v>208721861793458.34</v>
+      </c>
+      <c r="G13" s="29">
+        <f t="shared" si="2"/>
+        <v>253866758866762.53</v>
+      </c>
+      <c r="H13" s="29">
+        <f t="shared" si="2"/>
+        <v>259729732512646.19</v>
+      </c>
+      <c r="I13" s="29">
+        <f t="shared" si="2"/>
+        <v>335948389909133.81</v>
+      </c>
+      <c r="J13" s="29">
+        <f t="shared" si="2"/>
+        <v>318359468971482.81</v>
+      </c>
+      <c r="K13" s="29">
+        <f t="shared" si="2"/>
+        <v>330085416263250.12</v>
+      </c>
+      <c r="L13" s="29">
+        <f t="shared" si="2"/>
+        <v>447344889180923.31</v>
+      </c>
+      <c r="M13" s="29">
+        <f t="shared" si="2"/>
+        <v>382852179076203.06</v>
+      </c>
+      <c r="N13" s="29">
+        <f t="shared" si="2"/>
+        <v>382852179076203.06</v>
+      </c>
+      <c r="O13" s="29">
+        <f t="shared" si="2"/>
+        <v>347674337200901.06</v>
+      </c>
+      <c r="P13" s="29">
+        <f t="shared" si="2"/>
+        <v>505974625639759.94</v>
+      </c>
+      <c r="Q13" s="29">
+        <f t="shared" si="2"/>
+        <v>388715152722086.75</v>
+      </c>
+      <c r="R13" s="29">
+        <f t="shared" si="2"/>
+        <v>230414864283227.91</v>
+      </c>
+      <c r="S13" s="29">
+        <f t="shared" si="2"/>
+        <v>86772009959078.188</v>
+      </c>
+      <c r="T13" s="29">
+        <f t="shared" si="2"/>
+        <v>39281923427420.523</v>
+      </c>
+      <c r="U13" s="29">
+        <f t="shared" si="2"/>
+        <v>-14657434114709.154</v>
+      </c>
+      <c r="V13" s="29">
+        <f t="shared" si="2"/>
+        <v>-44558599708715.828</v>
+      </c>
+      <c r="W13" s="29">
+        <f t="shared" si="2"/>
+        <v>21693002489769.547</v>
+      </c>
+      <c r="X13" s="29">
+        <f t="shared" si="2"/>
+        <v>119604662376026.69</v>
+      </c>
+      <c r="Y13" s="29">
+        <f t="shared" si="2"/>
+        <v>189374048762042.25</v>
+      </c>
+      <c r="Z13" s="29">
+        <f t="shared" si="2"/>
+        <v>212825943345576.91</v>
+      </c>
+      <c r="AA13" s="29">
+        <f t="shared" si="2"/>
+        <v>224551890637344.22</v>
+      </c>
+      <c r="AB13" s="29">
+        <f t="shared" si="2"/>
+        <v>230414864283227.91</v>
+      </c>
+      <c r="AC13" s="29">
+        <f t="shared" si="2"/>
+        <v>236277837929111.53</v>
+      </c>
+      <c r="AD13" s="29">
+        <f t="shared" si="2"/>
+        <v>236277837929111.53</v>
+      </c>
+      <c r="AE13" s="29">
+        <f t="shared" si="2"/>
+        <v>236277837929111.53</v>
+      </c>
+      <c r="AF13" s="29">
+        <f t="shared" si="2"/>
+        <v>236277837929111.53</v>
+      </c>
+      <c r="AG13" s="29">
+        <f t="shared" si="2"/>
+        <v>230414864283227.91</v>
+      </c>
+      <c r="AH13" s="29">
+        <f t="shared" si="2"/>
+        <v>230414864283227.91</v>
+      </c>
+      <c r="AI13" s="29">
+        <f t="shared" si="2"/>
+        <v>224551890637344.22</v>
+      </c>
+      <c r="AJ13" s="29">
+        <f t="shared" si="2"/>
+        <v>215171132803930.38</v>
+      </c>
+      <c r="AK13" s="29">
+        <f t="shared" si="2"/>
+        <v>207549267064281.62</v>
+      </c>
+      <c r="AL13" s="29">
+        <f t="shared" si="2"/>
+        <v>199927401324632.84</v>
+      </c>
+      <c r="AM13" s="29">
+        <f t="shared" si="2"/>
+        <v>194064427678749.19</v>
+      </c>
+      <c r="AN13" s="29">
+        <f t="shared" si="2"/>
+        <v>179993290928628.38</v>
+      </c>
+      <c r="AO13" s="29">
+        <f t="shared" si="2"/>
+        <v>171198830459802.91</v>
+      </c>
+      <c r="AP13" s="29">
+        <f t="shared" si="2"/>
+        <v>168267343636861.09</v>
+      </c>
+      <c r="AQ13" s="29">
+        <f t="shared" si="2"/>
+        <v>171785127824391.28</v>
+      </c>
+      <c r="AR13" s="29">
+        <f t="shared" si="2"/>
+        <v>177648101470274.94</v>
+      </c>
+      <c r="AS13" s="29">
+        <f t="shared" si="2"/>
+        <v>186442561939100.41</v>
+      </c>
+      <c r="AT13" s="29">
+        <f t="shared" si="2"/>
+        <v>196409617137102.66</v>
+      </c>
+      <c r="AU13" s="29">
+        <f t="shared" si="2"/>
+        <v>204031482876751.44</v>
+      </c>
+      <c r="AV13" s="29">
+        <f t="shared" si="2"/>
+        <v>207549267064281.62</v>
+      </c>
+      <c r="AW13" s="29">
+        <f t="shared" si="2"/>
+        <v>208135564428869.97</v>
+      </c>
+      <c r="AX13" s="29">
+        <f t="shared" si="2"/>
+        <v>208135564428869.97</v>
+      </c>
+      <c r="AY13" s="29">
+        <f t="shared" si="2"/>
+        <v>207549267064281.62</v>
+      </c>
+      <c r="AZ13" s="29">
+        <f t="shared" si="2"/>
+        <v>206376672335104.88</v>
+      </c>
+      <c r="BA13" s="29">
+        <f t="shared" si="2"/>
+        <v>204617780241339.78</v>
+      </c>
+      <c r="BB13" s="29">
+        <f t="shared" si="2"/>
+        <v>203445185512163.03</v>
+      </c>
+      <c r="BC13" s="29">
+        <f t="shared" si="2"/>
+        <v>201686293418397.94</v>
+      </c>
+      <c r="BD13" s="29">
+        <f t="shared" si="2"/>
+        <v>200513698689221.22</v>
+      </c>
+      <c r="BE13" s="29">
+        <f t="shared" si="2"/>
+        <v>198754806595456.12</v>
+      </c>
+      <c r="BF13" s="29">
+        <f t="shared" si="2"/>
+        <v>197582211866279.41</v>
+      </c>
+      <c r="BG13" s="29">
+        <f t="shared" si="2"/>
+        <v>196409617137102.66</v>
+      </c>
+      <c r="BH13" s="29">
+        <f t="shared" si="2"/>
+        <v>195237022407925.91</v>
+      </c>
+      <c r="BI13" s="29">
+        <f t="shared" si="2"/>
+        <v>195237022407925.91</v>
+      </c>
+      <c r="BJ13" s="29">
+        <f t="shared" si="2"/>
+        <v>194650725043337.56</v>
+      </c>
+      <c r="BK13" s="29">
+        <f t="shared" si="2"/>
+        <v>194650725043337.56</v>
+      </c>
+      <c r="BL13" s="29">
+        <f t="shared" si="2"/>
+        <v>195237022407925.91</v>
+      </c>
+      <c r="BM13" s="29">
+        <f t="shared" si="2"/>
+        <v>196409617137102.66</v>
+      </c>
+      <c r="BN13" s="29">
+        <f t="shared" si="2"/>
+        <v>197582211866279.41</v>
+      </c>
+      <c r="BO13" s="29">
+        <f t="shared" ref="BO13:BS15" si="3">BO7*$B$10</f>
+        <v>198754806595456.12</v>
+      </c>
+      <c r="BP13" s="29">
         <f t="shared" si="3"/>
-        <v>-112423093392029.81</v>
-      </c>
-      <c r="E13" s="29">
+        <v>199927401324632.84</v>
+      </c>
+      <c r="BQ13" s="29">
         <f t="shared" si="3"/>
-        <v>206216241859993.41</v>
-      </c>
-      <c r="F13" s="29">
+        <v>200513698689221.22</v>
+      </c>
+      <c r="BR13" s="29">
         <f t="shared" si="3"/>
-        <v>187118259206285.97</v>
-      </c>
-      <c r="G13" s="29">
+        <v>200513698689221.22</v>
+      </c>
+      <c r="BS13" s="29">
         <f t="shared" si="3"/>
-        <v>231338032644205.22</v>
-      </c>
-      <c r="H13" s="29">
-        <f t="shared" si="3"/>
-        <v>309894321149790.56</v>
-      </c>
-      <c r="I13" s="29">
-        <f t="shared" si="3"/>
-        <v>234768737403032.44</v>
-      </c>
-      <c r="J13" s="29">
-        <f t="shared" si="3"/>
-        <v>453730538889359</v>
-      </c>
-      <c r="K13" s="29">
-        <f t="shared" si="3"/>
-        <v>235249287962392.25</v>
-      </c>
-      <c r="L13" s="29">
-        <f t="shared" si="3"/>
-        <v>348549672134743.75</v>
-      </c>
-      <c r="M13" s="29">
-        <f t="shared" si="3"/>
-        <v>662484427917326.5</v>
-      </c>
-      <c r="N13" s="29">
-        <f t="shared" si="3"/>
-        <v>138975962872784.77</v>
-      </c>
-      <c r="O13" s="29">
-        <f t="shared" si="3"/>
-        <v>450231920582079.94</v>
-      </c>
-      <c r="P13" s="29">
-        <f t="shared" si="3"/>
-        <v>367028561787199.31</v>
-      </c>
-      <c r="Q13" s="29">
-        <f t="shared" si="3"/>
-        <v>676425513471397.25</v>
-      </c>
-      <c r="R13" s="29">
-        <f t="shared" si="3"/>
-        <v>120910179082712.19</v>
-      </c>
-      <c r="S13" s="29">
-        <f t="shared" si="3"/>
-        <v>83613373547126.562</v>
-      </c>
-      <c r="T13" s="29">
-        <f t="shared" si="3"/>
-        <v>70521494915223.375</v>
-      </c>
-      <c r="U13" s="29">
-        <f t="shared" si="3"/>
-        <v>-15161000005483.406</v>
-      </c>
-      <c r="V13" s="29">
-        <f t="shared" si="3"/>
-        <v>-63045259813125.086</v>
-      </c>
-      <c r="W13" s="29">
-        <f t="shared" si="3"/>
-        <v>-43563562172683.203</v>
-      </c>
-      <c r="X13" s="29">
-        <f t="shared" si="3"/>
-        <v>132723593799971.42</v>
-      </c>
-      <c r="Y13" s="29">
-        <f t="shared" si="3"/>
-        <v>200108257859431.75</v>
-      </c>
-      <c r="Z13" s="29">
-        <f t="shared" si="3"/>
-        <v>212119615435578.12</v>
-      </c>
-      <c r="AA13" s="29">
-        <f t="shared" si="3"/>
-        <v>221209351179883.25</v>
-      </c>
-      <c r="AB13" s="29">
-        <f t="shared" si="3"/>
-        <v>235715109639531.69</v>
-      </c>
-      <c r="AC13" s="29">
-        <f t="shared" si="3"/>
-        <v>236997669108207.12</v>
-      </c>
-      <c r="AD13" s="29">
-        <f t="shared" si="3"/>
-        <v>239166339103943</v>
-      </c>
-      <c r="AE13" s="29">
-        <f t="shared" si="3"/>
-        <v>239506700254366.22</v>
-      </c>
-      <c r="AF13" s="29">
-        <f t="shared" si="3"/>
-        <v>236446368911087</v>
-      </c>
-      <c r="AG13" s="29">
-        <f t="shared" si="3"/>
-        <v>236519309411437.03</v>
-      </c>
-      <c r="AH13" s="29">
-        <f t="shared" si="3"/>
-        <v>227075342912397.09</v>
-      </c>
-      <c r="AI13" s="29">
-        <f t="shared" si="3"/>
-        <v>226719953997179.91</v>
-      </c>
-      <c r="AJ13" s="29">
-        <f t="shared" si="3"/>
-        <v>221423009730329.28</v>
-      </c>
-      <c r="AK13" s="29">
-        <f t="shared" si="3"/>
-        <v>202246426330894.59</v>
-      </c>
-      <c r="AL13" s="29">
-        <f t="shared" si="3"/>
-        <v>204997316046464.69</v>
-      </c>
-      <c r="AM13" s="29">
-        <f t="shared" si="3"/>
-        <v>194334941936220.5</v>
-      </c>
-      <c r="AN13" s="29">
-        <f t="shared" si="3"/>
-        <v>186826523681830.03</v>
-      </c>
-      <c r="AO13" s="29">
-        <f t="shared" si="3"/>
-        <v>165539611082283.59</v>
-      </c>
-      <c r="AP13" s="29">
-        <f t="shared" si="3"/>
-        <v>167480021169221.47</v>
-      </c>
-      <c r="AQ13" s="29">
-        <f t="shared" si="3"/>
-        <v>171126397152790.69</v>
-      </c>
-      <c r="AR13" s="29">
-        <f t="shared" si="3"/>
-        <v>175500523337032.78</v>
-      </c>
-      <c r="AS13" s="29">
-        <f t="shared" si="3"/>
-        <v>183790154786707.5</v>
-      </c>
-      <c r="AT13" s="29">
-        <f t="shared" si="3"/>
-        <v>194522129334526.38</v>
-      </c>
-      <c r="AU13" s="29">
-        <f t="shared" si="3"/>
-        <v>204873681139187.59</v>
-      </c>
-      <c r="AV13" s="29">
-        <f t="shared" si="3"/>
-        <v>208010641458284.06</v>
-      </c>
-      <c r="AW13" s="29">
-        <f t="shared" si="3"/>
-        <v>208354223353886.31</v>
-      </c>
-      <c r="AX13" s="29">
-        <f t="shared" si="3"/>
-        <v>208190510654682.22</v>
-      </c>
-      <c r="AY13" s="29">
-        <f t="shared" si="3"/>
-        <v>207624474110108.28</v>
-      </c>
-      <c r="AZ13" s="29">
-        <f t="shared" si="3"/>
-        <v>206403142130568.12</v>
-      </c>
-      <c r="BA13" s="29">
-        <f t="shared" si="3"/>
-        <v>205072945305453.41</v>
-      </c>
-      <c r="BB13" s="29">
-        <f t="shared" si="3"/>
-        <v>203590623835953.84</v>
-      </c>
-      <c r="BC13" s="29">
-        <f t="shared" si="3"/>
-        <v>202029055296022.84</v>
-      </c>
-      <c r="BD13" s="29">
-        <f t="shared" si="3"/>
-        <v>200532650356237.5</v>
-      </c>
-      <c r="BE13" s="29">
-        <f t="shared" si="3"/>
-        <v>198968013006011.53</v>
-      </c>
-      <c r="BF13" s="29">
-        <f t="shared" si="3"/>
-        <v>197745955183994.72</v>
-      </c>
-      <c r="BG13" s="29">
-        <f t="shared" si="3"/>
-        <v>196486216105160.62</v>
-      </c>
-      <c r="BH13" s="29">
-        <f t="shared" si="3"/>
-        <v>195402007686674.94</v>
-      </c>
-      <c r="BI13" s="29">
-        <f t="shared" si="3"/>
-        <v>195104424267361.12</v>
-      </c>
-      <c r="BJ13" s="29">
-        <f t="shared" si="3"/>
-        <v>194674298537834.88</v>
-      </c>
-      <c r="BK13" s="29">
-        <f t="shared" si="3"/>
-        <v>194689053172687.53</v>
-      </c>
-      <c r="BL13" s="29">
-        <f t="shared" si="3"/>
-        <v>195030902280985.72</v>
-      </c>
-      <c r="BM13" s="29">
-        <f t="shared" si="3"/>
-        <v>196313132333103.16</v>
-      </c>
-      <c r="BN13" s="29">
-        <f t="shared" si="3"/>
-        <v>197566745861967.62</v>
-      </c>
-      <c r="BO13" s="29">
-        <f t="shared" ref="BO13:BS15" si="4">BO7*$B$10</f>
-        <v>198716326240627.5</v>
-      </c>
-      <c r="BP13" s="29">
-        <f t="shared" si="4"/>
-        <v>199725708975566.47</v>
-      </c>
-      <c r="BQ13" s="29">
-        <f t="shared" si="4"/>
-        <v>200418559157690.72</v>
-      </c>
-      <c r="BR13" s="29">
-        <f t="shared" si="4"/>
-        <v>200674925671741.34</v>
-      </c>
-      <c r="BS13" s="29">
-        <f t="shared" si="4"/>
-        <v>200492371086200.19</v>
+        <v>200513698689221.22</v>
       </c>
     </row>
     <row r="14" spans="1:75" x14ac:dyDescent="0.2">
@@ -6552,284 +7497,284 @@
         <v>68</v>
       </c>
       <c r="B14" s="29">
-        <f t="shared" ref="B14:Q15" si="5">B8*$B$10</f>
-        <v>-33007002384248.672</v>
+        <f t="shared" ref="B14:Q15" si="4">B8*$B$10</f>
+        <v>-15501261278335.312</v>
       </c>
       <c r="C14" s="29">
-        <f t="shared" si="5"/>
-        <v>1324430043422.9617</v>
+        <f t="shared" si="4"/>
+        <v>-26174260847025.199</v>
       </c>
       <c r="D14" s="29">
-        <f t="shared" si="5"/>
-        <v>-48727574084735.336</v>
+        <f t="shared" si="4"/>
+        <v>17280094539783.627</v>
       </c>
       <c r="E14" s="29">
-        <f t="shared" si="5"/>
-        <v>89380365719601.406</v>
+        <f t="shared" si="4"/>
+        <v>54889712067547.992</v>
       </c>
       <c r="F14" s="29">
-        <f t="shared" si="5"/>
-        <v>81102721540371.812</v>
+        <f t="shared" si="4"/>
+        <v>90466377296514.266</v>
       </c>
       <c r="G14" s="29">
-        <f t="shared" si="5"/>
-        <v>100268910809801.58</v>
+        <f t="shared" si="4"/>
+        <v>110033543172445.75</v>
       </c>
       <c r="H14" s="29">
-        <f t="shared" si="5"/>
-        <v>134317585797151.89</v>
+        <f t="shared" si="4"/>
+        <v>112574733545943.33</v>
       </c>
       <c r="I14" s="29">
-        <f t="shared" si="5"/>
-        <v>101755882171776.73</v>
+        <f t="shared" si="4"/>
+        <v>145610208401412.03</v>
       </c>
       <c r="J14" s="29">
-        <f t="shared" si="5"/>
-        <v>196660559509257.81</v>
+        <f t="shared" si="4"/>
+        <v>137986637280919.25</v>
       </c>
       <c r="K14" s="29">
-        <f t="shared" si="5"/>
-        <v>101964167340563.3</v>
+        <f t="shared" si="4"/>
+        <v>143069018027914.44</v>
       </c>
       <c r="L14" s="29">
-        <f t="shared" si="5"/>
-        <v>151071985823510.62</v>
+        <f t="shared" si="4"/>
+        <v>193892825497866.28</v>
       </c>
       <c r="M14" s="29">
-        <f t="shared" si="5"/>
-        <v>287140818379345.5</v>
+        <f t="shared" si="4"/>
+        <v>165939731389392.75</v>
       </c>
       <c r="N14" s="29">
-        <f t="shared" si="5"/>
-        <v>60236392030831.109</v>
+        <f t="shared" si="4"/>
+        <v>165939731389392.75</v>
       </c>
       <c r="O14" s="29">
-        <f t="shared" si="5"/>
-        <v>195144152358213.91</v>
+        <f t="shared" si="4"/>
+        <v>150692589148407.22</v>
       </c>
       <c r="P14" s="29">
-        <f t="shared" si="5"/>
-        <v>159081296343047.62</v>
+        <f t="shared" si="4"/>
+        <v>219304729232842.22</v>
       </c>
       <c r="Q14" s="29">
-        <f t="shared" si="5"/>
-        <v>293183307147990.12</v>
+        <f t="shared" si="4"/>
+        <v>168480921762890.38</v>
       </c>
       <c r="R14" s="29">
+        <f t="shared" si="2"/>
+        <v>99868781678455.375</v>
+      </c>
+      <c r="S14" s="29">
+        <f t="shared" si="2"/>
+        <v>37609617527764.367</v>
+      </c>
+      <c r="T14" s="29">
+        <f t="shared" si="2"/>
+        <v>17025975502433.867</v>
+      </c>
+      <c r="U14" s="29">
+        <f t="shared" si="2"/>
+        <v>-6352975933743.9805</v>
+      </c>
+      <c r="V14" s="29">
+        <f t="shared" si="2"/>
+        <v>-19313046838581.699</v>
+      </c>
+      <c r="W14" s="29">
+        <f t="shared" si="2"/>
+        <v>9402404381941.0918</v>
+      </c>
+      <c r="X14" s="29">
+        <f t="shared" si="2"/>
+        <v>51840283619350.883</v>
+      </c>
+      <c r="Y14" s="29">
+        <f t="shared" si="2"/>
+        <v>82080449063972.219</v>
+      </c>
+      <c r="Z14" s="29">
+        <f t="shared" si="2"/>
+        <v>92245210557962.594</v>
+      </c>
+      <c r="AA14" s="29">
+        <f t="shared" si="2"/>
+        <v>97327591304957.781</v>
+      </c>
+      <c r="AB14" s="29">
+        <f t="shared" si="2"/>
+        <v>99868781678455.375</v>
+      </c>
+      <c r="AC14" s="29">
+        <f t="shared" si="2"/>
+        <v>102409972051952.95</v>
+      </c>
+      <c r="AD14" s="29">
+        <f t="shared" si="2"/>
+        <v>102409972051952.95</v>
+      </c>
+      <c r="AE14" s="29">
+        <f t="shared" si="2"/>
+        <v>102409972051952.95</v>
+      </c>
+      <c r="AF14" s="29">
+        <f t="shared" si="2"/>
+        <v>102409972051952.95</v>
+      </c>
+      <c r="AG14" s="29">
+        <f t="shared" si="2"/>
+        <v>99868781678455.375</v>
+      </c>
+      <c r="AH14" s="29">
+        <f t="shared" si="2"/>
+        <v>99868781678455.375</v>
+      </c>
+      <c r="AI14" s="29">
+        <f t="shared" si="2"/>
+        <v>97327591304957.781</v>
+      </c>
+      <c r="AJ14" s="29">
+        <f t="shared" si="2"/>
+        <v>93261686707361.641</v>
+      </c>
+      <c r="AK14" s="29">
+        <f t="shared" si="2"/>
+        <v>89958139221814.766</v>
+      </c>
+      <c r="AL14" s="29">
+        <f t="shared" si="2"/>
+        <v>86654591736267.891</v>
+      </c>
+      <c r="AM14" s="29">
+        <f t="shared" si="2"/>
+        <v>84113401362770.297</v>
+      </c>
+      <c r="AN14" s="29">
+        <f t="shared" si="2"/>
+        <v>78014544466376.078</v>
+      </c>
+      <c r="AO14" s="29">
+        <f t="shared" si="2"/>
+        <v>74202758906129.688</v>
+      </c>
+      <c r="AP14" s="29">
+        <f t="shared" si="2"/>
+        <v>72932163719380.906</v>
+      </c>
+      <c r="AQ14" s="29">
+        <f t="shared" si="2"/>
+        <v>74456877943479.453</v>
+      </c>
+      <c r="AR14" s="29">
+        <f t="shared" si="2"/>
+        <v>76998068316977.031</v>
+      </c>
+      <c r="AS14" s="29">
+        <f t="shared" si="2"/>
+        <v>80809853877223.438</v>
+      </c>
+      <c r="AT14" s="29">
+        <f t="shared" si="2"/>
+        <v>85129877512169.328</v>
+      </c>
+      <c r="AU14" s="29">
+        <f t="shared" si="2"/>
+        <v>88433424997716.203</v>
+      </c>
+      <c r="AV14" s="29">
+        <f t="shared" si="2"/>
+        <v>89958139221814.766</v>
+      </c>
+      <c r="AW14" s="29">
+        <f t="shared" si="2"/>
+        <v>90212258259164.531</v>
+      </c>
+      <c r="AX14" s="29">
+        <f t="shared" si="2"/>
+        <v>90212258259164.531</v>
+      </c>
+      <c r="AY14" s="29">
+        <f t="shared" si="2"/>
+        <v>89958139221814.766</v>
+      </c>
+      <c r="AZ14" s="29">
+        <f t="shared" si="2"/>
+        <v>89449901147115.25</v>
+      </c>
+      <c r="BA14" s="29">
+        <f t="shared" si="2"/>
+        <v>88687544035065.969</v>
+      </c>
+      <c r="BB14" s="29">
+        <f t="shared" si="2"/>
+        <v>88179305960366.438</v>
+      </c>
+      <c r="BC14" s="29">
+        <f t="shared" si="2"/>
+        <v>87416948848317.172</v>
+      </c>
+      <c r="BD14" s="29">
+        <f t="shared" si="2"/>
+        <v>86908710773617.656</v>
+      </c>
+      <c r="BE14" s="29">
+        <f t="shared" si="2"/>
+        <v>86146353661568.375</v>
+      </c>
+      <c r="BF14" s="29">
+        <f t="shared" si="2"/>
+        <v>85638115586868.859</v>
+      </c>
+      <c r="BG14" s="29">
+        <f t="shared" si="2"/>
+        <v>85129877512169.328</v>
+      </c>
+      <c r="BH14" s="29">
+        <f t="shared" si="2"/>
+        <v>84621639437469.828</v>
+      </c>
+      <c r="BI14" s="29">
+        <f t="shared" si="2"/>
+        <v>84621639437469.828</v>
+      </c>
+      <c r="BJ14" s="29">
+        <f t="shared" si="2"/>
+        <v>84367520400120.062</v>
+      </c>
+      <c r="BK14" s="29">
+        <f t="shared" si="2"/>
+        <v>84367520400120.062</v>
+      </c>
+      <c r="BL14" s="29">
+        <f t="shared" si="2"/>
+        <v>84621639437469.828</v>
+      </c>
+      <c r="BM14" s="29">
+        <f t="shared" si="2"/>
+        <v>85129877512169.328</v>
+      </c>
+      <c r="BN14" s="29">
+        <f t="shared" si="2"/>
+        <v>85638115586868.859</v>
+      </c>
+      <c r="BO14" s="29">
         <f t="shared" si="3"/>
-        <v>52406134105443.148</v>
-      </c>
-      <c r="S14" s="29">
+        <v>86146353661568.375</v>
+      </c>
+      <c r="BP14" s="29">
         <f t="shared" si="3"/>
-        <v>36240568828549.094</v>
-      </c>
-      <c r="T14" s="29">
+        <v>86654591736267.891</v>
+      </c>
+      <c r="BQ14" s="29">
         <f t="shared" si="3"/>
-        <v>30566152063304.203</v>
-      </c>
-      <c r="U14" s="29">
+        <v>86908710773617.656</v>
+      </c>
+      <c r="BR14" s="29">
         <f t="shared" si="3"/>
-        <v>-6571236644323.1084</v>
-      </c>
-      <c r="V14" s="29">
+        <v>86908710773617.656</v>
+      </c>
+      <c r="BS14" s="29">
         <f t="shared" si="3"/>
-        <v>-27325725307370.27</v>
-      </c>
-      <c r="W14" s="29">
-        <f t="shared" si="3"/>
-        <v>-18881767429776.895</v>
-      </c>
-      <c r="X14" s="29">
-        <f t="shared" si="3"/>
-        <v>57526425884122.867</v>
-      </c>
-      <c r="Y14" s="29">
-        <f t="shared" si="3"/>
-        <v>86732980436776.156</v>
-      </c>
-      <c r="Z14" s="29">
-        <f t="shared" si="3"/>
-        <v>91939066646385.953</v>
-      </c>
-      <c r="AA14" s="29">
-        <f t="shared" si="3"/>
-        <v>95878833455210.438</v>
-      </c>
-      <c r="AB14" s="29">
-        <f t="shared" si="3"/>
-        <v>102166068565642.88</v>
-      </c>
-      <c r="AC14" s="29">
-        <f t="shared" si="3"/>
-        <v>102721968689383.77</v>
-      </c>
-      <c r="AD14" s="29">
-        <f t="shared" si="3"/>
-        <v>103661935956732.17</v>
-      </c>
-      <c r="AE14" s="29">
-        <f t="shared" si="3"/>
-        <v>103809458789207.36</v>
-      </c>
-      <c r="AF14" s="29">
-        <f t="shared" si="3"/>
-        <v>102483018484514.16</v>
-      </c>
-      <c r="AG14" s="29">
-        <f t="shared" si="3"/>
-        <v>102514633106807.02</v>
-      </c>
-      <c r="AH14" s="29">
-        <f t="shared" si="3"/>
-        <v>98421331958874.438</v>
-      </c>
-      <c r="AI14" s="29">
-        <f t="shared" si="3"/>
-        <v>98267295637931.438</v>
-      </c>
-      <c r="AJ14" s="29">
-        <f t="shared" si="3"/>
-        <v>95971439542906.234</v>
-      </c>
-      <c r="AK14" s="29">
-        <f t="shared" si="3"/>
-        <v>87659727419582.797</v>
-      </c>
-      <c r="AL14" s="29">
-        <f t="shared" si="3"/>
-        <v>88852046349528.547</v>
-      </c>
-      <c r="AM14" s="29">
-        <f t="shared" si="3"/>
-        <v>84230650436107.438</v>
-      </c>
-      <c r="AN14" s="29">
-        <f t="shared" si="3"/>
-        <v>80976274527110</v>
-      </c>
-      <c r="AO14" s="29">
-        <f t="shared" si="3"/>
-        <v>71749881804463.031</v>
-      </c>
-      <c r="AP14" s="29">
-        <f t="shared" si="3"/>
-        <v>72590914313116.062</v>
-      </c>
-      <c r="AQ14" s="29">
-        <f t="shared" si="3"/>
-        <v>74171364116792.844</v>
-      </c>
-      <c r="AR14" s="29">
-        <f t="shared" si="3"/>
-        <v>76067242901727.156</v>
-      </c>
-      <c r="AS14" s="29">
-        <f t="shared" si="3"/>
-        <v>79660220273294.578</v>
-      </c>
-      <c r="AT14" s="29">
-        <f t="shared" si="3"/>
-        <v>84311783124627.859</v>
-      </c>
-      <c r="AU14" s="29">
-        <f t="shared" si="3"/>
-        <v>88798459235688.922</v>
-      </c>
-      <c r="AV14" s="29">
-        <f t="shared" si="3"/>
-        <v>90158112859670.109</v>
-      </c>
-      <c r="AW14" s="29">
-        <f t="shared" si="3"/>
-        <v>90307031660665.469</v>
-      </c>
-      <c r="AX14" s="29">
-        <f t="shared" si="3"/>
-        <v>90236073617808.031</v>
-      </c>
-      <c r="AY14" s="29">
-        <f t="shared" si="3"/>
-        <v>89990736233573.141</v>
-      </c>
-      <c r="AZ14" s="29">
-        <f t="shared" si="3"/>
-        <v>89461373958265.75</v>
-      </c>
-      <c r="BA14" s="29">
-        <f t="shared" si="3"/>
-        <v>88884826361260.641</v>
-      </c>
-      <c r="BB14" s="29">
-        <f t="shared" si="3"/>
-        <v>88242343335370.562</v>
-      </c>
-      <c r="BC14" s="29">
-        <f t="shared" si="3"/>
-        <v>87565512228681.984</v>
-      </c>
-      <c r="BD14" s="29">
-        <f t="shared" si="3"/>
-        <v>86916925000167.578</v>
-      </c>
-      <c r="BE14" s="29">
-        <f t="shared" si="3"/>
-        <v>86238763778139.812</v>
-      </c>
-      <c r="BF14" s="29">
-        <f t="shared" si="3"/>
-        <v>85709086900716.547</v>
-      </c>
-      <c r="BG14" s="29">
-        <f t="shared" si="3"/>
-        <v>85163077825185.484</v>
-      </c>
-      <c r="BH14" s="29">
-        <f t="shared" si="3"/>
-        <v>84693149054849.766</v>
-      </c>
-      <c r="BI14" s="29">
-        <f t="shared" si="3"/>
-        <v>84564167386817.938</v>
-      </c>
-      <c r="BJ14" s="29">
-        <f t="shared" si="3"/>
-        <v>84377737866700.062</v>
-      </c>
-      <c r="BK14" s="29">
-        <f t="shared" si="3"/>
-        <v>84384132972377.938</v>
-      </c>
-      <c r="BL14" s="29">
-        <f t="shared" si="3"/>
-        <v>84532300730867.875</v>
-      </c>
-      <c r="BM14" s="29">
-        <f t="shared" si="3"/>
-        <v>85088058075494.141</v>
-      </c>
-      <c r="BN14" s="29">
-        <f t="shared" si="3"/>
-        <v>85631412152119.312</v>
-      </c>
-      <c r="BO14" s="29">
-        <f t="shared" si="4"/>
-        <v>86129675110176.984</v>
-      </c>
-      <c r="BP14" s="29">
-        <f t="shared" si="4"/>
-        <v>86567172162718.312</v>
-      </c>
-      <c r="BQ14" s="29">
-        <f t="shared" si="4"/>
-        <v>86867474418780.188</v>
-      </c>
-      <c r="BR14" s="29">
-        <f t="shared" si="4"/>
-        <v>86978591431569.406</v>
-      </c>
-      <c r="BS14" s="29">
-        <f t="shared" si="4"/>
-        <v>86899466744433.781</v>
+        <v>86908710773617.656</v>
       </c>
     </row>
     <row r="15" spans="1:75" x14ac:dyDescent="0.2">
@@ -6837,284 +7782,284 @@
         <v>69</v>
       </c>
       <c r="B15" s="29">
+        <f t="shared" si="4"/>
+        <v>-9734599481774.3516</v>
+      </c>
+      <c r="C15" s="29">
+        <f t="shared" ref="C15:BN15" si="5">C9*$B$10</f>
+        <v>-16437110600373.086</v>
+      </c>
+      <c r="D15" s="29">
         <f t="shared" si="5"/>
-        <v>-20727987389884.023</v>
-      </c>
-      <c r="C15" s="29">
-        <f t="shared" ref="C15:BN15" si="6">C9*$B$10</f>
-        <v>831725611410.12561</v>
-      </c>
-      <c r="D15" s="29">
-        <f t="shared" si="6"/>
-        <v>-30600311091867.863</v>
+        <v>10851684668207.475</v>
       </c>
       <c r="E15" s="29">
-        <f t="shared" si="6"/>
-        <v>56129759133269.203</v>
+        <f t="shared" si="5"/>
+        <v>34470057181364.918</v>
       </c>
       <c r="F15" s="29">
-        <f t="shared" si="6"/>
-        <v>50931501437293.242</v>
+        <f t="shared" si="5"/>
+        <v>56811760910027.359</v>
       </c>
       <c r="G15" s="29">
-        <f t="shared" si="6"/>
-        <v>62967630161253.203</v>
+        <f t="shared" si="5"/>
+        <v>69099697960791.711</v>
       </c>
       <c r="H15" s="29">
-        <f t="shared" si="6"/>
-        <v>84349775003247.531</v>
+        <f t="shared" si="5"/>
+        <v>70695533941410.453</v>
       </c>
       <c r="I15" s="29">
-        <f t="shared" si="6"/>
-        <v>63901429701160.789</v>
+        <f t="shared" si="5"/>
+        <v>91441401689454.156</v>
       </c>
       <c r="J15" s="29">
-        <f t="shared" si="6"/>
-        <v>123500387891653.2</v>
+        <f t="shared" si="5"/>
+        <v>86653893747597.922</v>
       </c>
       <c r="K15" s="29">
-        <f t="shared" si="6"/>
-        <v>64032230199244.43</v>
+        <f t="shared" si="5"/>
+        <v>89845565708835.406</v>
       </c>
       <c r="L15" s="29">
-        <f t="shared" si="6"/>
-        <v>94871330048705.531</v>
+        <f t="shared" si="5"/>
+        <v>121762285321210.33</v>
       </c>
       <c r="M15" s="29">
-        <f t="shared" si="6"/>
-        <v>180320866257408.03</v>
+        <f t="shared" si="5"/>
+        <v>104208089534404.11</v>
       </c>
       <c r="N15" s="29">
-        <f t="shared" si="6"/>
-        <v>37827705766550.148</v>
+        <f t="shared" si="5"/>
+        <v>104208089534404.11</v>
       </c>
       <c r="O15" s="29">
-        <f t="shared" si="6"/>
-        <v>122548103041946.03</v>
+        <f t="shared" si="5"/>
+        <v>94633073650691.641</v>
       </c>
       <c r="P15" s="29">
-        <f t="shared" si="6"/>
-        <v>99901077540403.047</v>
+        <f t="shared" si="5"/>
+        <v>137720645127397.78</v>
       </c>
       <c r="Q15" s="29">
-        <f t="shared" si="6"/>
-        <v>184115474127032.44</v>
+        <f t="shared" si="5"/>
+        <v>105803925515022.86</v>
       </c>
       <c r="R15" s="29">
-        <f t="shared" si="6"/>
-        <v>32910401079274.602</v>
+        <f t="shared" si="5"/>
+        <v>62716354038316.719</v>
       </c>
       <c r="S15" s="29">
-        <f t="shared" si="6"/>
-        <v>22758626940290.352</v>
+        <f t="shared" si="5"/>
+        <v>23618372513157.441</v>
       </c>
       <c r="T15" s="29">
-        <f t="shared" si="6"/>
-        <v>19195163715557.414</v>
+        <f t="shared" si="5"/>
+        <v>10692101070145.6</v>
       </c>
       <c r="U15" s="29">
-        <f t="shared" si="6"/>
-        <v>-4126654965931.5176</v>
+        <f t="shared" si="5"/>
+        <v>-3989589951546.8652</v>
       </c>
       <c r="V15" s="29">
-        <f t="shared" si="6"/>
-        <v>-17160215974683.66</v>
+        <f t="shared" si="5"/>
+        <v>-12128353452702.471</v>
       </c>
       <c r="W15" s="29">
-        <f t="shared" si="6"/>
-        <v>-11857515342559.857</v>
+        <f t="shared" si="5"/>
+        <v>5904593128289.3604</v>
       </c>
       <c r="X15" s="29">
-        <f t="shared" si="6"/>
-        <v>36125880697370.672</v>
+        <f t="shared" si="5"/>
+        <v>32555054004622.422</v>
       </c>
       <c r="Y15" s="29">
-        <f t="shared" si="6"/>
-        <v>54467234069049.711</v>
+        <f t="shared" si="5"/>
+        <v>51545502173985.5</v>
       </c>
       <c r="Z15" s="29">
-        <f t="shared" si="6"/>
-        <v>57736591523785.969</v>
+        <f t="shared" si="5"/>
+        <v>57928846096460.484</v>
       </c>
       <c r="AA15" s="29">
-        <f t="shared" si="6"/>
-        <v>60210716128671.875</v>
+        <f t="shared" si="5"/>
+        <v>61120518057697.977</v>
       </c>
       <c r="AB15" s="29">
-        <f t="shared" si="6"/>
-        <v>64159021659999.703</v>
+        <f t="shared" si="5"/>
+        <v>62716354038316.719</v>
       </c>
       <c r="AC15" s="29">
-        <f t="shared" si="6"/>
-        <v>64508120030727.086</v>
+        <f t="shared" si="5"/>
+        <v>64312190018935.461</v>
       </c>
       <c r="AD15" s="29">
-        <f t="shared" si="6"/>
-        <v>65098407795659.039</v>
+        <f t="shared" si="5"/>
+        <v>64312190018935.461</v>
       </c>
       <c r="AE15" s="29">
-        <f t="shared" si="6"/>
-        <v>65191050301502.727</v>
+        <f t="shared" si="5"/>
+        <v>64312190018935.461</v>
       </c>
       <c r="AF15" s="29">
-        <f t="shared" si="6"/>
-        <v>64358062270992.117</v>
+        <f t="shared" si="5"/>
+        <v>64312190018935.461</v>
       </c>
       <c r="AG15" s="29">
-        <f t="shared" si="6"/>
-        <v>64377915860984.734</v>
+        <f t="shared" si="5"/>
+        <v>62716354038316.719</v>
       </c>
       <c r="AH15" s="29">
-        <f t="shared" si="6"/>
-        <v>61807373598781.789</v>
+        <f t="shared" si="5"/>
+        <v>62716354038316.719</v>
       </c>
       <c r="AI15" s="29">
-        <f t="shared" si="6"/>
-        <v>61710640703109.492</v>
+        <f t="shared" si="5"/>
+        <v>61120518057697.977</v>
       </c>
       <c r="AJ15" s="29">
-        <f t="shared" si="6"/>
-        <v>60268871601127.055</v>
+        <f t="shared" si="5"/>
+        <v>58567180488707.984</v>
       </c>
       <c r="AK15" s="29">
-        <f t="shared" si="6"/>
-        <v>55049219659549.625</v>
+        <f t="shared" si="5"/>
+        <v>56492593713903.617</v>
       </c>
       <c r="AL15" s="29">
-        <f t="shared" si="6"/>
-        <v>55797981133158.32</v>
+        <f t="shared" si="5"/>
+        <v>54418006939099.242</v>
       </c>
       <c r="AM15" s="29">
-        <f t="shared" si="6"/>
-        <v>52895801919732.758</v>
+        <f t="shared" si="5"/>
+        <v>52822170958480.492</v>
       </c>
       <c r="AN15" s="29">
-        <f t="shared" si="6"/>
-        <v>50852094284051.414</v>
+        <f t="shared" si="5"/>
+        <v>48992164604995.508</v>
       </c>
       <c r="AO15" s="29">
-        <f t="shared" si="6"/>
-        <v>45058034290878.32</v>
+        <f t="shared" si="5"/>
+        <v>46598410634067.383</v>
       </c>
       <c r="AP15" s="29">
-        <f t="shared" si="6"/>
-        <v>45586192256600.211</v>
+        <f t="shared" si="5"/>
+        <v>45800492643758.016</v>
       </c>
       <c r="AQ15" s="29">
-        <f t="shared" si="6"/>
-        <v>46578695096439.75</v>
+        <f t="shared" si="5"/>
+        <v>46757994232129.258</v>
       </c>
       <c r="AR15" s="29">
-        <f t="shared" si="6"/>
-        <v>47769283417347.688</v>
+        <f t="shared" si="5"/>
+        <v>48353830212748.008</v>
       </c>
       <c r="AS15" s="29">
-        <f t="shared" si="6"/>
-        <v>50025628564446.797</v>
+        <f t="shared" si="5"/>
+        <v>50747584183676.125</v>
       </c>
       <c r="AT15" s="29">
-        <f t="shared" si="6"/>
-        <v>52946752240061.18</v>
+        <f t="shared" si="5"/>
+        <v>53460505350728</v>
       </c>
       <c r="AU15" s="29">
-        <f t="shared" si="6"/>
-        <v>55764329091479.477</v>
+        <f t="shared" si="5"/>
+        <v>55535092125532.367</v>
       </c>
       <c r="AV15" s="29">
-        <f t="shared" si="6"/>
-        <v>56618174673832.062</v>
+        <f t="shared" si="5"/>
+        <v>56492593713903.617</v>
       </c>
       <c r="AW15" s="29">
-        <f t="shared" si="6"/>
-        <v>56711693830561.719</v>
+        <f t="shared" si="5"/>
+        <v>56652177311965.484</v>
       </c>
       <c r="AX15" s="29">
-        <f t="shared" si="6"/>
-        <v>56667133061291.086</v>
+        <f t="shared" si="5"/>
+        <v>56652177311965.484</v>
       </c>
       <c r="AY15" s="29">
-        <f t="shared" si="6"/>
-        <v>56513064232274.531</v>
+        <f t="shared" si="5"/>
+        <v>56492593713903.617</v>
       </c>
       <c r="AZ15" s="29">
-        <f t="shared" si="6"/>
-        <v>56180631300634.297</v>
+        <f t="shared" si="5"/>
+        <v>56173426517779.867</v>
       </c>
       <c r="BA15" s="29">
-        <f t="shared" si="6"/>
-        <v>55818566573238.969</v>
+        <f t="shared" si="5"/>
+        <v>55694675723594.242</v>
       </c>
       <c r="BB15" s="29">
-        <f t="shared" si="6"/>
-        <v>55415095215742.43</v>
+        <f t="shared" si="5"/>
+        <v>55375508527470.492</v>
       </c>
       <c r="BC15" s="29">
-        <f t="shared" si="6"/>
-        <v>54990053690274.578</v>
+        <f t="shared" si="5"/>
+        <v>54896757733284.867</v>
       </c>
       <c r="BD15" s="29">
-        <f t="shared" si="6"/>
-        <v>54582748969373.844</v>
+        <f t="shared" si="5"/>
+        <v>54577590537161.117</v>
       </c>
       <c r="BE15" s="29">
-        <f t="shared" si="6"/>
-        <v>54156872147999.477</v>
+        <f t="shared" si="5"/>
+        <v>54098839742975.492</v>
       </c>
       <c r="BF15" s="29">
-        <f t="shared" si="6"/>
-        <v>53824241650139.367</v>
+        <f t="shared" si="5"/>
+        <v>53779672546851.75</v>
       </c>
       <c r="BG15" s="29">
-        <f t="shared" si="6"/>
-        <v>53481354734792.852</v>
+        <f t="shared" si="5"/>
+        <v>53460505350728</v>
       </c>
       <c r="BH15" s="29">
-        <f t="shared" si="6"/>
-        <v>53186245305821.773</v>
+        <f t="shared" si="5"/>
+        <v>53141338154604.25</v>
       </c>
       <c r="BI15" s="29">
-        <f t="shared" si="6"/>
-        <v>53105246420877.117</v>
+        <f t="shared" si="5"/>
+        <v>53141338154604.25</v>
       </c>
       <c r="BJ15" s="29">
-        <f t="shared" si="6"/>
-        <v>52988170998604.016</v>
+        <f t="shared" si="5"/>
+        <v>52981754556542.367</v>
       </c>
       <c r="BK15" s="29">
-        <f t="shared" si="6"/>
-        <v>52992187045511.414</v>
+        <f t="shared" si="5"/>
+        <v>52981754556542.367</v>
       </c>
       <c r="BL15" s="29">
-        <f t="shared" si="6"/>
-        <v>53085234556879.25</v>
+        <f t="shared" si="5"/>
+        <v>53141338154604.25</v>
       </c>
       <c r="BM15" s="29">
-        <f t="shared" si="6"/>
-        <v>53434243264096.672</v>
+        <f t="shared" si="5"/>
+        <v>53460505350728</v>
       </c>
       <c r="BN15" s="29">
-        <f t="shared" si="6"/>
-        <v>53775462873118.273</v>
+        <f t="shared" si="5"/>
+        <v>53779672546851.75</v>
       </c>
       <c r="BO15" s="29">
-        <f t="shared" si="4"/>
-        <v>54088365819930.383</v>
+        <f t="shared" si="3"/>
+        <v>54098839742975.492</v>
       </c>
       <c r="BP15" s="29">
-        <f t="shared" si="4"/>
-        <v>54363108533086.172</v>
+        <f t="shared" si="3"/>
+        <v>54418006939099.242</v>
       </c>
       <c r="BQ15" s="29">
-        <f t="shared" si="4"/>
-        <v>54551694618679.18</v>
+        <f t="shared" si="3"/>
+        <v>54577590537161.117</v>
       </c>
       <c r="BR15" s="29">
-        <f t="shared" si="4"/>
-        <v>54621474722097.344</v>
+        <f t="shared" si="3"/>
+        <v>54577590537161.117</v>
       </c>
       <c r="BS15" s="29">
-        <f t="shared" si="4"/>
-        <v>54571785401689.422</v>
+        <f t="shared" si="3"/>
+        <v>54577590537161.117</v>
       </c>
     </row>
     <row r="16" spans="1:75" x14ac:dyDescent="0.2">
@@ -7196,283 +8141,283 @@
       </c>
       <c r="B17" s="29">
         <f>B13/$B$24</f>
-        <v>-76152966391934.312</v>
+        <v>-35764139239890.336</v>
       </c>
       <c r="C17" s="29">
-        <f t="shared" ref="C17:BN17" si="7">C13/$B$24</f>
-        <v>3055693316560.8555</v>
+        <f t="shared" ref="C17:BN17" si="6">C13/$B$24</f>
+        <v>-60388628552601.711</v>
       </c>
       <c r="D17" s="29">
+        <f t="shared" si="6"/>
+        <v>39868220792008.898</v>
+      </c>
+      <c r="E17" s="29">
+        <f t="shared" si="6"/>
+        <v>126640230751087.08</v>
+      </c>
+      <c r="F17" s="29">
+        <f t="shared" si="6"/>
+        <v>208721861793458.34</v>
+      </c>
+      <c r="G17" s="29">
+        <f t="shared" si="6"/>
+        <v>253866758866762.53</v>
+      </c>
+      <c r="H17" s="29">
+        <f t="shared" si="6"/>
+        <v>259729732512646.19</v>
+      </c>
+      <c r="I17" s="29">
+        <f t="shared" si="6"/>
+        <v>335948389909133.81</v>
+      </c>
+      <c r="J17" s="29">
+        <f t="shared" si="6"/>
+        <v>318359468971482.81</v>
+      </c>
+      <c r="K17" s="29">
+        <f t="shared" si="6"/>
+        <v>330085416263250.12</v>
+      </c>
+      <c r="L17" s="29">
+        <f t="shared" si="6"/>
+        <v>447344889180923.31</v>
+      </c>
+      <c r="M17" s="29">
+        <f t="shared" si="6"/>
+        <v>382852179076203.06</v>
+      </c>
+      <c r="N17" s="29">
+        <f t="shared" si="6"/>
+        <v>382852179076203.06</v>
+      </c>
+      <c r="O17" s="29">
+        <f t="shared" si="6"/>
+        <v>347674337200901.06</v>
+      </c>
+      <c r="P17" s="29">
+        <f t="shared" si="6"/>
+        <v>505974625639759.94</v>
+      </c>
+      <c r="Q17" s="29">
+        <f t="shared" si="6"/>
+        <v>388715152722086.75</v>
+      </c>
+      <c r="R17" s="29">
+        <f t="shared" si="6"/>
+        <v>230414864283227.91</v>
+      </c>
+      <c r="S17" s="29">
+        <f t="shared" si="6"/>
+        <v>86772009959078.188</v>
+      </c>
+      <c r="T17" s="29">
+        <f t="shared" si="6"/>
+        <v>39281923427420.523</v>
+      </c>
+      <c r="U17" s="29">
+        <f t="shared" si="6"/>
+        <v>-14657434114709.154</v>
+      </c>
+      <c r="V17" s="29">
+        <f t="shared" si="6"/>
+        <v>-44558599708715.828</v>
+      </c>
+      <c r="W17" s="29">
+        <f t="shared" si="6"/>
+        <v>21693002489769.547</v>
+      </c>
+      <c r="X17" s="29">
+        <f t="shared" si="6"/>
+        <v>119604662376026.69</v>
+      </c>
+      <c r="Y17" s="29">
+        <f t="shared" si="6"/>
+        <v>189374048762042.25</v>
+      </c>
+      <c r="Z17" s="29">
+        <f t="shared" si="6"/>
+        <v>212825943345576.91</v>
+      </c>
+      <c r="AA17" s="29">
+        <f t="shared" si="6"/>
+        <v>224551890637344.22</v>
+      </c>
+      <c r="AB17" s="29">
+        <f t="shared" si="6"/>
+        <v>230414864283227.91</v>
+      </c>
+      <c r="AC17" s="29">
+        <f t="shared" si="6"/>
+        <v>236277837929111.53</v>
+      </c>
+      <c r="AD17" s="29">
+        <f t="shared" si="6"/>
+        <v>236277837929111.53</v>
+      </c>
+      <c r="AE17" s="29">
+        <f t="shared" si="6"/>
+        <v>236277837929111.53</v>
+      </c>
+      <c r="AF17" s="29">
+        <f t="shared" si="6"/>
+        <v>236277837929111.53</v>
+      </c>
+      <c r="AG17" s="29">
+        <f t="shared" si="6"/>
+        <v>230414864283227.91</v>
+      </c>
+      <c r="AH17" s="29">
+        <f t="shared" si="6"/>
+        <v>230414864283227.91</v>
+      </c>
+      <c r="AI17" s="29">
+        <f t="shared" si="6"/>
+        <v>224551890637344.22</v>
+      </c>
+      <c r="AJ17" s="29">
+        <f t="shared" si="6"/>
+        <v>215171132803930.38</v>
+      </c>
+      <c r="AK17" s="29">
+        <f t="shared" si="6"/>
+        <v>207549267064281.62</v>
+      </c>
+      <c r="AL17" s="29">
+        <f t="shared" si="6"/>
+        <v>199927401324632.84</v>
+      </c>
+      <c r="AM17" s="29">
+        <f t="shared" si="6"/>
+        <v>194064427678749.19</v>
+      </c>
+      <c r="AN17" s="29">
+        <f t="shared" si="6"/>
+        <v>179993290928628.38</v>
+      </c>
+      <c r="AO17" s="29">
+        <f t="shared" si="6"/>
+        <v>171198830459802.91</v>
+      </c>
+      <c r="AP17" s="29">
+        <f t="shared" si="6"/>
+        <v>168267343636861.09</v>
+      </c>
+      <c r="AQ17" s="29">
+        <f t="shared" si="6"/>
+        <v>171785127824391.28</v>
+      </c>
+      <c r="AR17" s="29">
+        <f t="shared" si="6"/>
+        <v>177648101470274.94</v>
+      </c>
+      <c r="AS17" s="29">
+        <f t="shared" si="6"/>
+        <v>186442561939100.41</v>
+      </c>
+      <c r="AT17" s="29">
+        <f t="shared" si="6"/>
+        <v>196409617137102.66</v>
+      </c>
+      <c r="AU17" s="29">
+        <f t="shared" si="6"/>
+        <v>204031482876751.44</v>
+      </c>
+      <c r="AV17" s="29">
+        <f t="shared" si="6"/>
+        <v>207549267064281.62</v>
+      </c>
+      <c r="AW17" s="29">
+        <f t="shared" si="6"/>
+        <v>208135564428869.97</v>
+      </c>
+      <c r="AX17" s="29">
+        <f t="shared" si="6"/>
+        <v>208135564428869.97</v>
+      </c>
+      <c r="AY17" s="29">
+        <f t="shared" si="6"/>
+        <v>207549267064281.62</v>
+      </c>
+      <c r="AZ17" s="29">
+        <f t="shared" si="6"/>
+        <v>206376672335104.88</v>
+      </c>
+      <c r="BA17" s="29">
+        <f t="shared" si="6"/>
+        <v>204617780241339.78</v>
+      </c>
+      <c r="BB17" s="29">
+        <f t="shared" si="6"/>
+        <v>203445185512163.03</v>
+      </c>
+      <c r="BC17" s="29">
+        <f t="shared" si="6"/>
+        <v>201686293418397.94</v>
+      </c>
+      <c r="BD17" s="29">
+        <f t="shared" si="6"/>
+        <v>200513698689221.22</v>
+      </c>
+      <c r="BE17" s="29">
+        <f t="shared" si="6"/>
+        <v>198754806595456.12</v>
+      </c>
+      <c r="BF17" s="29">
+        <f t="shared" si="6"/>
+        <v>197582211866279.41</v>
+      </c>
+      <c r="BG17" s="29">
+        <f t="shared" si="6"/>
+        <v>196409617137102.66</v>
+      </c>
+      <c r="BH17" s="29">
+        <f t="shared" si="6"/>
+        <v>195237022407925.91</v>
+      </c>
+      <c r="BI17" s="29">
+        <f t="shared" si="6"/>
+        <v>195237022407925.91</v>
+      </c>
+      <c r="BJ17" s="29">
+        <f t="shared" si="6"/>
+        <v>194650725043337.56</v>
+      </c>
+      <c r="BK17" s="29">
+        <f t="shared" si="6"/>
+        <v>194650725043337.56</v>
+      </c>
+      <c r="BL17" s="29">
+        <f t="shared" si="6"/>
+        <v>195237022407925.91</v>
+      </c>
+      <c r="BM17" s="29">
+        <f t="shared" si="6"/>
+        <v>196409617137102.66</v>
+      </c>
+      <c r="BN17" s="29">
+        <f t="shared" si="6"/>
+        <v>197582211866279.41</v>
+      </c>
+      <c r="BO17" s="29">
+        <f t="shared" ref="BO17:BS17" si="7">BO13/$B$24</f>
+        <v>198754806595456.12</v>
+      </c>
+      <c r="BP17" s="29">
         <f t="shared" si="7"/>
-        <v>-112423093392029.81</v>
-      </c>
-      <c r="E17" s="29">
+        <v>199927401324632.84</v>
+      </c>
+      <c r="BQ17" s="29">
         <f t="shared" si="7"/>
-        <v>206216241859993.41</v>
-      </c>
-      <c r="F17" s="29">
+        <v>200513698689221.22</v>
+      </c>
+      <c r="BR17" s="29">
         <f t="shared" si="7"/>
-        <v>187118259206285.97</v>
-      </c>
-      <c r="G17" s="29">
+        <v>200513698689221.22</v>
+      </c>
+      <c r="BS17" s="29">
         <f t="shared" si="7"/>
-        <v>231338032644205.22</v>
-      </c>
-      <c r="H17" s="29">
-        <f t="shared" si="7"/>
-        <v>309894321149790.56</v>
-      </c>
-      <c r="I17" s="29">
-        <f t="shared" si="7"/>
-        <v>234768737403032.44</v>
-      </c>
-      <c r="J17" s="29">
-        <f t="shared" si="7"/>
-        <v>453730538889359</v>
-      </c>
-      <c r="K17" s="29">
-        <f t="shared" si="7"/>
-        <v>235249287962392.25</v>
-      </c>
-      <c r="L17" s="29">
-        <f t="shared" si="7"/>
-        <v>348549672134743.75</v>
-      </c>
-      <c r="M17" s="29">
-        <f t="shared" si="7"/>
-        <v>662484427917326.5</v>
-      </c>
-      <c r="N17" s="29">
-        <f t="shared" si="7"/>
-        <v>138975962872784.77</v>
-      </c>
-      <c r="O17" s="29">
-        <f t="shared" si="7"/>
-        <v>450231920582079.94</v>
-      </c>
-      <c r="P17" s="29">
-        <f t="shared" si="7"/>
-        <v>367028561787199.31</v>
-      </c>
-      <c r="Q17" s="29">
-        <f t="shared" si="7"/>
-        <v>676425513471397.25</v>
-      </c>
-      <c r="R17" s="29">
-        <f t="shared" si="7"/>
-        <v>120910179082712.19</v>
-      </c>
-      <c r="S17" s="29">
-        <f t="shared" si="7"/>
-        <v>83613373547126.562</v>
-      </c>
-      <c r="T17" s="29">
-        <f t="shared" si="7"/>
-        <v>70521494915223.375</v>
-      </c>
-      <c r="U17" s="29">
-        <f t="shared" si="7"/>
-        <v>-15161000005483.406</v>
-      </c>
-      <c r="V17" s="29">
-        <f t="shared" si="7"/>
-        <v>-63045259813125.086</v>
-      </c>
-      <c r="W17" s="29">
-        <f t="shared" si="7"/>
-        <v>-43563562172683.203</v>
-      </c>
-      <c r="X17" s="29">
-        <f t="shared" si="7"/>
-        <v>132723593799971.42</v>
-      </c>
-      <c r="Y17" s="29">
-        <f t="shared" si="7"/>
-        <v>200108257859431.75</v>
-      </c>
-      <c r="Z17" s="29">
-        <f t="shared" si="7"/>
-        <v>212119615435578.12</v>
-      </c>
-      <c r="AA17" s="29">
-        <f t="shared" si="7"/>
-        <v>221209351179883.25</v>
-      </c>
-      <c r="AB17" s="29">
-        <f t="shared" si="7"/>
-        <v>235715109639531.69</v>
-      </c>
-      <c r="AC17" s="29">
-        <f t="shared" si="7"/>
-        <v>236997669108207.12</v>
-      </c>
-      <c r="AD17" s="29">
-        <f t="shared" si="7"/>
-        <v>239166339103943</v>
-      </c>
-      <c r="AE17" s="29">
-        <f t="shared" si="7"/>
-        <v>239506700254366.22</v>
-      </c>
-      <c r="AF17" s="29">
-        <f t="shared" si="7"/>
-        <v>236446368911087</v>
-      </c>
-      <c r="AG17" s="29">
-        <f t="shared" si="7"/>
-        <v>236519309411437.03</v>
-      </c>
-      <c r="AH17" s="29">
-        <f t="shared" si="7"/>
-        <v>227075342912397.09</v>
-      </c>
-      <c r="AI17" s="29">
-        <f t="shared" si="7"/>
-        <v>226719953997179.91</v>
-      </c>
-      <c r="AJ17" s="29">
-        <f t="shared" si="7"/>
-        <v>221423009730329.28</v>
-      </c>
-      <c r="AK17" s="29">
-        <f t="shared" si="7"/>
-        <v>202246426330894.59</v>
-      </c>
-      <c r="AL17" s="29">
-        <f t="shared" si="7"/>
-        <v>204997316046464.69</v>
-      </c>
-      <c r="AM17" s="29">
-        <f t="shared" si="7"/>
-        <v>194334941936220.5</v>
-      </c>
-      <c r="AN17" s="29">
-        <f t="shared" si="7"/>
-        <v>186826523681830.03</v>
-      </c>
-      <c r="AO17" s="29">
-        <f t="shared" si="7"/>
-        <v>165539611082283.59</v>
-      </c>
-      <c r="AP17" s="29">
-        <f t="shared" si="7"/>
-        <v>167480021169221.47</v>
-      </c>
-      <c r="AQ17" s="29">
-        <f t="shared" si="7"/>
-        <v>171126397152790.69</v>
-      </c>
-      <c r="AR17" s="29">
-        <f t="shared" si="7"/>
-        <v>175500523337032.78</v>
-      </c>
-      <c r="AS17" s="29">
-        <f t="shared" si="7"/>
-        <v>183790154786707.5</v>
-      </c>
-      <c r="AT17" s="29">
-        <f t="shared" si="7"/>
-        <v>194522129334526.38</v>
-      </c>
-      <c r="AU17" s="29">
-        <f t="shared" si="7"/>
-        <v>204873681139187.59</v>
-      </c>
-      <c r="AV17" s="29">
-        <f t="shared" si="7"/>
-        <v>208010641458284.06</v>
-      </c>
-      <c r="AW17" s="29">
-        <f t="shared" si="7"/>
-        <v>208354223353886.31</v>
-      </c>
-      <c r="AX17" s="29">
-        <f t="shared" si="7"/>
-        <v>208190510654682.22</v>
-      </c>
-      <c r="AY17" s="29">
-        <f t="shared" si="7"/>
-        <v>207624474110108.28</v>
-      </c>
-      <c r="AZ17" s="29">
-        <f t="shared" si="7"/>
-        <v>206403142130568.12</v>
-      </c>
-      <c r="BA17" s="29">
-        <f t="shared" si="7"/>
-        <v>205072945305453.41</v>
-      </c>
-      <c r="BB17" s="29">
-        <f t="shared" si="7"/>
-        <v>203590623835953.84</v>
-      </c>
-      <c r="BC17" s="29">
-        <f t="shared" si="7"/>
-        <v>202029055296022.84</v>
-      </c>
-      <c r="BD17" s="29">
-        <f t="shared" si="7"/>
-        <v>200532650356237.5</v>
-      </c>
-      <c r="BE17" s="29">
-        <f t="shared" si="7"/>
-        <v>198968013006011.53</v>
-      </c>
-      <c r="BF17" s="29">
-        <f t="shared" si="7"/>
-        <v>197745955183994.72</v>
-      </c>
-      <c r="BG17" s="29">
-        <f t="shared" si="7"/>
-        <v>196486216105160.62</v>
-      </c>
-      <c r="BH17" s="29">
-        <f t="shared" si="7"/>
-        <v>195402007686674.94</v>
-      </c>
-      <c r="BI17" s="29">
-        <f t="shared" si="7"/>
-        <v>195104424267361.12</v>
-      </c>
-      <c r="BJ17" s="29">
-        <f t="shared" si="7"/>
-        <v>194674298537834.88</v>
-      </c>
-      <c r="BK17" s="29">
-        <f t="shared" si="7"/>
-        <v>194689053172687.53</v>
-      </c>
-      <c r="BL17" s="29">
-        <f t="shared" si="7"/>
-        <v>195030902280985.72</v>
-      </c>
-      <c r="BM17" s="29">
-        <f t="shared" si="7"/>
-        <v>196313132333103.16</v>
-      </c>
-      <c r="BN17" s="29">
-        <f t="shared" si="7"/>
-        <v>197566745861967.62</v>
-      </c>
-      <c r="BO17" s="29">
-        <f t="shared" ref="BO17:BS17" si="8">BO13/$B$24</f>
-        <v>198716326240627.5</v>
-      </c>
-      <c r="BP17" s="29">
-        <f t="shared" si="8"/>
-        <v>199725708975566.47</v>
-      </c>
-      <c r="BQ17" s="29">
-        <f t="shared" si="8"/>
-        <v>200418559157690.72</v>
-      </c>
-      <c r="BR17" s="29">
-        <f t="shared" si="8"/>
-        <v>200674925671741.34</v>
-      </c>
-      <c r="BS17" s="29">
-        <f t="shared" si="8"/>
-        <v>200492371086200.19</v>
+        <v>200513698689221.22</v>
       </c>
     </row>
     <row r="18" spans="1:71" x14ac:dyDescent="0.2">
@@ -7481,283 +8426,283 @@
       </c>
       <c r="B18" s="29">
         <f>B14/$B$25</f>
-        <v>-1178821513723.1667</v>
+        <v>-553616474226.26111</v>
       </c>
       <c r="C18" s="29">
-        <f t="shared" ref="C18:BN18" si="9">C14/$B$25</f>
-        <v>47301072979.391487</v>
+        <f t="shared" ref="C18:BN18" si="8">C14/$B$25</f>
+        <v>-934795030250.90002</v>
       </c>
       <c r="D18" s="29">
+        <f t="shared" si="8"/>
+        <v>617146233563.70093</v>
+      </c>
+      <c r="E18" s="29">
+        <f t="shared" si="8"/>
+        <v>1960346859555.2854</v>
+      </c>
+      <c r="F18" s="29">
+        <f t="shared" si="8"/>
+        <v>3230942046304.0811</v>
+      </c>
+      <c r="G18" s="29">
+        <f t="shared" si="8"/>
+        <v>3929769399015.9194</v>
+      </c>
+      <c r="H18" s="29">
+        <f t="shared" si="8"/>
+        <v>4020526198069.4048</v>
+      </c>
+      <c r="I18" s="29">
+        <f t="shared" si="8"/>
+        <v>5200364585764.7158</v>
+      </c>
+      <c r="J18" s="29">
+        <f t="shared" si="8"/>
+        <v>4928094188604.2588</v>
+      </c>
+      <c r="K18" s="29">
+        <f t="shared" si="8"/>
+        <v>5109607786711.2295</v>
+      </c>
+      <c r="L18" s="29">
+        <f t="shared" si="8"/>
+        <v>6924743767780.9385</v>
+      </c>
+      <c r="M18" s="29">
+        <f t="shared" si="8"/>
+        <v>5926418978192.5986</v>
+      </c>
+      <c r="N18" s="29">
+        <f t="shared" si="8"/>
+        <v>5926418978192.5986</v>
+      </c>
+      <c r="O18" s="29">
+        <f t="shared" si="8"/>
+        <v>5381878183871.6865</v>
+      </c>
+      <c r="P18" s="29">
+        <f t="shared" si="8"/>
+        <v>7832311758315.7939</v>
+      </c>
+      <c r="Q18" s="29">
+        <f t="shared" si="8"/>
+        <v>6017175777246.085</v>
+      </c>
+      <c r="R18" s="29">
+        <f t="shared" si="8"/>
+        <v>3566742202801.9775</v>
+      </c>
+      <c r="S18" s="29">
+        <f t="shared" si="8"/>
+        <v>1343200625991.5845</v>
+      </c>
+      <c r="T18" s="29">
+        <f t="shared" si="8"/>
+        <v>608070553658.35242</v>
+      </c>
+      <c r="U18" s="29">
+        <f t="shared" si="8"/>
+        <v>-226891997633.71359</v>
+      </c>
+      <c r="V18" s="29">
+        <f t="shared" si="8"/>
+        <v>-689751672806.48926</v>
+      </c>
+      <c r="W18" s="29">
+        <f t="shared" si="8"/>
+        <v>335800156497.89612</v>
+      </c>
+      <c r="X18" s="29">
+        <f t="shared" si="8"/>
+        <v>1851438700691.103</v>
+      </c>
+      <c r="Y18" s="29">
+        <f t="shared" si="8"/>
+        <v>2931444609427.5791</v>
+      </c>
+      <c r="Z18" s="29">
+        <f t="shared" si="8"/>
+        <v>3294471805641.521</v>
+      </c>
+      <c r="AA18" s="29">
+        <f t="shared" si="8"/>
+        <v>3475985403748.4922</v>
+      </c>
+      <c r="AB18" s="29">
+        <f t="shared" si="8"/>
+        <v>3566742202801.9775</v>
+      </c>
+      <c r="AC18" s="29">
+        <f t="shared" si="8"/>
+        <v>3657499001855.4624</v>
+      </c>
+      <c r="AD18" s="29">
+        <f t="shared" si="8"/>
+        <v>3657499001855.4624</v>
+      </c>
+      <c r="AE18" s="29">
+        <f t="shared" si="8"/>
+        <v>3657499001855.4624</v>
+      </c>
+      <c r="AF18" s="29">
+        <f t="shared" si="8"/>
+        <v>3657499001855.4624</v>
+      </c>
+      <c r="AG18" s="29">
+        <f t="shared" si="8"/>
+        <v>3566742202801.9775</v>
+      </c>
+      <c r="AH18" s="29">
+        <f t="shared" si="8"/>
+        <v>3566742202801.9775</v>
+      </c>
+      <c r="AI18" s="29">
+        <f t="shared" si="8"/>
+        <v>3475985403748.4922</v>
+      </c>
+      <c r="AJ18" s="29">
+        <f t="shared" si="8"/>
+        <v>3330774525262.9155</v>
+      </c>
+      <c r="AK18" s="29">
+        <f t="shared" si="8"/>
+        <v>3212790686493.3843</v>
+      </c>
+      <c r="AL18" s="29">
+        <f t="shared" si="8"/>
+        <v>3094806847723.853</v>
+      </c>
+      <c r="AM18" s="29">
+        <f t="shared" si="8"/>
+        <v>3004050048670.3677</v>
+      </c>
+      <c r="AN18" s="29">
+        <f t="shared" si="8"/>
+        <v>2786233730942.0029</v>
+      </c>
+      <c r="AO18" s="29">
+        <f t="shared" si="8"/>
+        <v>2650098532361.7744</v>
+      </c>
+      <c r="AP18" s="29">
+        <f t="shared" si="8"/>
+        <v>2604720132835.0322</v>
+      </c>
+      <c r="AQ18" s="29">
+        <f t="shared" si="8"/>
+        <v>2659174212267.1235</v>
+      </c>
+      <c r="AR18" s="29">
+        <f t="shared" si="8"/>
+        <v>2749931011320.6084</v>
+      </c>
+      <c r="AS18" s="29">
+        <f t="shared" si="8"/>
+        <v>2886066209900.8369</v>
+      </c>
+      <c r="AT18" s="29">
+        <f t="shared" si="8"/>
+        <v>3040352768291.7617</v>
+      </c>
+      <c r="AU18" s="29">
+        <f t="shared" si="8"/>
+        <v>3158336607061.293</v>
+      </c>
+      <c r="AV18" s="29">
+        <f t="shared" si="8"/>
+        <v>3212790686493.3843</v>
+      </c>
+      <c r="AW18" s="29">
+        <f t="shared" si="8"/>
+        <v>3221866366398.7334</v>
+      </c>
+      <c r="AX18" s="29">
+        <f t="shared" si="8"/>
+        <v>3221866366398.7334</v>
+      </c>
+      <c r="AY18" s="29">
+        <f t="shared" si="8"/>
+        <v>3212790686493.3843</v>
+      </c>
+      <c r="AZ18" s="29">
+        <f t="shared" si="8"/>
+        <v>3194639326682.6875</v>
+      </c>
+      <c r="BA18" s="29">
+        <f t="shared" si="8"/>
+        <v>3167412286966.6416</v>
+      </c>
+      <c r="BB18" s="29">
+        <f t="shared" si="8"/>
+        <v>3149260927155.9443</v>
+      </c>
+      <c r="BC18" s="29">
+        <f t="shared" si="8"/>
+        <v>3122033887439.8989</v>
+      </c>
+      <c r="BD18" s="29">
+        <f t="shared" si="8"/>
+        <v>3103882527629.2021</v>
+      </c>
+      <c r="BE18" s="29">
+        <f t="shared" si="8"/>
+        <v>3076655487913.1562</v>
+      </c>
+      <c r="BF18" s="29">
+        <f t="shared" si="8"/>
+        <v>3058504128102.4595</v>
+      </c>
+      <c r="BG18" s="29">
+        <f t="shared" si="8"/>
+        <v>3040352768291.7617</v>
+      </c>
+      <c r="BH18" s="29">
+        <f t="shared" si="8"/>
+        <v>3022201408481.0654</v>
+      </c>
+      <c r="BI18" s="29">
+        <f t="shared" si="8"/>
+        <v>3022201408481.0654</v>
+      </c>
+      <c r="BJ18" s="29">
+        <f t="shared" si="8"/>
+        <v>3013125728575.7163</v>
+      </c>
+      <c r="BK18" s="29">
+        <f t="shared" si="8"/>
+        <v>3013125728575.7163</v>
+      </c>
+      <c r="BL18" s="29">
+        <f t="shared" si="8"/>
+        <v>3022201408481.0654</v>
+      </c>
+      <c r="BM18" s="29">
+        <f t="shared" si="8"/>
+        <v>3040352768291.7617</v>
+      </c>
+      <c r="BN18" s="29">
+        <f t="shared" si="8"/>
+        <v>3058504128102.4595</v>
+      </c>
+      <c r="BO18" s="29">
+        <f t="shared" ref="BO18:BS18" si="9">BO14/$B$25</f>
+        <v>3076655487913.1562</v>
+      </c>
+      <c r="BP18" s="29">
         <f t="shared" si="9"/>
-        <v>-1740270503026.262</v>
-      </c>
-      <c r="E18" s="29">
+        <v>3094806847723.853</v>
+      </c>
+      <c r="BQ18" s="29">
         <f t="shared" si="9"/>
-        <v>3192155918557.1929</v>
-      </c>
-      <c r="F18" s="29">
+        <v>3103882527629.2021</v>
+      </c>
+      <c r="BR18" s="29">
         <f t="shared" si="9"/>
-        <v>2896525769298.9932</v>
-      </c>
-      <c r="G18" s="29">
+        <v>3103882527629.2021</v>
+      </c>
+      <c r="BS18" s="29">
         <f t="shared" si="9"/>
-        <v>3581032528921.4849</v>
-      </c>
-      <c r="H18" s="29">
-        <f t="shared" si="9"/>
-        <v>4797056635612.5674</v>
-      </c>
-      <c r="I18" s="29">
-        <f t="shared" si="9"/>
-        <v>3634138648992.0264</v>
-      </c>
-      <c r="J18" s="29">
-        <f t="shared" si="9"/>
-        <v>7023591411044.9219</v>
-      </c>
-      <c r="K18" s="29">
-        <f t="shared" si="9"/>
-        <v>3641577405020.1177</v>
-      </c>
-      <c r="L18" s="29">
-        <f t="shared" si="9"/>
-        <v>5395428065125.3799</v>
-      </c>
-      <c r="M18" s="29">
-        <f t="shared" si="9"/>
-        <v>10255029227833.768</v>
-      </c>
-      <c r="N18" s="29">
-        <f t="shared" si="9"/>
-        <v>2151299715386.8254</v>
-      </c>
-      <c r="O18" s="29">
-        <f t="shared" si="9"/>
-        <v>6969434012793.3535</v>
-      </c>
-      <c r="P18" s="29">
-        <f t="shared" si="9"/>
-        <v>5681474869394.5576</v>
-      </c>
-      <c r="Q18" s="29">
-        <f t="shared" si="9"/>
-        <v>10470832398142.504</v>
-      </c>
-      <c r="R18" s="29">
-        <f t="shared" si="9"/>
-        <v>1871647646622.9695</v>
-      </c>
-      <c r="S18" s="29">
-        <f t="shared" si="9"/>
-        <v>1294306029591.0391</v>
-      </c>
-      <c r="T18" s="29">
-        <f t="shared" si="9"/>
-        <v>1091648287975.1501</v>
-      </c>
-      <c r="U18" s="29">
-        <f t="shared" si="9"/>
-        <v>-234687023011.53958</v>
-      </c>
-      <c r="V18" s="29">
-        <f t="shared" si="9"/>
-        <v>-975918760977.50964</v>
-      </c>
-      <c r="W18" s="29">
-        <f t="shared" si="9"/>
-        <v>-674348836777.74622</v>
-      </c>
-      <c r="X18" s="29">
-        <f t="shared" si="9"/>
-        <v>2054515210147.2454</v>
-      </c>
-      <c r="Y18" s="29">
-        <f t="shared" si="9"/>
-        <v>3097606444170.5771</v>
-      </c>
-      <c r="Z18" s="29">
-        <f t="shared" si="9"/>
-        <v>3283538094513.7842</v>
-      </c>
-      <c r="AA18" s="29">
-        <f t="shared" si="9"/>
-        <v>3424244051971.8013</v>
-      </c>
-      <c r="AB18" s="29">
-        <f t="shared" si="9"/>
-        <v>3648788163058.6743</v>
-      </c>
-      <c r="AC18" s="29">
-        <f t="shared" si="9"/>
-        <v>3668641738906.563</v>
-      </c>
-      <c r="AD18" s="29">
-        <f t="shared" si="9"/>
-        <v>3702211998454.7202</v>
-      </c>
-      <c r="AE18" s="29">
-        <f t="shared" si="9"/>
-        <v>3707480671043.1201</v>
-      </c>
-      <c r="AF18" s="29">
-        <f t="shared" si="9"/>
-        <v>3660107803018.3628</v>
-      </c>
-      <c r="AG18" s="29">
-        <f t="shared" si="9"/>
-        <v>3661236896671.6792</v>
-      </c>
-      <c r="AH18" s="29">
-        <f t="shared" si="9"/>
-        <v>3515047569959.8013</v>
-      </c>
-      <c r="AI18" s="29">
-        <f t="shared" si="9"/>
-        <v>3509546272783.2656</v>
-      </c>
-      <c r="AJ18" s="29">
-        <f t="shared" si="9"/>
-        <v>3427551412246.6514</v>
-      </c>
-      <c r="AK18" s="29">
-        <f t="shared" si="9"/>
-        <v>3130704550699.3857</v>
-      </c>
-      <c r="AL18" s="29">
-        <f t="shared" si="9"/>
-        <v>3173287369626.0195</v>
-      </c>
-      <c r="AM18" s="29">
-        <f t="shared" si="9"/>
-        <v>3008237515575.2656</v>
-      </c>
-      <c r="AN18" s="29">
-        <f t="shared" si="9"/>
-        <v>2892009804539.6431</v>
-      </c>
-      <c r="AO18" s="29">
-        <f t="shared" si="9"/>
-        <v>2562495778730.8228</v>
-      </c>
-      <c r="AP18" s="29">
-        <f t="shared" si="9"/>
-        <v>2592532654039.8594</v>
-      </c>
-      <c r="AQ18" s="29">
-        <f t="shared" si="9"/>
-        <v>2648977289885.4585</v>
-      </c>
-      <c r="AR18" s="29">
-        <f t="shared" si="9"/>
-        <v>2716687246490.2554</v>
-      </c>
-      <c r="AS18" s="29">
-        <f t="shared" si="9"/>
-        <v>2845007866903.3779</v>
-      </c>
-      <c r="AT18" s="29">
-        <f t="shared" si="9"/>
-        <v>3011135111593.8521</v>
-      </c>
-      <c r="AU18" s="29">
-        <f t="shared" si="9"/>
-        <v>3171373544131.7471</v>
-      </c>
-      <c r="AV18" s="29">
-        <f t="shared" si="9"/>
-        <v>3219932602131.0752</v>
-      </c>
-      <c r="AW18" s="29">
-        <f t="shared" si="9"/>
-        <v>3225251130738.0522</v>
-      </c>
-      <c r="AX18" s="29">
-        <f t="shared" si="9"/>
-        <v>3222716914921.7153</v>
-      </c>
-      <c r="AY18" s="29">
-        <f t="shared" si="9"/>
-        <v>3213954865484.7549</v>
-      </c>
-      <c r="AZ18" s="29">
-        <f t="shared" si="9"/>
-        <v>3195049069938.0625</v>
-      </c>
-      <c r="BA18" s="29">
-        <f t="shared" si="9"/>
-        <v>3174458084330.7373</v>
-      </c>
-      <c r="BB18" s="29">
-        <f t="shared" si="9"/>
-        <v>3151512261977.52</v>
-      </c>
-      <c r="BC18" s="29">
-        <f t="shared" si="9"/>
-        <v>3127339722452.9282</v>
-      </c>
-      <c r="BD18" s="29">
-        <f t="shared" si="9"/>
-        <v>3104175892863.1279</v>
-      </c>
-      <c r="BE18" s="29">
-        <f t="shared" si="9"/>
-        <v>3079955849219.2788</v>
-      </c>
-      <c r="BF18" s="29">
-        <f t="shared" si="9"/>
-        <v>3061038817882.7339</v>
-      </c>
-      <c r="BG18" s="29">
-        <f t="shared" si="9"/>
-        <v>3041538493756.6245</v>
-      </c>
-      <c r="BH18" s="29">
-        <f t="shared" si="9"/>
-        <v>3024755323387.4917</v>
-      </c>
-      <c r="BI18" s="29">
-        <f t="shared" si="9"/>
-        <v>3020148835243.4976</v>
-      </c>
-      <c r="BJ18" s="29">
-        <f t="shared" si="9"/>
-        <v>3013490638096.4307</v>
-      </c>
-      <c r="BK18" s="29">
-        <f t="shared" si="9"/>
-        <v>3013719034727.7837</v>
-      </c>
-      <c r="BL18" s="29">
-        <f t="shared" si="9"/>
-        <v>3019010740388.1382</v>
-      </c>
-      <c r="BM18" s="29">
-        <f t="shared" si="9"/>
-        <v>3038859216981.9336</v>
-      </c>
-      <c r="BN18" s="29">
-        <f t="shared" si="9"/>
-        <v>3058264719718.5469</v>
-      </c>
-      <c r="BO18" s="29">
-        <f t="shared" ref="BO18:BS18" si="10">BO14/$B$25</f>
-        <v>3076059825363.4639</v>
-      </c>
-      <c r="BP18" s="29">
-        <f t="shared" si="10"/>
-        <v>3091684720097.0825</v>
-      </c>
-      <c r="BQ18" s="29">
-        <f t="shared" si="10"/>
-        <v>3102409800670.7212</v>
-      </c>
-      <c r="BR18" s="29">
-        <f t="shared" si="10"/>
-        <v>3106378265413.1929</v>
-      </c>
-      <c r="BS18" s="29">
-        <f t="shared" si="10"/>
-        <v>3103552383729.7778</v>
+        <v>3103882527629.2021</v>
       </c>
     </row>
     <row r="19" spans="1:71" x14ac:dyDescent="0.2">
@@ -7766,283 +8711,283 @@
       </c>
       <c r="B19" s="29">
         <f>B15/$B$26</f>
-        <v>-78218820339.184998</v>
+        <v>-36734337667.073029</v>
       </c>
       <c r="C19" s="29">
-        <f t="shared" ref="C19:BN19" si="11">C15/$B$26</f>
-        <v>3138587212.8683987</v>
+        <f t="shared" ref="C19:BN19" si="10">C15/$B$26</f>
+        <v>-62026832454.23806</v>
       </c>
       <c r="D19" s="29">
+        <f t="shared" si="10"/>
+        <v>40949753464.933868</v>
+      </c>
+      <c r="E19" s="29">
+        <f t="shared" si="10"/>
+        <v>130075687476.84874</v>
+      </c>
+      <c r="F19" s="29">
+        <f t="shared" si="10"/>
+        <v>214384003434.06552</v>
+      </c>
+      <c r="G19" s="29">
+        <f t="shared" si="10"/>
+        <v>260753577210.53476</v>
+      </c>
+      <c r="H19" s="29">
+        <f t="shared" si="10"/>
+        <v>266775599778.90738</v>
+      </c>
+      <c r="I19" s="29">
+        <f t="shared" si="10"/>
+        <v>345061893167.75153</v>
+      </c>
+      <c r="J19" s="29">
+        <f t="shared" si="10"/>
+        <v>326995825462.63367</v>
+      </c>
+      <c r="K19" s="29">
+        <f t="shared" si="10"/>
+        <v>339039870599.37891</v>
+      </c>
+      <c r="L19" s="29">
+        <f t="shared" si="10"/>
+        <v>459480321966.83142</v>
+      </c>
+      <c r="M19" s="29">
+        <f t="shared" si="10"/>
+        <v>393238073714.73248</v>
+      </c>
+      <c r="N19" s="29">
+        <f t="shared" si="10"/>
+        <v>393238073714.73248</v>
+      </c>
+      <c r="O19" s="29">
+        <f t="shared" si="10"/>
+        <v>357105938304.49677</v>
+      </c>
+      <c r="P19" s="29">
+        <f t="shared" si="10"/>
+        <v>519700547650.55768</v>
+      </c>
+      <c r="Q19" s="29">
+        <f t="shared" si="10"/>
+        <v>399260096283.1051</v>
+      </c>
+      <c r="R19" s="29">
+        <f t="shared" si="10"/>
+        <v>236665486937.04422</v>
+      </c>
+      <c r="S19" s="29">
+        <f t="shared" si="10"/>
+        <v>89125934011.914871</v>
+      </c>
+      <c r="T19" s="29">
+        <f t="shared" si="10"/>
+        <v>40347551208.096603</v>
+      </c>
+      <c r="U19" s="29">
+        <f t="shared" si="10"/>
+        <v>-15055056420.931566</v>
+      </c>
+      <c r="V19" s="29">
+        <f t="shared" si="10"/>
+        <v>-45767371519.631966</v>
+      </c>
+      <c r="W19" s="29">
+        <f t="shared" si="10"/>
+        <v>22281483502.978718</v>
+      </c>
+      <c r="X19" s="29">
+        <f t="shared" si="10"/>
+        <v>122849260394.80159</v>
+      </c>
+      <c r="Y19" s="29">
+        <f t="shared" si="10"/>
+        <v>194511328958.43585</v>
+      </c>
+      <c r="Z19" s="29">
+        <f t="shared" si="10"/>
+        <v>218599419231.92636</v>
+      </c>
+      <c r="AA19" s="29">
+        <f t="shared" si="10"/>
+        <v>230643464368.6716</v>
+      </c>
+      <c r="AB19" s="29">
+        <f t="shared" si="10"/>
+        <v>236665486937.04422</v>
+      </c>
+      <c r="AC19" s="29">
+        <f t="shared" si="10"/>
+        <v>242687509505.41684</v>
+      </c>
+      <c r="AD19" s="29">
+        <f t="shared" si="10"/>
+        <v>242687509505.41684</v>
+      </c>
+      <c r="AE19" s="29">
+        <f t="shared" si="10"/>
+        <v>242687509505.41684</v>
+      </c>
+      <c r="AF19" s="29">
+        <f t="shared" si="10"/>
+        <v>242687509505.41684</v>
+      </c>
+      <c r="AG19" s="29">
+        <f t="shared" si="10"/>
+        <v>236665486937.04422</v>
+      </c>
+      <c r="AH19" s="29">
+        <f t="shared" si="10"/>
+        <v>236665486937.04422</v>
+      </c>
+      <c r="AI19" s="29">
+        <f t="shared" si="10"/>
+        <v>230643464368.6716</v>
+      </c>
+      <c r="AJ19" s="29">
+        <f t="shared" si="10"/>
+        <v>221008228259.27542</v>
+      </c>
+      <c r="AK19" s="29">
+        <f t="shared" si="10"/>
+        <v>213179598920.39102</v>
+      </c>
+      <c r="AL19" s="29">
+        <f t="shared" si="10"/>
+        <v>205350969581.50656</v>
+      </c>
+      <c r="AM19" s="29">
+        <f t="shared" si="10"/>
+        <v>199328947013.13394</v>
+      </c>
+      <c r="AN19" s="29">
+        <f t="shared" si="10"/>
+        <v>184876092849.03964</v>
+      </c>
+      <c r="AO19" s="29">
+        <f t="shared" si="10"/>
+        <v>175843058996.48068</v>
+      </c>
+      <c r="AP19" s="29">
+        <f t="shared" si="10"/>
+        <v>172832047712.2944</v>
+      </c>
+      <c r="AQ19" s="29">
+        <f t="shared" si="10"/>
+        <v>176445261253.31796</v>
+      </c>
+      <c r="AR19" s="29">
+        <f t="shared" si="10"/>
+        <v>182467283821.69058</v>
+      </c>
+      <c r="AS19" s="29">
+        <f t="shared" si="10"/>
+        <v>191500317674.24954</v>
+      </c>
+      <c r="AT19" s="29">
+        <f t="shared" si="10"/>
+        <v>201737756040.48303</v>
+      </c>
+      <c r="AU19" s="29">
+        <f t="shared" si="10"/>
+        <v>209566385379.36743</v>
+      </c>
+      <c r="AV19" s="29">
+        <f t="shared" si="10"/>
+        <v>213179598920.39102</v>
+      </c>
+      <c r="AW19" s="29">
+        <f t="shared" si="10"/>
+        <v>213781801177.22824</v>
+      </c>
+      <c r="AX19" s="29">
+        <f t="shared" si="10"/>
+        <v>213781801177.22824</v>
+      </c>
+      <c r="AY19" s="29">
+        <f t="shared" si="10"/>
+        <v>213179598920.39102</v>
+      </c>
+      <c r="AZ19" s="29">
+        <f t="shared" si="10"/>
+        <v>211975194406.71649</v>
+      </c>
+      <c r="BA19" s="29">
+        <f t="shared" si="10"/>
+        <v>210168587636.20468</v>
+      </c>
+      <c r="BB19" s="29">
+        <f t="shared" si="10"/>
+        <v>208964183122.53015</v>
+      </c>
+      <c r="BC19" s="29">
+        <f t="shared" si="10"/>
+        <v>207157576352.01837</v>
+      </c>
+      <c r="BD19" s="29">
+        <f t="shared" si="10"/>
+        <v>205953171838.34384</v>
+      </c>
+      <c r="BE19" s="29">
+        <f t="shared" si="10"/>
+        <v>204146565067.83203</v>
+      </c>
+      <c r="BF19" s="29">
+        <f t="shared" si="10"/>
+        <v>202942160554.15756</v>
+      </c>
+      <c r="BG19" s="29">
+        <f t="shared" si="10"/>
+        <v>201737756040.48303</v>
+      </c>
+      <c r="BH19" s="29">
+        <f t="shared" si="10"/>
+        <v>200533351526.8085</v>
+      </c>
+      <c r="BI19" s="29">
+        <f t="shared" si="10"/>
+        <v>200533351526.8085</v>
+      </c>
+      <c r="BJ19" s="29">
+        <f t="shared" si="10"/>
+        <v>199931149269.97119</v>
+      </c>
+      <c r="BK19" s="29">
+        <f t="shared" si="10"/>
+        <v>199931149269.97119</v>
+      </c>
+      <c r="BL19" s="29">
+        <f t="shared" si="10"/>
+        <v>200533351526.8085</v>
+      </c>
+      <c r="BM19" s="29">
+        <f t="shared" si="10"/>
+        <v>201737756040.48303</v>
+      </c>
+      <c r="BN19" s="29">
+        <f t="shared" si="10"/>
+        <v>202942160554.15756</v>
+      </c>
+      <c r="BO19" s="29">
+        <f t="shared" ref="BO19:BS19" si="11">BO15/$B$26</f>
+        <v>204146565067.83203</v>
+      </c>
+      <c r="BP19" s="29">
         <f t="shared" si="11"/>
-        <v>-115472872044.78439</v>
-      </c>
-      <c r="E19" s="29">
+        <v>205350969581.50656</v>
+      </c>
+      <c r="BQ19" s="29">
         <f t="shared" si="11"/>
-        <v>211810411823.65738</v>
-      </c>
-      <c r="F19" s="29">
+        <v>205953171838.34384</v>
+      </c>
+      <c r="BR19" s="29">
         <f t="shared" si="11"/>
-        <v>192194345046.38959</v>
-      </c>
-      <c r="G19" s="29">
+        <v>205953171838.34384</v>
+      </c>
+      <c r="BS19" s="29">
         <f t="shared" si="11"/>
-        <v>237613698721.71021</v>
-      </c>
-      <c r="H19" s="29">
-        <f t="shared" si="11"/>
-        <v>318301037748.10388</v>
-      </c>
-      <c r="I19" s="29">
-        <f t="shared" si="11"/>
-        <v>241137470570.41806</v>
-      </c>
-      <c r="J19" s="29">
-        <f t="shared" si="11"/>
-        <v>466039199591.14417</v>
-      </c>
-      <c r="K19" s="29">
-        <f t="shared" si="11"/>
-        <v>241631057355.63934</v>
-      </c>
-      <c r="L19" s="29">
-        <f t="shared" si="11"/>
-        <v>358005019051.71899</v>
-      </c>
-      <c r="M19" s="29">
-        <f t="shared" si="11"/>
-        <v>680456099084.55859</v>
-      </c>
-      <c r="N19" s="29">
-        <f t="shared" si="11"/>
-        <v>142746059496.41565</v>
-      </c>
-      <c r="O19" s="29">
-        <f t="shared" si="11"/>
-        <v>462445671856.40015</v>
-      </c>
-      <c r="P19" s="29">
-        <f t="shared" si="11"/>
-        <v>376985198265.67188</v>
-      </c>
-      <c r="Q19" s="29">
-        <f t="shared" si="11"/>
-        <v>694775374064.27332</v>
-      </c>
-      <c r="R19" s="29">
-        <f t="shared" si="11"/>
-        <v>124190192751.97963</v>
-      </c>
-      <c r="S19" s="29">
-        <f t="shared" si="11"/>
-        <v>85881611095.435287</v>
-      </c>
-      <c r="T19" s="29">
-        <f t="shared" si="11"/>
-        <v>72434580058.70723</v>
-      </c>
-      <c r="U19" s="29">
-        <f t="shared" si="11"/>
-        <v>-15572282890.307613</v>
-      </c>
-      <c r="V19" s="29">
-        <f t="shared" si="11"/>
-        <v>-64755531979.938339</v>
-      </c>
-      <c r="W19" s="29">
-        <f t="shared" si="11"/>
-        <v>-44745340915.320213</v>
-      </c>
-      <c r="X19" s="29">
-        <f t="shared" si="11"/>
-        <v>136324078103.28555</v>
-      </c>
-      <c r="Y19" s="29">
-        <f t="shared" si="11"/>
-        <v>205536732336.03665</v>
-      </c>
-      <c r="Z19" s="29">
-        <f t="shared" si="11"/>
-        <v>217873930278.43762</v>
-      </c>
-      <c r="AA19" s="29">
-        <f t="shared" si="11"/>
-        <v>227210249542.15802</v>
-      </c>
-      <c r="AB19" s="29">
-        <f t="shared" si="11"/>
-        <v>242109515698.11209</v>
-      </c>
-      <c r="AC19" s="29">
-        <f t="shared" si="11"/>
-        <v>243426868040.47958</v>
-      </c>
-      <c r="AD19" s="29">
-        <f t="shared" si="11"/>
-        <v>245654369040.22278</v>
-      </c>
-      <c r="AE19" s="29">
-        <f t="shared" si="11"/>
-        <v>246003963401.89709</v>
-      </c>
-      <c r="AF19" s="29">
-        <f t="shared" si="11"/>
-        <v>242860612343.36649</v>
-      </c>
-      <c r="AG19" s="29">
-        <f t="shared" si="11"/>
-        <v>242935531550.8858</v>
-      </c>
-      <c r="AH19" s="29">
-        <f t="shared" si="11"/>
-        <v>233235372070.87466</v>
-      </c>
-      <c r="AI19" s="29">
-        <f t="shared" si="11"/>
-        <v>232870342275.88489</v>
-      </c>
-      <c r="AJ19" s="29">
-        <f t="shared" si="11"/>
-        <v>227429704155.19644</v>
-      </c>
-      <c r="AK19" s="29">
-        <f t="shared" si="11"/>
-        <v>207732904375.65897</v>
-      </c>
-      <c r="AL19" s="29">
-        <f t="shared" si="11"/>
-        <v>210558419370.40875</v>
-      </c>
-      <c r="AM19" s="29">
-        <f t="shared" si="11"/>
-        <v>199606799697.10474</v>
-      </c>
-      <c r="AN19" s="29">
-        <f t="shared" si="11"/>
-        <v>191894695411.51477</v>
-      </c>
-      <c r="AO19" s="29">
-        <f t="shared" si="11"/>
-        <v>170030318078.7861</v>
-      </c>
-      <c r="AP19" s="29">
-        <f t="shared" si="11"/>
-        <v>172023367006.03854</v>
-      </c>
-      <c r="AQ19" s="29">
-        <f t="shared" si="11"/>
-        <v>175768660741.28207</v>
-      </c>
-      <c r="AR19" s="29">
-        <f t="shared" si="11"/>
-        <v>180261446857.9158</v>
-      </c>
-      <c r="AS19" s="29">
-        <f t="shared" si="11"/>
-        <v>188775956846.96906</v>
-      </c>
-      <c r="AT19" s="29">
-        <f t="shared" si="11"/>
-        <v>199799065056.83463</v>
-      </c>
-      <c r="AU19" s="29">
-        <f t="shared" si="11"/>
-        <v>210431430533.88483</v>
-      </c>
-      <c r="AV19" s="29">
-        <f t="shared" si="11"/>
-        <v>213653489335.21533</v>
-      </c>
-      <c r="AW19" s="29">
-        <f t="shared" si="11"/>
-        <v>214006391813.44046</v>
-      </c>
-      <c r="AX19" s="29">
-        <f t="shared" si="11"/>
-        <v>213838237967.13617</v>
-      </c>
-      <c r="AY19" s="29">
-        <f t="shared" si="11"/>
-        <v>213256846159.52652</v>
-      </c>
-      <c r="AZ19" s="29">
-        <f t="shared" si="11"/>
-        <v>212002382266.54453</v>
-      </c>
-      <c r="BA19" s="29">
-        <f t="shared" si="11"/>
-        <v>210636100276.37347</v>
-      </c>
-      <c r="BB19" s="29">
-        <f t="shared" si="11"/>
-        <v>209113566851.85822</v>
-      </c>
-      <c r="BC19" s="29">
-        <f t="shared" si="11"/>
-        <v>207509636567.07388</v>
-      </c>
-      <c r="BD19" s="29">
-        <f t="shared" si="11"/>
-        <v>205972637620.27866</v>
-      </c>
-      <c r="BE19" s="29">
-        <f t="shared" si="11"/>
-        <v>204365555275.46973</v>
-      </c>
-      <c r="BF19" s="29">
-        <f t="shared" si="11"/>
-        <v>203110345849.58252</v>
-      </c>
-      <c r="BG19" s="29">
-        <f t="shared" si="11"/>
-        <v>201816432961.48245</v>
-      </c>
-      <c r="BH19" s="29">
-        <f t="shared" si="11"/>
-        <v>200702812474.79913</v>
-      </c>
-      <c r="BI19" s="29">
-        <f t="shared" si="11"/>
-        <v>200397156305.19666</v>
-      </c>
-      <c r="BJ19" s="29">
-        <f t="shared" si="11"/>
-        <v>199955362258.88309</v>
-      </c>
-      <c r="BK19" s="29">
-        <f t="shared" si="11"/>
-        <v>199970517152.87326</v>
-      </c>
-      <c r="BL19" s="29">
-        <f t="shared" si="11"/>
-        <v>200321639837.28018</v>
-      </c>
-      <c r="BM19" s="29">
-        <f t="shared" si="11"/>
-        <v>201638653826.77991</v>
-      </c>
-      <c r="BN19" s="29">
-        <f t="shared" si="11"/>
-        <v>202926274992.89914</v>
-      </c>
-      <c r="BO19" s="29">
-        <f t="shared" ref="BO19:BS19" si="12">BO15/$B$26</f>
-        <v>204107040829.92596</v>
-      </c>
-      <c r="BP19" s="29">
-        <f t="shared" si="12"/>
-        <v>205143805785.23083</v>
-      </c>
-      <c r="BQ19" s="29">
-        <f t="shared" si="12"/>
-        <v>205855451391.24219</v>
-      </c>
-      <c r="BR19" s="29">
-        <f t="shared" si="12"/>
-        <v>206118772536.2164</v>
-      </c>
-      <c r="BS19" s="29">
-        <f t="shared" si="12"/>
-        <v>205931265666.75253</v>
+        <v>205953171838.34384</v>
       </c>
     </row>
     <row r="20" spans="1:71" x14ac:dyDescent="0.2">
@@ -8935,7 +9880,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C71DDFC0-D0C3-F44E-A71C-CAD2C075BB35}">
   <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9514,7 +10459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2FFCF5-0EE5-E84B-A49F-5F2EF30FC797}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9523,7 +10468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F60411-ADAC-D94F-9CA3-BD5BA5358F0E}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -9698,207 +10643,207 @@
       </c>
       <c r="B2" s="24">
         <f>'Global Watch Data'!U17</f>
-        <v>-15161000005483.406</v>
+        <v>-14657434114709.154</v>
       </c>
       <c r="C2" s="24">
         <f>'Global Watch Data'!V17</f>
-        <v>-63045259813125.086</v>
+        <v>-44558599708715.828</v>
       </c>
       <c r="D2" s="24">
         <f>'Global Watch Data'!W17</f>
-        <v>-43563562172683.203</v>
+        <v>21693002489769.547</v>
       </c>
       <c r="E2" s="24">
         <f>'Global Watch Data'!X17</f>
-        <v>132723593799971.42</v>
+        <v>119604662376026.69</v>
       </c>
       <c r="F2" s="24">
         <f>'Global Watch Data'!Y17</f>
-        <v>200108257859431.75</v>
+        <v>189374048762042.25</v>
       </c>
       <c r="G2" s="24">
         <f>'Global Watch Data'!Z17</f>
-        <v>212119615435578.12</v>
+        <v>212825943345576.91</v>
       </c>
       <c r="H2" s="24">
         <f>'Global Watch Data'!AA17</f>
-        <v>221209351179883.25</v>
+        <v>224551890637344.22</v>
       </c>
       <c r="I2" s="24">
         <f>'Global Watch Data'!AB17</f>
-        <v>235715109639531.69</v>
+        <v>230414864283227.91</v>
       </c>
       <c r="J2" s="24">
         <f>'Global Watch Data'!AC17</f>
-        <v>236997669108207.12</v>
+        <v>236277837929111.53</v>
       </c>
       <c r="K2" s="24">
         <f>'Global Watch Data'!AD17</f>
-        <v>239166339103943</v>
+        <v>236277837929111.53</v>
       </c>
       <c r="L2" s="24">
         <f>'Global Watch Data'!AE17</f>
-        <v>239506700254366.22</v>
+        <v>236277837929111.53</v>
       </c>
       <c r="M2" s="24">
         <f>'Global Watch Data'!AF17</f>
-        <v>236446368911087</v>
+        <v>236277837929111.53</v>
       </c>
       <c r="N2" s="24">
         <f>'Global Watch Data'!AG17</f>
-        <v>236519309411437.03</v>
+        <v>230414864283227.91</v>
       </c>
       <c r="O2" s="24">
         <f>'Global Watch Data'!AH17</f>
-        <v>227075342912397.09</v>
+        <v>230414864283227.91</v>
       </c>
       <c r="P2" s="24">
         <f>'Global Watch Data'!AI17</f>
-        <v>226719953997179.91</v>
+        <v>224551890637344.22</v>
       </c>
       <c r="Q2" s="24">
         <f>'Global Watch Data'!AJ17</f>
-        <v>221423009730329.28</v>
+        <v>215171132803930.38</v>
       </c>
       <c r="R2" s="24">
         <f>'Global Watch Data'!AK17</f>
-        <v>202246426330894.59</v>
+        <v>207549267064281.62</v>
       </c>
       <c r="S2" s="24">
         <f>'Global Watch Data'!AL17</f>
-        <v>204997316046464.69</v>
+        <v>199927401324632.84</v>
       </c>
       <c r="T2" s="24">
         <f>'Global Watch Data'!AM17</f>
-        <v>194334941936220.5</v>
+        <v>194064427678749.19</v>
       </c>
       <c r="U2" s="24">
         <f>'Global Watch Data'!AN17</f>
-        <v>186826523681830.03</v>
+        <v>179993290928628.38</v>
       </c>
       <c r="V2" s="24">
         <f>'Global Watch Data'!AO17</f>
-        <v>165539611082283.59</v>
+        <v>171198830459802.91</v>
       </c>
       <c r="W2" s="24">
         <f>'Global Watch Data'!AP17</f>
-        <v>167480021169221.47</v>
+        <v>168267343636861.09</v>
       </c>
       <c r="X2" s="24">
         <f>'Global Watch Data'!AQ17</f>
-        <v>171126397152790.69</v>
+        <v>171785127824391.28</v>
       </c>
       <c r="Y2" s="24">
         <f>'Global Watch Data'!AR17</f>
-        <v>175500523337032.78</v>
+        <v>177648101470274.94</v>
       </c>
       <c r="Z2" s="24">
         <f>'Global Watch Data'!AS17</f>
-        <v>183790154786707.5</v>
+        <v>186442561939100.41</v>
       </c>
       <c r="AA2" s="24">
         <f>'Global Watch Data'!AT17</f>
-        <v>194522129334526.38</v>
+        <v>196409617137102.66</v>
       </c>
       <c r="AB2" s="24">
         <f>'Global Watch Data'!AU17</f>
-        <v>204873681139187.59</v>
+        <v>204031482876751.44</v>
       </c>
       <c r="AC2" s="24">
         <f>'Global Watch Data'!AV17</f>
-        <v>208010641458284.06</v>
+        <v>207549267064281.62</v>
       </c>
       <c r="AD2" s="24">
         <f>'Global Watch Data'!AW17</f>
-        <v>208354223353886.31</v>
+        <v>208135564428869.97</v>
       </c>
       <c r="AE2" s="24">
         <f>'Global Watch Data'!AX17</f>
-        <v>208190510654682.22</v>
+        <v>208135564428869.97</v>
       </c>
       <c r="AF2" s="24">
         <f>'Global Watch Data'!AY17</f>
-        <v>207624474110108.28</v>
+        <v>207549267064281.62</v>
       </c>
       <c r="AG2" s="24">
         <f>'Global Watch Data'!AZ17</f>
-        <v>206403142130568.12</v>
+        <v>206376672335104.88</v>
       </c>
       <c r="AH2" s="24">
         <f>'Global Watch Data'!BA17</f>
-        <v>205072945305453.41</v>
+        <v>204617780241339.78</v>
       </c>
       <c r="AI2" s="24">
         <f>'Global Watch Data'!BB17</f>
-        <v>203590623835953.84</v>
+        <v>203445185512163.03</v>
       </c>
       <c r="AJ2" s="24">
         <f>'Global Watch Data'!BC17</f>
-        <v>202029055296022.84</v>
+        <v>201686293418397.94</v>
       </c>
       <c r="AK2" s="24">
         <f>'Global Watch Data'!BD17</f>
-        <v>200532650356237.5</v>
+        <v>200513698689221.22</v>
       </c>
       <c r="AL2" s="24">
         <f>'Global Watch Data'!BE17</f>
-        <v>198968013006011.53</v>
+        <v>198754806595456.12</v>
       </c>
       <c r="AM2" s="24">
         <f>'Global Watch Data'!BF17</f>
-        <v>197745955183994.72</v>
+        <v>197582211866279.41</v>
       </c>
       <c r="AN2" s="24">
         <f>'Global Watch Data'!BG17</f>
-        <v>196486216105160.62</v>
+        <v>196409617137102.66</v>
       </c>
       <c r="AO2" s="24">
         <f>'Global Watch Data'!BH17</f>
-        <v>195402007686674.94</v>
+        <v>195237022407925.91</v>
       </c>
       <c r="AP2" s="24">
         <f>'Global Watch Data'!BI17</f>
-        <v>195104424267361.12</v>
+        <v>195237022407925.91</v>
       </c>
       <c r="AQ2" s="24">
         <f>'Global Watch Data'!BJ17</f>
-        <v>194674298537834.88</v>
+        <v>194650725043337.56</v>
       </c>
       <c r="AR2" s="24">
         <f>'Global Watch Data'!BK17</f>
-        <v>194689053172687.53</v>
+        <v>194650725043337.56</v>
       </c>
       <c r="AS2" s="24">
         <f>'Global Watch Data'!BL17</f>
-        <v>195030902280985.72</v>
+        <v>195237022407925.91</v>
       </c>
       <c r="AT2" s="24">
         <f>'Global Watch Data'!BM17</f>
-        <v>196313132333103.16</v>
+        <v>196409617137102.66</v>
       </c>
       <c r="AU2" s="24">
         <f>'Global Watch Data'!BN17</f>
-        <v>197566745861967.62</v>
+        <v>197582211866279.41</v>
       </c>
       <c r="AV2" s="24">
         <f>'Global Watch Data'!BO17</f>
-        <v>198716326240627.5</v>
+        <v>198754806595456.12</v>
       </c>
       <c r="AW2" s="24">
         <f>'Global Watch Data'!BP17</f>
-        <v>199725708975566.47</v>
+        <v>199927401324632.84</v>
       </c>
       <c r="AX2" s="24">
         <f>'Global Watch Data'!BQ17</f>
-        <v>200418559157690.72</v>
+        <v>200513698689221.22</v>
       </c>
       <c r="AY2" s="24">
         <f>'Global Watch Data'!BR17</f>
-        <v>200674925671741.34</v>
+        <v>200513698689221.22</v>
       </c>
       <c r="AZ2" s="24">
         <f>'Global Watch Data'!BS17</f>
-        <v>200492371086200.19</v>
+        <v>200513698689221.22</v>
       </c>
     </row>
     <row r="3" spans="1:52" x14ac:dyDescent="0.2">
@@ -11171,207 +12116,207 @@
       </c>
       <c r="B11" s="27">
         <f>'Global Watch Data'!U18</f>
-        <v>-234687023011.53958</v>
+        <v>-226891997633.71359</v>
       </c>
       <c r="C11" s="27">
         <f>'Global Watch Data'!V18</f>
-        <v>-975918760977.50964</v>
+        <v>-689751672806.48926</v>
       </c>
       <c r="D11" s="27">
         <f>'Global Watch Data'!W18</f>
-        <v>-674348836777.74622</v>
+        <v>335800156497.89612</v>
       </c>
       <c r="E11" s="27">
         <f>'Global Watch Data'!X18</f>
-        <v>2054515210147.2454</v>
+        <v>1851438700691.103</v>
       </c>
       <c r="F11" s="27">
         <f>'Global Watch Data'!Y18</f>
-        <v>3097606444170.5771</v>
+        <v>2931444609427.5791</v>
       </c>
       <c r="G11" s="27">
         <f>'Global Watch Data'!Z18</f>
-        <v>3283538094513.7842</v>
+        <v>3294471805641.521</v>
       </c>
       <c r="H11" s="27">
         <f>'Global Watch Data'!AA18</f>
-        <v>3424244051971.8013</v>
+        <v>3475985403748.4922</v>
       </c>
       <c r="I11" s="27">
         <f>'Global Watch Data'!AB18</f>
-        <v>3648788163058.6743</v>
+        <v>3566742202801.9775</v>
       </c>
       <c r="J11" s="27">
         <f>'Global Watch Data'!AC18</f>
-        <v>3668641738906.563</v>
+        <v>3657499001855.4624</v>
       </c>
       <c r="K11" s="27">
         <f>'Global Watch Data'!AD18</f>
-        <v>3702211998454.7202</v>
+        <v>3657499001855.4624</v>
       </c>
       <c r="L11" s="27">
         <f>'Global Watch Data'!AE18</f>
-        <v>3707480671043.1201</v>
+        <v>3657499001855.4624</v>
       </c>
       <c r="M11" s="27">
         <f>'Global Watch Data'!AF18</f>
-        <v>3660107803018.3628</v>
+        <v>3657499001855.4624</v>
       </c>
       <c r="N11" s="27">
         <f>'Global Watch Data'!AG18</f>
-        <v>3661236896671.6792</v>
+        <v>3566742202801.9775</v>
       </c>
       <c r="O11" s="27">
         <f>'Global Watch Data'!AH18</f>
-        <v>3515047569959.8013</v>
+        <v>3566742202801.9775</v>
       </c>
       <c r="P11" s="27">
         <f>'Global Watch Data'!AI18</f>
-        <v>3509546272783.2656</v>
+        <v>3475985403748.4922</v>
       </c>
       <c r="Q11" s="27">
         <f>'Global Watch Data'!AJ18</f>
-        <v>3427551412246.6514</v>
+        <v>3330774525262.9155</v>
       </c>
       <c r="R11" s="27">
         <f>'Global Watch Data'!AK18</f>
-        <v>3130704550699.3857</v>
+        <v>3212790686493.3843</v>
       </c>
       <c r="S11" s="27">
         <f>'Global Watch Data'!AL18</f>
-        <v>3173287369626.0195</v>
+        <v>3094806847723.853</v>
       </c>
       <c r="T11" s="27">
         <f>'Global Watch Data'!AM18</f>
-        <v>3008237515575.2656</v>
+        <v>3004050048670.3677</v>
       </c>
       <c r="U11" s="27">
         <f>'Global Watch Data'!AN18</f>
-        <v>2892009804539.6431</v>
+        <v>2786233730942.0029</v>
       </c>
       <c r="V11" s="27">
         <f>'Global Watch Data'!AO18</f>
-        <v>2562495778730.8228</v>
+        <v>2650098532361.7744</v>
       </c>
       <c r="W11" s="27">
         <f>'Global Watch Data'!AP18</f>
-        <v>2592532654039.8594</v>
+        <v>2604720132835.0322</v>
       </c>
       <c r="X11" s="27">
         <f>'Global Watch Data'!AQ18</f>
-        <v>2648977289885.4585</v>
+        <v>2659174212267.1235</v>
       </c>
       <c r="Y11" s="27">
         <f>'Global Watch Data'!AR18</f>
-        <v>2716687246490.2554</v>
+        <v>2749931011320.6084</v>
       </c>
       <c r="Z11" s="27">
         <f>'Global Watch Data'!AS18</f>
-        <v>2845007866903.3779</v>
+        <v>2886066209900.8369</v>
       </c>
       <c r="AA11" s="27">
         <f>'Global Watch Data'!AT18</f>
-        <v>3011135111593.8521</v>
+        <v>3040352768291.7617</v>
       </c>
       <c r="AB11" s="27">
         <f>'Global Watch Data'!AU18</f>
-        <v>3171373544131.7471</v>
+        <v>3158336607061.293</v>
       </c>
       <c r="AC11" s="27">
         <f>'Global Watch Data'!AV18</f>
-        <v>3219932602131.0752</v>
+        <v>3212790686493.3843</v>
       </c>
       <c r="AD11" s="27">
         <f>'Global Watch Data'!AW18</f>
-        <v>3225251130738.0522</v>
+        <v>3221866366398.7334</v>
       </c>
       <c r="AE11" s="27">
         <f>'Global Watch Data'!AX18</f>
-        <v>3222716914921.7153</v>
+        <v>3221866366398.7334</v>
       </c>
       <c r="AF11" s="27">
         <f>'Global Watch Data'!AY18</f>
-        <v>3213954865484.7549</v>
+        <v>3212790686493.3843</v>
       </c>
       <c r="AG11" s="27">
         <f>'Global Watch Data'!AZ18</f>
-        <v>3195049069938.0625</v>
+        <v>3194639326682.6875</v>
       </c>
       <c r="AH11" s="27">
         <f>'Global Watch Data'!BA18</f>
-        <v>3174458084330.7373</v>
+        <v>3167412286966.6416</v>
       </c>
       <c r="AI11" s="27">
         <f>'Global Watch Data'!BB18</f>
-        <v>3151512261977.52</v>
+        <v>3149260927155.9443</v>
       </c>
       <c r="AJ11" s="27">
         <f>'Global Watch Data'!BC18</f>
-        <v>3127339722452.9282</v>
+        <v>3122033887439.8989</v>
       </c>
       <c r="AK11" s="27">
         <f>'Global Watch Data'!BD18</f>
-        <v>3104175892863.1279</v>
+        <v>3103882527629.2021</v>
       </c>
       <c r="AL11" s="27">
         <f>'Global Watch Data'!BE18</f>
-        <v>3079955849219.2788</v>
+        <v>3076655487913.1562</v>
       </c>
       <c r="AM11" s="27">
         <f>'Global Watch Data'!BF18</f>
-        <v>3061038817882.7339</v>
+        <v>3058504128102.4595</v>
       </c>
       <c r="AN11" s="27">
         <f>'Global Watch Data'!BG18</f>
-        <v>3041538493756.6245</v>
+        <v>3040352768291.7617</v>
       </c>
       <c r="AO11" s="27">
         <f>'Global Watch Data'!BH18</f>
-        <v>3024755323387.4917</v>
+        <v>3022201408481.0654</v>
       </c>
       <c r="AP11" s="27">
         <f>'Global Watch Data'!BI18</f>
-        <v>3020148835243.4976</v>
+        <v>3022201408481.0654</v>
       </c>
       <c r="AQ11" s="27">
         <f>'Global Watch Data'!BJ18</f>
-        <v>3013490638096.4307</v>
+        <v>3013125728575.7163</v>
       </c>
       <c r="AR11" s="27">
         <f>'Global Watch Data'!BK18</f>
-        <v>3013719034727.7837</v>
+        <v>3013125728575.7163</v>
       </c>
       <c r="AS11" s="27">
         <f>'Global Watch Data'!BL18</f>
-        <v>3019010740388.1382</v>
+        <v>3022201408481.0654</v>
       </c>
       <c r="AT11" s="27">
         <f>'Global Watch Data'!BM18</f>
-        <v>3038859216981.9336</v>
+        <v>3040352768291.7617</v>
       </c>
       <c r="AU11" s="27">
         <f>'Global Watch Data'!BN18</f>
-        <v>3058264719718.5469</v>
+        <v>3058504128102.4595</v>
       </c>
       <c r="AV11" s="27">
         <f>'Global Watch Data'!BO18</f>
-        <v>3076059825363.4639</v>
+        <v>3076655487913.1562</v>
       </c>
       <c r="AW11" s="27">
         <f>'Global Watch Data'!BP18</f>
-        <v>3091684720097.0825</v>
+        <v>3094806847723.853</v>
       </c>
       <c r="AX11" s="27">
         <f>'Global Watch Data'!BQ18</f>
-        <v>3102409800670.7212</v>
+        <v>3103882527629.2021</v>
       </c>
       <c r="AY11" s="27">
         <f>'Global Watch Data'!BR18</f>
-        <v>3106378265413.1929</v>
+        <v>3103882527629.2021</v>
       </c>
       <c r="AZ11" s="27">
         <f>'Global Watch Data'!BS18</f>
-        <v>3103552383729.7778</v>
+        <v>3103882527629.2021</v>
       </c>
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.2">
@@ -11380,207 +12325,207 @@
       </c>
       <c r="B12" s="27">
         <f>'Global Watch Data'!U19</f>
-        <v>-15572282890.307613</v>
+        <v>-15055056420.931566</v>
       </c>
       <c r="C12" s="27">
         <f>'Global Watch Data'!V19</f>
-        <v>-64755531979.938339</v>
+        <v>-45767371519.631966</v>
       </c>
       <c r="D12" s="27">
         <f>'Global Watch Data'!W19</f>
-        <v>-44745340915.320213</v>
+        <v>22281483502.978718</v>
       </c>
       <c r="E12" s="27">
         <f>'Global Watch Data'!X19</f>
-        <v>136324078103.28555</v>
+        <v>122849260394.80159</v>
       </c>
       <c r="F12" s="27">
         <f>'Global Watch Data'!Y19</f>
-        <v>205536732336.03665</v>
+        <v>194511328958.43585</v>
       </c>
       <c r="G12" s="27">
         <f>'Global Watch Data'!Z19</f>
-        <v>217873930278.43762</v>
+        <v>218599419231.92636</v>
       </c>
       <c r="H12" s="27">
         <f>'Global Watch Data'!AA19</f>
-        <v>227210249542.15802</v>
+        <v>230643464368.6716</v>
       </c>
       <c r="I12" s="27">
         <f>'Global Watch Data'!AB19</f>
-        <v>242109515698.11209</v>
+        <v>236665486937.04422</v>
       </c>
       <c r="J12" s="27">
         <f>'Global Watch Data'!AC19</f>
-        <v>243426868040.47958</v>
+        <v>242687509505.41684</v>
       </c>
       <c r="K12" s="27">
         <f>'Global Watch Data'!AD19</f>
-        <v>245654369040.22278</v>
+        <v>242687509505.41684</v>
       </c>
       <c r="L12" s="27">
         <f>'Global Watch Data'!AE19</f>
-        <v>246003963401.89709</v>
+        <v>242687509505.41684</v>
       </c>
       <c r="M12" s="27">
         <f>'Global Watch Data'!AF19</f>
-        <v>242860612343.36649</v>
+        <v>242687509505.41684</v>
       </c>
       <c r="N12" s="27">
         <f>'Global Watch Data'!AG19</f>
-        <v>242935531550.8858</v>
+        <v>236665486937.04422</v>
       </c>
       <c r="O12" s="27">
         <f>'Global Watch Data'!AH19</f>
-        <v>233235372070.87466</v>
+        <v>236665486937.04422</v>
       </c>
       <c r="P12" s="27">
         <f>'Global Watch Data'!AI19</f>
-        <v>232870342275.88489</v>
+        <v>230643464368.6716</v>
       </c>
       <c r="Q12" s="27">
         <f>'Global Watch Data'!AJ19</f>
-        <v>227429704155.19644</v>
+        <v>221008228259.27542</v>
       </c>
       <c r="R12" s="27">
         <f>'Global Watch Data'!AK19</f>
-        <v>207732904375.65897</v>
+        <v>213179598920.39102</v>
       </c>
       <c r="S12" s="27">
         <f>'Global Watch Data'!AL19</f>
-        <v>210558419370.40875</v>
+        <v>205350969581.50656</v>
       </c>
       <c r="T12" s="27">
         <f>'Global Watch Data'!AM19</f>
-        <v>199606799697.10474</v>
+        <v>199328947013.13394</v>
       </c>
       <c r="U12" s="27">
         <f>'Global Watch Data'!AN19</f>
-        <v>191894695411.51477</v>
+        <v>184876092849.03964</v>
       </c>
       <c r="V12" s="27">
         <f>'Global Watch Data'!AO19</f>
-        <v>170030318078.7861</v>
+        <v>175843058996.48068</v>
       </c>
       <c r="W12" s="27">
         <f>'Global Watch Data'!AP19</f>
-        <v>172023367006.03854</v>
+        <v>172832047712.2944</v>
       </c>
       <c r="X12" s="27">
         <f>'Global Watch Data'!AQ19</f>
-        <v>175768660741.28207</v>
+        <v>176445261253.31796</v>
       </c>
       <c r="Y12" s="27">
         <f>'Global Watch Data'!AR19</f>
-        <v>180261446857.9158</v>
+        <v>182467283821.69058</v>
       </c>
       <c r="Z12" s="27">
         <f>'Global Watch Data'!AS19</f>
-        <v>188775956846.96906</v>
+        <v>191500317674.24954</v>
       </c>
       <c r="AA12" s="27">
         <f>'Global Watch Data'!AT19</f>
-        <v>199799065056.83463</v>
+        <v>201737756040.48303</v>
       </c>
       <c r="AB12" s="27">
         <f>'Global Watch Data'!AU19</f>
-        <v>210431430533.88483</v>
+        <v>209566385379.36743</v>
       </c>
       <c r="AC12" s="27">
         <f>'Global Watch Data'!AV19</f>
-        <v>213653489335.21533</v>
+        <v>213179598920.39102</v>
       </c>
       <c r="AD12" s="27">
         <f>'Global Watch Data'!AW19</f>
-        <v>214006391813.44046</v>
+        <v>213781801177.22824</v>
       </c>
       <c r="AE12" s="27">
         <f>'Global Watch Data'!AX19</f>
-        <v>213838237967.13617</v>
+        <v>213781801177.22824</v>
       </c>
       <c r="AF12" s="27">
         <f>'Global Watch Data'!AY19</f>
-        <v>213256846159.52652</v>
+        <v>213179598920.39102</v>
       </c>
       <c r="AG12" s="27">
         <f>'Global Watch Data'!AZ19</f>
-        <v>212002382266.54453</v>
+        <v>211975194406.71649</v>
       </c>
       <c r="AH12" s="27">
         <f>'Global Watch Data'!BA19</f>
-        <v>210636100276.37347</v>
+        <v>210168587636.20468</v>
       </c>
       <c r="AI12" s="27">
         <f>'Global Watch Data'!BB19</f>
-        <v>209113566851.85822</v>
+        <v>208964183122.53015</v>
       </c>
       <c r="AJ12" s="27">
         <f>'Global Watch Data'!BC19</f>
-        <v>207509636567.07388</v>
+        <v>207157576352.01837</v>
       </c>
       <c r="AK12" s="27">
         <f>'Global Watch Data'!BD19</f>
-        <v>205972637620.27866</v>
+        <v>205953171838.34384</v>
       </c>
       <c r="AL12" s="27">
         <f>'Global Watch Data'!BE19</f>
-        <v>204365555275.46973</v>
+        <v>204146565067.83203</v>
       </c>
       <c r="AM12" s="27">
         <f>'Global Watch Data'!BF19</f>
-        <v>203110345849.58252</v>
+        <v>202942160554.15756</v>
       </c>
       <c r="AN12" s="27">
         <f>'Global Watch Data'!BG19</f>
-        <v>201816432961.48245</v>
+        <v>201737756040.48303</v>
       </c>
       <c r="AO12" s="27">
         <f>'Global Watch Data'!BH19</f>
-        <v>200702812474.79913</v>
+        <v>200533351526.8085</v>
       </c>
       <c r="AP12" s="27">
         <f>'Global Watch Data'!BI19</f>
-        <v>200397156305.19666</v>
+        <v>200533351526.8085</v>
       </c>
       <c r="AQ12" s="27">
         <f>'Global Watch Data'!BJ19</f>
-        <v>199955362258.88309</v>
+        <v>199931149269.97119</v>
       </c>
       <c r="AR12" s="27">
         <f>'Global Watch Data'!BK19</f>
-        <v>199970517152.87326</v>
+        <v>199931149269.97119</v>
       </c>
       <c r="AS12" s="27">
         <f>'Global Watch Data'!BL19</f>
-        <v>200321639837.28018</v>
+        <v>200533351526.8085</v>
       </c>
       <c r="AT12" s="27">
         <f>'Global Watch Data'!BM19</f>
-        <v>201638653826.77991</v>
+        <v>201737756040.48303</v>
       </c>
       <c r="AU12" s="27">
         <f>'Global Watch Data'!BN19</f>
-        <v>202926274992.89914</v>
+        <v>202942160554.15756</v>
       </c>
       <c r="AV12" s="27">
         <f>'Global Watch Data'!BO19</f>
-        <v>204107040829.92596</v>
+        <v>204146565067.83203</v>
       </c>
       <c r="AW12" s="27">
         <f>'Global Watch Data'!BP19</f>
-        <v>205143805785.23083</v>
+        <v>205350969581.50656</v>
       </c>
       <c r="AX12" s="27">
         <f>'Global Watch Data'!BQ19</f>
-        <v>205855451391.24219</v>
+        <v>205953171838.34384</v>
       </c>
       <c r="AY12" s="27">
         <f>'Global Watch Data'!BR19</f>
-        <v>206118772536.2164</v>
+        <v>205953171838.34384</v>
       </c>
       <c r="AZ12" s="27">
         <f>'Global Watch Data'!BS19</f>
-        <v>205931265666.75253</v>
+        <v>205953171838.34384</v>
       </c>
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.2">

--- a/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
+++ b/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/land/BLAPE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7D5D32-E1E0-D84B-BD61-DE1144AF335A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CF161F-5235-DC43-9FE3-FDC7489E1C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1394,7 +1394,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>376</c:v>
+                  <c:v>336</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>326</c:v>
@@ -7623,7 +7623,7 @@
         <v>818.65</v>
       </c>
       <c r="V12">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="W12">
         <v>326</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="B21">
         <f>V12</f>
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="C21">
         <f t="shared" ref="C21:D21" si="43">W12</f>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="B81">
         <f>B21</f>
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="C81">
         <f t="shared" ref="C81:AZ81" si="46">C21</f>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="B2" s="37">
         <f>'GWF-Smoothing '!B81</f>
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="C2" s="37">
         <f>'GWF-Smoothing '!C81</f>
@@ -11720,10 +11720,10 @@
       </c>
       <c r="B4" s="37">
         <f>B2*$B$3</f>
-        <v>376000000</v>
+        <v>336000000</v>
       </c>
       <c r="C4" s="37">
-        <f t="shared" ref="C4:BN4" si="0">C2*$B$3</f>
+        <f t="shared" ref="C4:AZ4" si="0">C2*$B$3</f>
         <v>326000000</v>
       </c>
       <c r="D4" s="37">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="B5" s="29">
         <f>B4*'Share of Pollutants'!$B$19</f>
-        <v>220447809.08522567</v>
+        <v>196995914.50169101</v>
       </c>
       <c r="C5" s="29">
         <f>C4*'Share of Pollutants'!$B$19</f>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="B6" s="29">
         <f>B4*'Share of Pollutants'!$B$20</f>
-        <v>95548758.043509468</v>
+        <v>85383996.549519092</v>
       </c>
       <c r="C6" s="29">
         <f>C4*'Share of Pollutants'!$B$20</f>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="B7" s="29">
         <f>B4*'Share of Pollutants'!$B$21</f>
-        <v>60003432.871264853</v>
+        <v>53620088.948789872</v>
       </c>
       <c r="C7" s="29">
         <f>C4*'Share of Pollutants'!$B$21</f>
@@ -12855,10 +12855,10 @@
       </c>
       <c r="B11" s="29">
         <f>B5*$B$8</f>
-        <v>220447809085225.66</v>
+        <v>196995914501691</v>
       </c>
       <c r="C11" s="29">
-        <f t="shared" ref="C11:BN12" si="1">C5*$B$8</f>
+        <f t="shared" ref="C11:AZ12" si="1">C5*$B$8</f>
         <v>191132940855807.38</v>
       </c>
       <c r="D11" s="29">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="B12" s="29">
         <f t="shared" ref="B12:Q13" si="2">B6*$B$8</f>
-        <v>95548758043509.469</v>
+        <v>85383996549519.094</v>
       </c>
       <c r="C12" s="29">
         <f t="shared" si="2"/>
@@ -13311,10 +13311,10 @@
       </c>
       <c r="B13" s="29">
         <f t="shared" si="2"/>
-        <v>60003432871264.852</v>
+        <v>53620088948789.875</v>
       </c>
       <c r="C13" s="29">
-        <f t="shared" ref="C13:BN13" si="3">C7*$B$8</f>
+        <f t="shared" ref="C13:AZ13" si="3">C7*$B$8</f>
         <v>52024252968171.117</v>
       </c>
       <c r="D13" s="29">
@@ -13612,10 +13612,10 @@
       </c>
       <c r="B15" s="29">
         <f>B11/$B$22</f>
-        <v>220447809085225.66</v>
+        <v>196995914501691</v>
       </c>
       <c r="C15" s="29">
-        <f t="shared" ref="C15:BN15" si="4">C11/$B$22</f>
+        <f t="shared" ref="C15:AZ15" si="4">C11/$B$22</f>
         <v>191132940855807.38</v>
       </c>
       <c r="D15" s="29">
@@ -13840,10 +13840,10 @@
       </c>
       <c r="B16" s="29">
         <f>B12/$B$23</f>
-        <v>3412455644411.0522</v>
+        <v>3049428448197.1104</v>
       </c>
       <c r="C16" s="29">
-        <f t="shared" ref="C16:BN16" si="5">C12/$B$23</f>
+        <f t="shared" ref="C16:AZ16" si="5">C12/$B$23</f>
         <v>2958671649143.625</v>
       </c>
       <c r="D16" s="29">
@@ -14068,10 +14068,10 @@
       </c>
       <c r="B17" s="29">
         <f>B13/$B$24</f>
-        <v>226428048570.81076</v>
+        <v>202339958297.32028</v>
       </c>
       <c r="C17" s="29">
-        <f t="shared" ref="C17:BN17" si="6">C13/$B$24</f>
+        <f t="shared" ref="C17:AZ17" si="6">C13/$B$24</f>
         <v>196317935728.9476</v>
       </c>
       <c r="D17" s="29">
@@ -15355,7 +15355,7 @@
       </c>
       <c r="B2" s="24">
         <f>'Global Watch Data'!B15</f>
-        <v>220447809085225.66</v>
+        <v>196995914501691</v>
       </c>
       <c r="C2" s="24">
         <f>'Global Watch Data'!C15</f>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="B11" s="27">
         <f>'Global Watch Data'!B16</f>
-        <v>3412455644411.0522</v>
+        <v>3049428448197.1104</v>
       </c>
       <c r="C11" s="27">
         <f>'Global Watch Data'!C16</f>
@@ -17037,7 +17037,7 @@
       </c>
       <c r="B12" s="27">
         <f>'Global Watch Data'!B17</f>
-        <v>226428048570.81076</v>
+        <v>202339958297.32028</v>
       </c>
       <c r="C12" s="27">
         <f>'Global Watch Data'!C17</f>

--- a/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
+++ b/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/land/BLAPE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CF161F-5235-DC43-9FE3-FDC7489E1C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54440B6-3C19-984A-89B4-6C13699EAB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
